--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aeed6c68800b108e/Bureaublad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Bayer\fastCAPv2\fastCAP-backend\srv\xlsx-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{5AD4E6D3-988B-499C-93AC-2F92E5DBE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3669B00E-362F-4B5C-8667-4AA71D1E8CF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCD3417-AF0E-4A8F-8E07-6B52F4321981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Procurement Method</t>
   </si>
   <si>
-    <t>!!! Missing from OfferValidation !!!</t>
-  </si>
-  <si>
     <t>Contract Number</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>Delivery Terms</t>
   </si>
   <si>
-    <t>SKU Code</t>
-  </si>
-  <si>
     <t>Article Name</t>
   </si>
   <si>
@@ -155,12 +149,6 @@
     <t>${table:offerProductValidation.FOC}</t>
   </si>
   <si>
-    <t>${table:offerProductValidation.UNIT === 'Unit' ? offerProductValidation.TOTAL_QUANTITY_UNITS + ' ' + offerProductValidation.UNIT + 's' : (offerProductValidation.TOTAL_QUANTITY_UNITS / offerProductValidation.PACKSIZE) + ' ' + offerProductValidation.UNIT + 's'}</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.NET_PRICE + ' ' + offerProductValidation.CURRENCY}</t>
-  </si>
-  <si>
     <t>Total Amount</t>
   </si>
   <si>
@@ -170,21 +158,6 @@
     <t>Total Amount with VAT</t>
   </si>
   <si>
-    <t>${offerValidation.AMOUNT_IN_NUMBERS + ' ' + offerValidation.CURRENCY}</t>
-  </si>
-  <si>
-    <t>${offerValidation.VAT_TOTAL + ' ' + offerValidation.CURRENCY}</t>
-  </si>
-  <si>
-    <t>${offerValidation.AMOUNT_IN_NUMBERS_VAT + ' ' + offerValidation.CURRENCY}</t>
-  </si>
-  <si>
-    <t>In page: {fastAppData&gt;/EditTender/PROCUREMENT_METHOD_ID} {fastAppData&gt;/EditTender/PROCUREMENT_REASON}</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.PAID_VOLUME}</t>
   </si>
   <si>
@@ -237,13 +210,70 @@
   </si>
   <si>
     <t>SORTER</t>
+  </si>
+  <si>
+    <t>Header fields</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Product table fields</t>
+  </si>
+  <si>
+    <t>SKU CODE</t>
+  </si>
+  <si>
+    <t>Article name</t>
+  </si>
+  <si>
+    <t>Total Quantity Units</t>
+  </si>
+  <si>
+    <t>Total QTY</t>
+  </si>
+  <si>
+    <t>Net Price</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.NET_PRICE}</t>
+  </si>
+  <si>
+    <t>Amount in numbers</t>
+  </si>
+  <si>
+    <t>${offerValidation.AMOUNT_IN_NUMBERS}</t>
+  </si>
+  <si>
+    <t>VAT total</t>
+  </si>
+  <si>
+    <t>${offerValidation.AMOUNT_IN_NUMBERS_VAT}</t>
+  </si>
+  <si>
+    <t>Amount in numbers vat</t>
+  </si>
+  <si>
+    <t>${offerValidation.PROCUREMENT_REASON}</t>
+  </si>
+  <si>
+    <t>Procurement reason</t>
+  </si>
+  <si>
+    <t>${offerValidation.VAT_TOTAL}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.TOTAL_QUANTITY_UNITS}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,16 +313,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -320,11 +364,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -349,12 +437,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -364,11 +455,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -392,9 +536,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:colOff>1348740</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -437,6 +581,47 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}" name="Tabel1" displayName="Tabel1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:B13" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{22EAB7A2-53F9-497F-A4B5-CA34E48AC441}" name="Header fields"/>
+    <tableColumn id="2" xr3:uid="{331DD14B-B263-41D9-B2C5-D198B6F2436E}" name="Description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}" name="Tabel2" displayName="Tabel2" ref="C17:U52" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="C17:U52" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{6E1F8ECB-E862-46B4-998C-BE8E89C238BA}" name="PAID VOLUME"/>
+    <tableColumn id="2" xr3:uid="{6497AF92-63C8-4790-818D-6E5BE819E8D6}" name="UNIT"/>
+    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{1CB5E955-18ED-4738-ACA1-E270D15916F8}" name="CURRENCY"/>
+    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{06958303-4A18-40AA-8AD0-9A7EEFDCAF3E}" name="OFFER_ID"/>
+    <tableColumn id="9" xr3:uid="{A1218AAF-0481-41A2-9C10-3038D1BF8C7D}" name="SORTER"/>
+    <tableColumn id="10" xr3:uid="{5A7FFAC3-1C22-44BF-8C52-F3578967B0F3}" name="Pack Factor"/>
+    <tableColumn id="11" xr3:uid="{2D111679-3BB3-4B04-986E-34E61AC9B6D1}" name="Samples"/>
+    <tableColumn id="12" xr3:uid="{4A42B0A1-255A-4E7E-955E-674BA8AAA444}" name="Origin"/>
+    <tableColumn id="13" xr3:uid="{7D1379AA-4B8F-4BC6-9726-365EBAE15341}" name="FOC"/>
+    <tableColumn id="14" xr3:uid="{DF88A36E-0423-48FC-A1FC-B18BF3BA8D1A}" name="Total Quantity Units"/>
+    <tableColumn id="15" xr3:uid="{6B128E87-63EB-483B-88D7-EA33600F43AB}" name="Total QTY" dataDxfId="0">
+      <calculatedColumnFormula>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{E4D044B6-D053-487A-AA8C-F40FE34F30A7}" name="Net Price"/>
+    <tableColumn id="17" xr3:uid="{F95E93A8-C80D-4AC7-9526-72374F546CE7}" name="Amount in numbers"/>
+    <tableColumn id="18" xr3:uid="{2DDE85E8-6C8E-4D93-A4E8-1F80D965246B}" name="VAT total"/>
+    <tableColumn id="19" xr3:uid="{F55B5874-4E65-4E44-AEFE-7CFF114E939A}" name="Amount in numbers vat"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,39 +921,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F4731A-D70B-4034-AE07-DF495FD0B95B}">
-  <dimension ref="C3:Q66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:Q36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="10" width="20.7109375" customWidth="1"/>
-    <col min="16" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="1" max="2" width="2.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="10" width="20.6640625" customWidth="1"/>
+    <col min="16" max="17" width="20.6640625" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="str">
+        <f>Settings!A9</f>
+        <v>${offerValidation.INSTITUTENAME}</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="D5" s="4" t="str">
+        <f>Settings!A10</f>
+        <v>${offerValidation.PROCUREMENT_REASON}</v>
+      </c>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -785,43 +970,47 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-    </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C8" s="20" t="str">
+        <f>Settings!A2</f>
+        <v>${offerValidation.OFFERID}</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="19" t="str">
+        <f>Settings!A3</f>
+        <v>${offerValidation.TENDERID}</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19" t="str">
+        <f>Settings!A4</f>
+        <v>${offerValidation.OFFERDATE}</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19" t="str">
+        <f>Settings!A5</f>
+        <v>${offerValidation.OFFERVALIDITY}</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -838,598 +1027,1054 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="1" t="s">
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C11" s="21" t="str">
+        <f>Settings!A6</f>
+        <v>${offerValidation.SHIPMENTTERMS}</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21" t="str">
+        <f>Settings!A7</f>
+        <v>${offerValidation.PAYMENTTERMS}</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21" t="str">
+        <f>Settings!A8</f>
+        <v>${offerValidation.DELIVERYTERMS}</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+    </row>
+    <row r="12" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C11" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-    </row>
-    <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="L13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="P13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="Q13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="P13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
+    </row>
+    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C14" t="str">
+        <f>IF(Settings!A18="","",Settings!A18)</f>
+        <v>${table:offerProductValidation.SKU}</v>
+      </c>
+      <c r="D14" t="str">
+        <f>IF(Settings!B18="","",Settings!B18)</f>
+        <v>${table:offerProductValidation.PRODUCT_UNIT_NAME}</v>
       </c>
       <c r="E14" t="str">
-        <f>IF(CONCATENATE(Quotation!C66," ",Quotation!D66,"s")=" s"," ",CONCATENATE(Quotation!C66," ",Quotation!D66,"s"))</f>
+        <f>IF(CONCATENATE(Settings!C18," ",Settings!D18,"s")=" s"," ",CONCATENATE(Settings!C18," ",Settings!D18,"s"))</f>
         <v>${table:offerProductValidation.PAID_VOLUME} ${table:offerProductValidation.UNIT}s</v>
       </c>
-      <c r="F14" t="s">
-        <v>34</v>
+      <c r="F14" t="str">
+        <f>IF(Settings!L18="","",Settings!L18)</f>
+        <v>${table:offerProductValidation.PACKSIZE}</v>
       </c>
       <c r="G14" t="str">
-        <f>CONCATENATE(E66," ",F66)</f>
+        <f>CONCATENATE(Settings!E18," ",Settings!F18)</f>
         <v>${table:offerProductValidation.OFFER_PRICE} ${table:offerProductValidation.CURRENCY}</v>
       </c>
       <c r="H14" t="str">
-        <f>CONCATENATE(G66," ",F66)</f>
+        <f>CONCATENATE(Settings!G18," ",Settings!F18)</f>
         <v>${table:offerProductValidation.OFFER_PRICE_VAT} ${table:offerProductValidation.CURRENCY}</v>
       </c>
       <c r="I14" t="str">
-        <f>CONCATENATE(H66," ",F66)</f>
+        <f>CONCATENATE(Settings!H18," ",Settings!F18)</f>
         <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY} ${table:offerProductValidation.CURRENCY}</v>
       </c>
       <c r="J14" t="str">
-        <f>CONCATENATE(I66," ",F66)</f>
+        <f>CONCATENATE(Settings!I18," ",Settings!F18)</f>
         <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY_VAT} ${table:offerProductValidation.CURRENCY}</v>
       </c>
-      <c r="L14" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="L14" t="str">
+        <f>IF(Settings!M18="","",Settings!M18)</f>
+        <v>${table:offerProductValidation.SAMPLES}</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IF(Settings!N18="","",Settings!N18)</f>
+        <v>${table:offerProductValidation.COUNTRYOFORIGIN}</v>
+      </c>
+      <c r="N14" t="str">
+        <f>IF(CONCATENATE(Settings!J18,"-",Settings!K18) = "-","",CONCATENATE(Settings!J18,"-",Settings!K18))</f>
+        <v>${table:offerProductValidation.OFFER_ID}-${table:offerProductValidation.SORTER}</v>
+      </c>
+      <c r="O14" t="str">
+        <f>IF(Settings!O18="","",Settings!O18)</f>
+        <v>${table:offerProductValidation.FOC}</v>
+      </c>
+      <c r="P14" t="e">
+        <f>Settings!Q18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>_xlfn.CONCAT(Settings!R18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.NET_PRICE} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C15" t="str">
+        <f>IF(Settings!A19="","",Settings!A19)</f>
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <f>IF(Settings!B19="","",Settings!B19)</f>
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <f>IF(CONCATENATE(Settings!C19," ",Settings!D19,"s")=" s"," ",CONCATENATE(Settings!C19," ",Settings!D19,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F15" t="str">
+        <f>IF(Settings!L19="","",Settings!L19)</f>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <f>CONCATENATE(Settings!E19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H15" t="str">
+        <f>CONCATENATE(Settings!G19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I15" t="str">
+        <f>CONCATENATE(Settings!H19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J15" t="str">
+        <f>CONCATENATE(Settings!I19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L15" t="str">
+        <f>IF(Settings!M19="","",Settings!M19)</f>
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <f>IF(Settings!N19="","",Settings!N19)</f>
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <f>IF(CONCATENATE(Settings!J19,"-",Settings!K19) = "-","",CONCATENATE(Settings!J19,"-",Settings!K19))</f>
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <f>IF(Settings!O19="","",Settings!O19)</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <f>Settings!Q19</f>
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <f>_xlfn.CONCAT(Settings!R19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C16" t="str">
+        <f>IF(Settings!A20="","",Settings!A20)</f>
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(Settings!B20="","",Settings!B20)</f>
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <f>IF(CONCATENATE(Settings!C20," ",Settings!D20,"s")=" s"," ",CONCATENATE(Settings!C20," ",Settings!D20,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(Settings!L20="","",Settings!L20)</f>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <f>CONCATENATE(Settings!E20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H16" t="str">
+        <f>CONCATENATE(Settings!G20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I16" t="str">
+        <f>CONCATENATE(Settings!H20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J16" t="str">
+        <f>CONCATENATE(Settings!I20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L16" t="str">
+        <f>IF(Settings!M20="","",Settings!M20)</f>
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <f>IF(Settings!N20="","",Settings!N20)</f>
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <f>IF(CONCATENATE(Settings!J20,"-",Settings!K20) = "-","",CONCATENATE(Settings!J20,"-",Settings!K20))</f>
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <f>IF(Settings!O20="","",Settings!O20)</f>
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <f>Settings!Q20</f>
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <f>_xlfn.CONCAT(Settings!R20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C17" t="str">
+        <f>IF(Settings!A21="","",Settings!A21)</f>
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <f>IF(Settings!B21="","",Settings!B21)</f>
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(CONCATENATE(Settings!C21," ",Settings!D21,"s")=" s"," ",CONCATENATE(Settings!C21," ",Settings!D21,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(Settings!L21="","",Settings!L21)</f>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <f>CONCATENATE(Settings!E21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H17" t="str">
+        <f>CONCATENATE(Settings!G21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I17" t="str">
+        <f>CONCATENATE(Settings!H21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J17" t="str">
+        <f>CONCATENATE(Settings!I21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L17" t="str">
+        <f>IF(Settings!M21="","",Settings!M21)</f>
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <f>IF(Settings!N21="","",Settings!N21)</f>
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <f>IF(CONCATENATE(Settings!J21,"-",Settings!K21) = "-","",CONCATENATE(Settings!J21,"-",Settings!K21))</f>
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <f>IF(Settings!O21="","",Settings!O21)</f>
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <f>Settings!Q21</f>
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <f>_xlfn.CONCAT(Settings!R21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C18" t="str">
+        <f>IF(Settings!A22="","",Settings!A22)</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f>IF(Settings!B22="","",Settings!B22)</f>
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(CONCATENATE(Settings!C22," ",Settings!D22,"s")=" s"," ",CONCATENATE(Settings!C22," ",Settings!D22,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(Settings!L22="","",Settings!L22)</f>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <f>CONCATENATE(Settings!E22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H18" t="str">
+        <f>CONCATENATE(Settings!G22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I18" t="str">
+        <f>CONCATENATE(Settings!H22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J18" t="str">
+        <f>CONCATENATE(Settings!I22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L18" t="str">
+        <f>IF(Settings!M22="","",Settings!M22)</f>
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <f>IF(Settings!N22="","",Settings!N22)</f>
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <f>IF(CONCATENATE(Settings!J22,"-",Settings!K22) = "-","",CONCATENATE(Settings!J22,"-",Settings!K22))</f>
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <f>IF(Settings!O22="","",Settings!O22)</f>
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <f>Settings!Q22</f>
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <f>_xlfn.CONCAT(Settings!R22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C19" t="str">
+        <f>IF(Settings!A23="","",Settings!A23)</f>
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <f>IF(Settings!B23="","",Settings!B23)</f>
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <f>IF(CONCATENATE(Settings!C23," ",Settings!D23,"s")=" s"," ",CONCATENATE(Settings!C23," ",Settings!D23,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F19" t="str">
+        <f>IF(Settings!L23="","",Settings!L23)</f>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <f>CONCATENATE(Settings!E23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H19" t="str">
+        <f>CONCATENATE(Settings!G23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I19" t="str">
+        <f>CONCATENATE(Settings!H23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J19" t="str">
+        <f>CONCATENATE(Settings!I23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L19" t="str">
+        <f>IF(Settings!M23="","",Settings!M23)</f>
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <f>IF(Settings!N23="","",Settings!N23)</f>
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <f>IF(CONCATENATE(Settings!J23,"-",Settings!K23) = "-","",CONCATENATE(Settings!J23,"-",Settings!K23))</f>
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <f>IF(Settings!O23="","",Settings!O23)</f>
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <f>Settings!Q23</f>
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <f>_xlfn.CONCAT(Settings!R23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C20" t="str">
+        <f>IF(Settings!A24="","",Settings!A24)</f>
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <f>IF(Settings!B24="","",Settings!B24)</f>
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <f>IF(CONCATENATE(Settings!C24," ",Settings!D24,"s")=" s"," ",CONCATENATE(Settings!C24," ",Settings!D24,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F20" t="str">
+        <f>IF(Settings!L24="","",Settings!L24)</f>
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <f>CONCATENATE(Settings!E24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H20" t="str">
+        <f>CONCATENATE(Settings!G24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I20" t="str">
+        <f>CONCATENATE(Settings!H24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J20" t="str">
+        <f>CONCATENATE(Settings!I24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L20" t="str">
+        <f>IF(Settings!M24="","",Settings!M24)</f>
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <f>IF(Settings!N24="","",Settings!N24)</f>
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <f>IF(CONCATENATE(Settings!J24,"-",Settings!K24) = "-","",CONCATENATE(Settings!J24,"-",Settings!K24))</f>
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <f>IF(Settings!O24="","",Settings!O24)</f>
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <f>Settings!Q24</f>
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <f>_xlfn.CONCAT(Settings!R24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C21" t="str">
+        <f>IF(Settings!A25="","",Settings!A25)</f>
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(Settings!B25="","",Settings!B25)</f>
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(CONCATENATE(Settings!C25," ",Settings!D25,"s")=" s"," ",CONCATENATE(Settings!C25," ",Settings!D25,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(Settings!L25="","",Settings!L25)</f>
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <f>CONCATENATE(Settings!E25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H21" t="str">
+        <f>CONCATENATE(Settings!G25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I21" t="str">
+        <f>CONCATENATE(Settings!H25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J21" t="str">
+        <f>CONCATENATE(Settings!I25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(Settings!M25="","",Settings!M25)</f>
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(Settings!N25="","",Settings!N25)</f>
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(CONCATENATE(Settings!J25,"-",Settings!K25) = "-","",CONCATENATE(Settings!J25,"-",Settings!K25))</f>
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(Settings!O25="","",Settings!O25)</f>
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <f>Settings!Q25</f>
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <f>_xlfn.CONCAT(Settings!R25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C22" t="str">
+        <f>IF(Settings!A26="","",Settings!A26)</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(Settings!B26="","",Settings!B26)</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(CONCATENATE(Settings!C26," ",Settings!D26,"s")=" s"," ",CONCATENATE(Settings!C26," ",Settings!D26,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(Settings!L26="","",Settings!L26)</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>CONCATENATE(Settings!E26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H22" t="str">
+        <f>CONCATENATE(Settings!G26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I22" t="str">
+        <f>CONCATENATE(Settings!H26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J22" t="str">
+        <f>CONCATENATE(Settings!I26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(Settings!M26="","",Settings!M26)</f>
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(Settings!N26="","",Settings!N26)</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <f>IF(CONCATENATE(Settings!J26,"-",Settings!K26) = "-","",CONCATENATE(Settings!J26,"-",Settings!K26))</f>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <f>IF(Settings!O26="","",Settings!O26)</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <f>Settings!Q26</f>
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <f>_xlfn.CONCAT(Settings!R26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C23" t="str">
+        <f>IF(Settings!A27="","",Settings!A27)</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f>IF(Settings!B27="","",Settings!B27)</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(CONCATENATE(Settings!C27," ",Settings!D27,"s")=" s"," ",CONCATENATE(Settings!C27," ",Settings!D27,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(Settings!L27="","",Settings!L27)</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>CONCATENATE(Settings!E27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H23" t="str">
+        <f>CONCATENATE(Settings!G27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I23" t="str">
+        <f>CONCATENATE(Settings!H27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J23" t="str">
+        <f>CONCATENATE(Settings!I27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(Settings!M27="","",Settings!M27)</f>
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(Settings!N27="","",Settings!N27)</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <f>IF(CONCATENATE(Settings!J27,"-",Settings!K27) = "-","",CONCATENATE(Settings!J27,"-",Settings!K27))</f>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <f>IF(Settings!O27="","",Settings!O27)</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <f>Settings!Q27</f>
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <f>_xlfn.CONCAT(Settings!R27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C24" t="str">
+        <f>IF(Settings!A28="","",Settings!A28)</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(Settings!B28="","",Settings!B28)</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(CONCATENATE(Settings!C28," ",Settings!D28,"s")=" s"," ",CONCATENATE(Settings!C28," ",Settings!D28,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(Settings!L28="","",Settings!L28)</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>CONCATENATE(Settings!E28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H24" t="str">
+        <f>CONCATENATE(Settings!G28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I24" t="str">
+        <f>CONCATENATE(Settings!H28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J24" t="str">
+        <f>CONCATENATE(Settings!I28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(Settings!M28="","",Settings!M28)</f>
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(Settings!N28="","",Settings!N28)</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <f>IF(CONCATENATE(Settings!J28,"-",Settings!K28) = "-","",CONCATENATE(Settings!J28,"-",Settings!K28))</f>
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <f>IF(Settings!O28="","",Settings!O28)</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <f>Settings!Q28</f>
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <f>_xlfn.CONCAT(Settings!R28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C25" t="str">
+        <f>IF(Settings!A29="","",Settings!A29)</f>
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <f>IF(Settings!B29="","",Settings!B29)</f>
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(CONCATENATE(Settings!C29," ",Settings!D29,"s")=" s"," ",CONCATENATE(Settings!C29," ",Settings!D29,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F25" t="str">
+        <f>IF(Settings!L29="","",Settings!L29)</f>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <f>CONCATENATE(Settings!E29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H25" t="str">
+        <f>CONCATENATE(Settings!G29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I25" t="str">
+        <f>CONCATENATE(Settings!H29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J25" t="str">
+        <f>CONCATENATE(Settings!I29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L25" t="str">
+        <f>IF(Settings!M29="","",Settings!M29)</f>
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <f>IF(Settings!N29="","",Settings!N29)</f>
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <f>IF(CONCATENATE(Settings!J29,"-",Settings!K29) = "-","",CONCATENATE(Settings!J29,"-",Settings!K29))</f>
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <f>IF(Settings!O29="","",Settings!O29)</f>
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <f>Settings!Q29</f>
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <f>_xlfn.CONCAT(Settings!R29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C26" t="str">
+        <f>IF(Settings!A30="","",Settings!A30)</f>
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <f>IF(Settings!B30="","",Settings!B30)</f>
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <f>IF(CONCATENATE(Settings!C30," ",Settings!D30,"s")=" s"," ",CONCATENATE(Settings!C30," ",Settings!D30,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F26" t="str">
+        <f>IF(Settings!L30="","",Settings!L30)</f>
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <f>CONCATENATE(Settings!E30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H26" t="str">
+        <f>CONCATENATE(Settings!G30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I26" t="str">
+        <f>CONCATENATE(Settings!H30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J26" t="str">
+        <f>CONCATENATE(Settings!I30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(Settings!M30="","",Settings!M30)</f>
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(Settings!N30="","",Settings!N30)</f>
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <f>IF(CONCATENATE(Settings!J30,"-",Settings!K30) = "-","",CONCATENATE(Settings!J30,"-",Settings!K30))</f>
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <f>IF(Settings!O30="","",Settings!O30)</f>
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <f>Settings!Q30</f>
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <f>_xlfn.CONCAT(Settings!R30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C27" t="str">
+        <f>IF(Settings!A31="","",Settings!A31)</f>
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <f>IF(Settings!B31="","",Settings!B31)</f>
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(CONCATENATE(Settings!C31," ",Settings!D31,"s")=" s"," ",CONCATENATE(Settings!C31," ",Settings!D31,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F27" t="str">
+        <f>IF(Settings!L31="","",Settings!L31)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>CONCATENATE(Settings!E31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H27" t="str">
+        <f>CONCATENATE(Settings!G31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I27" t="str">
+        <f>CONCATENATE(Settings!H31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J27" t="str">
+        <f>CONCATENATE(Settings!I31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(Settings!M31="","",Settings!M31)</f>
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <f>IF(Settings!N31="","",Settings!N31)</f>
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <f>IF(CONCATENATE(Settings!J31,"-",Settings!K31) = "-","",CONCATENATE(Settings!J31,"-",Settings!K31))</f>
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <f>IF(Settings!O31="","",Settings!O31)</f>
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <f>Settings!Q31</f>
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <f>_xlfn.CONCAT(Settings!R31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C28" t="str">
+        <f>IF(Settings!A32="","",Settings!A32)</f>
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <f>IF(Settings!B32="","",Settings!B32)</f>
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(CONCATENATE(Settings!C32," ",Settings!D32,"s")=" s"," ",CONCATENATE(Settings!C32," ",Settings!D32,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F28" t="str">
+        <f>IF(Settings!L32="","",Settings!L32)</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>CONCATENATE(Settings!E32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H28" t="str">
+        <f>CONCATENATE(Settings!G32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I28" t="str">
+        <f>CONCATENATE(Settings!H32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J28" t="str">
+        <f>CONCATENATE(Settings!I32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" ref="N28:N33" si="0">IF(CONCATENATE(J80,"-",K80) = "-","",CONCATENATE(J80,"-",K80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C29" t="str">
+        <f>IF(Settings!A33="","",Settings!A33)</f>
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <f>IF(Settings!B33="","",Settings!B33)</f>
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(CONCATENATE(Settings!C33," ",Settings!D33,"s")=" s"," ",CONCATENATE(Settings!C33," ",Settings!D33,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F29" t="str">
+        <f>IF(Settings!L33="","",Settings!L33)</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>CONCATENATE(Settings!E33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H29" t="str">
+        <f>CONCATENATE(Settings!G33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I29" t="str">
+        <f>CONCATENATE(Settings!H33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J29" t="str">
+        <f>CONCATENATE(Settings!I33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N14" t="str">
-        <f>IF(CONCATENATE(J66,"-",K66) = "-","",CONCATENATE(J66,"-",K66))</f>
-        <v>${table:offerProductValidation.OFFER_ID}-${table:offerProductValidation.SORTER}</v>
-      </c>
-      <c r="O14" t="s">
-        <v>37</v>
-      </c>
-      <c r="P14" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E15" t="str">
-        <f>IF(CONCATENATE(Quotation!C67," ",Quotation!D67,"s")=" s"," ",CONCATENATE(Quotation!C67," ",Quotation!D67,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" ref="G15:G34" si="0">CONCATENATE(E67," ",F67)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" ref="H15:H35" si="1">CONCATENATE(G67," ",F67)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I15" t="str">
-        <f t="shared" ref="I15:I35" si="2">CONCATENATE(H67," ",F67)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" ref="J15:J34" si="3">CONCATENATE(I67," ",F67)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N15" t="str">
-        <f t="shared" ref="N15:N33" si="4">IF(CONCATENATE(J67,"-",K67) = "-","",CONCATENATE(J67,"-",K67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E16" t="str">
-        <f>IF(CONCATENATE(Quotation!C68," ",Quotation!D68,"s")=" s"," ",CONCATENATE(Quotation!C68," ",Quotation!D68,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G16" t="str">
+      <c r="Q29" t="str">
+        <f>_xlfn.CONCAT(Settings!S18," ",Settings!F18)</f>
+        <v>${offerValidation.AMOUNT_IN_NUMBERS} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C30" t="str">
+        <f>IF(Settings!A34="","",Settings!A34)</f>
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <f>IF(Settings!B34="","",Settings!B34)</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF(CONCATENATE(Settings!C34," ",Settings!D34,"s")=" s"," ",CONCATENATE(Settings!C34," ",Settings!D34,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F30" t="str">
+        <f>IF(Settings!L34="","",Settings!L34)</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>CONCATENATE(Settings!E34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H30" t="str">
+        <f>CONCATENATE(Settings!G34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I30" t="str">
+        <f>CONCATENATE(Settings!H34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J30" t="str">
+        <f>CONCATENATE(Settings!I34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H16" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I16" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J16" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E17" t="str">
-        <f>IF(CONCATENATE(Quotation!C69," ",Quotation!D69,"s")=" s"," ",CONCATENATE(Quotation!C69," ",Quotation!D69,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H17" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I17" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J17" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N17" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P17" s="8"/>
-    </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" t="str">
-        <f>IF(CONCATENATE(Quotation!C70," ",Quotation!D70,"s")=" s"," ",CONCATENATE(Quotation!C70," ",Quotation!D70,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G18" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I18" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J18" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E19" t="str">
-        <f>IF(CONCATENATE(Quotation!C71," ",Quotation!D71,"s")=" s"," ",CONCATENATE(Quotation!C71," ",Quotation!D71,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J19" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P19" s="8"/>
-    </row>
-    <row r="20" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E20" t="str">
-        <f>IF(CONCATENATE(Quotation!C72," ",Quotation!D72,"s")=" s"," ",CONCATENATE(Quotation!C72," ",Quotation!D72,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H20" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I20" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J20" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N20" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E21" t="str">
-        <f>IF(CONCATENATE(Quotation!C73," ",Quotation!D73,"s")=" s"," ",CONCATENATE(Quotation!C73," ",Quotation!D73,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H21" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I21" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J21" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E22" t="str">
-        <f>IF(CONCATENATE(Quotation!C74," ",Quotation!D74,"s")=" s"," ",CONCATENATE(Quotation!C74," ",Quotation!D74,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G22" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I22" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J22" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N22" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E23" t="str">
-        <f>IF(CONCATENATE(Quotation!C75," ",Quotation!D75,"s")=" s"," ",CONCATENATE(Quotation!C75," ",Quotation!D75,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H23" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I23" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J23" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N23" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E24" t="str">
-        <f>IF(CONCATENATE(Quotation!C76," ",Quotation!D76,"s")=" s"," ",CONCATENATE(Quotation!C76," ",Quotation!D76,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J24" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N24" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E25" t="str">
-        <f>IF(CONCATENATE(Quotation!C77," ",Quotation!D77,"s")=" s"," ",CONCATENATE(Quotation!C77," ",Quotation!D77,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I25" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J25" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E26" t="str">
-        <f>IF(CONCATENATE(Quotation!C78," ",Quotation!D78,"s")=" s"," ",CONCATENATE(Quotation!C78," ",Quotation!D78,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I26" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J26" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N26" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E27" t="str">
-        <f>IF(CONCATENATE(Quotation!C79," ",Quotation!D79,"s")=" s"," ",CONCATENATE(Quotation!C79," ",Quotation!D79,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J27" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N27" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E28" t="str">
-        <f>IF(CONCATENATE(Quotation!C80," ",Quotation!D80,"s")=" s"," ",CONCATENATE(Quotation!C80," ",Quotation!D80,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J28" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N28" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E29" t="str">
-        <f>IF(CONCATENATE(Quotation!C81," ",Quotation!D81,"s")=" s"," ",CONCATENATE(Quotation!C81," ",Quotation!D81,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J29" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N29" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E30" t="str">
-        <f>IF(CONCATENATE(Quotation!C82," ",Quotation!D82,"s")=" s"," ",CONCATENATE(Quotation!C82," ",Quotation!D82,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I30" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J30" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N30" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="5:17" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="E31" t="str">
         <f>IF(CONCATENATE(Quotation!C83," ",Quotation!D83,"s")=" s"," ",CONCATENATE(Quotation!C83," ",Quotation!D83,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G31" t="str">
+        <f>CONCATENATE(Settings!E35," ",Settings!F35)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" ref="H31:H35" si="1">CONCATENATE(G83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" ref="I31:I35" si="2">CONCATENATE(H83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" ref="J31:J34" si="3">CONCATENATE(I83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I31" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J31" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N31" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="5:17" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q31" t="str">
+        <f>_xlfn.CONCAT(Settings!T18," ",Settings!F18)</f>
+        <v>${offerValidation.VAT_TOTAL} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="E32" t="str">
         <f>IF(CONCATENATE(Quotation!C84," ",Quotation!D84,"s")=" s"," ",CONCATENATE(Quotation!C84," ",Quotation!D84,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE(Settings!E36," ",Settings!F36)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H32" t="str">
@@ -1445,17 +2090,18 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="N32" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="5:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P32" s="8"/>
+    </row>
+    <row r="33" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E33" t="str">
         <f>IF(CONCATENATE(Quotation!C85," ",Quotation!D85,"s")=" s"," ",CONCATENATE(Quotation!C85," ",Quotation!D85,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE(Settings!E37," ",Settings!F37)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H33" t="str">
@@ -1471,17 +2117,24 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="N33" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="5:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q33" t="str">
+        <f>_xlfn.CONCAT(Settings!U18," ",Settings!F18)</f>
+        <v>${offerValidation.AMOUNT_IN_NUMBERS_VAT} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="34" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E34" t="str">
         <f>IF(CONCATENATE(Quotation!C86," ",Quotation!D86,"s")=" s"," ",CONCATENATE(Quotation!C86," ",Quotation!D86,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE(Settings!E38," ",Settings!F38)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H34" t="str">
@@ -1497,7 +2150,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E35" t="str">
         <f>IF(CONCATENATE(Quotation!C87," ",Quotation!D87,"s")=" s"," ",CONCATENATE(Quotation!C87," ",Quotation!D87,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -1511,73 +2164,10 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="5:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E36" t="str">
         <f>IF(CONCATENATE(Quotation!C88," ",Quotation!D88,"s")=" s"," ",CONCATENATE(Quotation!C88," ",Quotation!D88,"s"))</f>
         <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C65" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H65" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I65" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K65" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C66" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" t="s">
-        <v>52</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G66" t="s">
-        <v>57</v>
-      </c>
-      <c r="H66" t="s">
-        <v>58</v>
-      </c>
-      <c r="I66" t="s">
-        <v>60</v>
-      </c>
-      <c r="J66" t="s">
-        <v>62</v>
-      </c>
-      <c r="K66" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1598,15 +2188,663 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BADA0-6CEF-4001-8243-A13FFD1BF3BE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="75.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="52.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.21875" customWidth="1"/>
+    <col min="18" max="18" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="43.33203125" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="T17" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" t="s">
+        <v>34</v>
+      </c>
+      <c r="O18" t="s">
+        <v>35</v>
+      </c>
+      <c r="P18" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q18" t="e">
+        <f>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R18" t="s">
+        <v>65</v>
+      </c>
+      <c r="S18" t="s">
+        <v>67</v>
+      </c>
+      <c r="T18" t="s">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14"/>
+      <c r="E19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="Q19" t="str">
+        <f>IF(D19&gt;0,IF(D19="Unit",CONCATENATE(Settings!P19," ",Settings!D19,"s"),CONCATENATE((Settings!P19/Settings!L19)," ",Settings!D19,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="E20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="Q20" t="str">
+        <f>IF(D20&gt;0,IF(D20="Unit",CONCATENATE(Settings!P20," ",Settings!D20,"s"),CONCATENATE((Settings!P20/Settings!L20)," ",Settings!D20,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="E21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="Q21" t="str">
+        <f>IF(D21&gt;0,IF(D21="Unit",CONCATENATE(Settings!P21," ",Settings!D21,"s"),CONCATENATE((Settings!P21/Settings!L21)," ",Settings!D21,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="E22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="Q22" t="str">
+        <f>IF(D22&gt;0,IF(D22="Unit",CONCATENATE(Settings!P22," ",Settings!D22,"s"),CONCATENATE((Settings!P22/Settings!L22)," ",Settings!D22,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="E23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="Q23" t="str">
+        <f>IF(D23&gt;0,IF(D23="Unit",CONCATENATE(Settings!P23," ",Settings!D23,"s"),CONCATENATE((Settings!P23/Settings!L23)," ",Settings!D23,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="E24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="Q24" t="str">
+        <f>IF(D24&gt;0,IF(D24="Unit",CONCATENATE(Settings!P24," ",Settings!D24,"s"),CONCATENATE((Settings!P24/Settings!L24)," ",Settings!D24,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="E25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="Q25" t="str">
+        <f>IF(D25&gt;0,IF(D25="Unit",CONCATENATE(Settings!P25," ",Settings!D25,"s"),CONCATENATE((Settings!P25/Settings!L25)," ",Settings!D25,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="E26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="Q26" t="str">
+        <f>IF(D26&gt;0,IF(D26="Unit",CONCATENATE(Settings!P26," ",Settings!D26,"s"),CONCATENATE((Settings!P26/Settings!L26)," ",Settings!D26,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="E27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="Q27" t="str">
+        <f>IF(D27&gt;0,IF(D27="Unit",CONCATENATE(Settings!P27," ",Settings!D27,"s"),CONCATENATE((Settings!P27/Settings!L27)," ",Settings!D27,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="E28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="Q28" t="str">
+        <f>IF(D28&gt;0,IF(D28="Unit",CONCATENATE(Settings!P28," ",Settings!D28,"s"),CONCATENATE((Settings!P28/Settings!L28)," ",Settings!D28,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="E29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="Q29" t="str">
+        <f>IF(D29&gt;0,IF(D29="Unit",CONCATENATE(Settings!P29," ",Settings!D29,"s"),CONCATENATE((Settings!P29/Settings!L29)," ",Settings!D29,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="E30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="Q30" t="str">
+        <f>IF(D30&gt;0,IF(D30="Unit",CONCATENATE(Settings!P30," ",Settings!D30,"s"),CONCATENATE((Settings!P30/Settings!L30)," ",Settings!D30,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="E31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="Q31" t="str">
+        <f>IF(D31&gt;0,IF(D31="Unit",CONCATENATE(Settings!P31," ",Settings!D31,"s"),CONCATENATE((Settings!P31/Settings!L31)," ",Settings!D31,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="E32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="Q32" t="str">
+        <f>IF(D32&gt;0,IF(D32="Unit",CONCATENATE(Settings!P32," ",Settings!D32,"s"),CONCATENATE((Settings!P32/Settings!L32)," ",Settings!D32,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="E33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="Q33" t="str">
+        <f>IF(D33&gt;0,IF(D33="Unit",CONCATENATE(Settings!P33," ",Settings!D33,"s"),CONCATENATE((Settings!P33/Settings!L33)," ",Settings!D33,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="E34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="Q34" t="str">
+        <f>IF(D34&gt;0,IF(D34="Unit",CONCATENATE(Settings!P34," ",Settings!D34,"s"),CONCATENATE((Settings!P34/Settings!L34)," ",Settings!D34,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="E35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="Q35" t="str">
+        <f>IF(D35&gt;0,IF(D35="Unit",CONCATENATE(Settings!P35," ",Settings!D35,"s"),CONCATENATE((Settings!P35/Settings!L35)," ",Settings!D35,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="E36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="Q36" t="str">
+        <f>IF(D36&gt;0,IF(D36="Unit",CONCATENATE(Settings!P36," ",Settings!D36,"s"),CONCATENATE((Settings!P36/Settings!L36)," ",Settings!D36,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="13"/>
+      <c r="B37" s="14"/>
+      <c r="E37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="Q37" t="str">
+        <f>IF(D37&gt;0,IF(D37="Unit",CONCATENATE(Settings!P37," ",Settings!D37,"s"),CONCATENATE((Settings!P37/Settings!L37)," ",Settings!D37,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="E38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="Q38" t="str">
+        <f>IF(D38&gt;0,IF(D38="Unit",CONCATENATE(Settings!P38," ",Settings!D38,"s"),CONCATENATE((Settings!P38/Settings!L38)," ",Settings!D38,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14"/>
+      <c r="E39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="Q39" t="str">
+        <f>IF(D39&gt;0,IF(D39="Unit",CONCATENATE(Settings!P39," ",Settings!D39,"s"),CONCATENATE((Settings!P39/Settings!L39)," ",Settings!D39,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="E40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="Q40" t="str">
+        <f>IF(D40&gt;0,IF(D40="Unit",CONCATENATE(Settings!P40," ",Settings!D40,"s"),CONCATENATE((Settings!P40/Settings!L40)," ",Settings!D40,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="14"/>
+      <c r="E41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="Q41" t="str">
+        <f>IF(D41&gt;0,IF(D41="Unit",CONCATENATE(Settings!P41," ",Settings!D41,"s"),CONCATENATE((Settings!P41/Settings!L41)," ",Settings!D41,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="E42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="Q42" t="str">
+        <f>IF(D42&gt;0,IF(D42="Unit",CONCATENATE(Settings!P42," ",Settings!D42,"s"),CONCATENATE((Settings!P42/Settings!L42)," ",Settings!D42,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="E43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="Q43" t="str">
+        <f>IF(D43&gt;0,IF(D43="Unit",CONCATENATE(Settings!P43," ",Settings!D43,"s"),CONCATENATE((Settings!P43/Settings!L43)," ",Settings!D43,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="E44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="Q44" t="str">
+        <f>IF(D44&gt;0,IF(D44="Unit",CONCATENATE(Settings!P44," ",Settings!D44,"s"),CONCATENATE((Settings!P44/Settings!L44)," ",Settings!D44,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="E45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="Q45" t="str">
+        <f>IF(D45&gt;0,IF(D45="Unit",CONCATENATE(Settings!P45," ",Settings!D45,"s"),CONCATENATE((Settings!P45/Settings!L45)," ",Settings!D45,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="14"/>
+      <c r="E46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="Q46" t="str">
+        <f>IF(D46&gt;0,IF(D46="Unit",CONCATENATE(Settings!P46," ",Settings!D46,"s"),CONCATENATE((Settings!P46/Settings!L46)," ",Settings!D46,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="14"/>
+      <c r="E47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="Q47" t="str">
+        <f>IF(D47&gt;0,IF(D47="Unit",CONCATENATE(Settings!P47," ",Settings!D47,"s"),CONCATENATE((Settings!P47/Settings!L47)," ",Settings!D47,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="E48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="Q48" t="str">
+        <f>IF(D48&gt;0,IF(D48="Unit",CONCATENATE(Settings!P48," ",Settings!D48,"s"),CONCATENATE((Settings!P48/Settings!L48)," ",Settings!D48,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="E49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="Q49" t="str">
+        <f>IF(D49&gt;0,IF(D49="Unit",CONCATENATE(Settings!P49," ",Settings!D49,"s"),CONCATENATE((Settings!P49/Settings!L49)," ",Settings!D49,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="14"/>
+      <c r="E50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="Q50" t="str">
+        <f>IF(D50&gt;0,IF(D50="Unit",CONCATENATE(Settings!P50," ",Settings!D50,"s"),CONCATENATE((Settings!P50/Settings!L50)," ",Settings!D50,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="E51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="Q51" t="str">
+        <f>IF(D51&gt;0,IF(D51="Unit",CONCATENATE(Settings!P51," ",Settings!D51,"s"),CONCATENATE((Settings!P51/Settings!L51)," ",Settings!D51,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" s="15"/>
+      <c r="B52" s="16"/>
+      <c r="E52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="Q52" t="str">
+        <f>IF(D52&gt;0,IF(D52="Unit",CONCATENATE(Settings!P52," ",Settings!D52,"s"),CONCATENATE((Settings!P52/Settings!L52)," ",Settings!D52,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1625,15 +2863,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -1830,6 +3059,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>
@@ -1841,14 +3079,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1865,4 +3095,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Bayer\fastCAPv2\fastCAP-backend\srv\xlsx-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCD3417-AF0E-4A8F-8E07-6B52F4321981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662F4A3F-58DB-4ADA-97CB-1B95B82C8CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="75">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -271,7 +271,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+    <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -434,18 +434,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -455,26 +456,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
       <font>
@@ -600,11 +600,11 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{6E1F8ECB-E862-46B4-998C-BE8E89C238BA}" name="PAID VOLUME"/>
     <tableColumn id="2" xr3:uid="{6497AF92-63C8-4790-818D-6E5BE819E8D6}" name="UNIT"/>
-    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{1CB5E955-18ED-4738-ACA1-E270D15916F8}" name="CURRENCY"/>
-    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{06958303-4A18-40AA-8AD0-9A7EEFDCAF3E}" name="OFFER_ID"/>
     <tableColumn id="9" xr3:uid="{A1218AAF-0481-41A2-9C10-3038D1BF8C7D}" name="SORTER"/>
     <tableColumn id="10" xr3:uid="{5A7FFAC3-1C22-44BF-8C52-F3578967B0F3}" name="Pack Factor"/>
@@ -922,19 +922,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F4731A-D70B-4034-AE07-DF495FD0B95B}">
   <dimension ref="C3:Q36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="10" width="20.6640625" customWidth="1"/>
-    <col min="16" max="17" width="20.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="1" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="10" width="20.7109375" customWidth="1"/>
+    <col min="16" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -943,7 +943,7 @@
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -953,7 +953,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -970,7 +970,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -984,33 +984,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C8" s="20" t="str">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C8" s="21" t="str">
         <f>Settings!A2</f>
         <v>${offerValidation.OFFERID}</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="19" t="str">
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="20" t="str">
         <f>Settings!A3</f>
         <v>${offerValidation.TENDERID}</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19" t="str">
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20" t="str">
         <f>Settings!A4</f>
         <v>${offerValidation.OFFERDATE}</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19" t="str">
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20" t="str">
         <f>Settings!A5</f>
         <v>${offerValidation.OFFERVALIDITY}</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-    </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -1027,7 +1027,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,28 +1038,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C11" s="21" t="str">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C11" s="22" t="str">
         <f>Settings!A6</f>
         <v>${offerValidation.SHIPMENTTERMS}</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21" t="str">
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-    </row>
-    <row r="12" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+    </row>
+    <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
         <v>10</v>
@@ -1101,7 +1101,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" t="str">
         <f>IF(Settings!A18="","",Settings!A18)</f>
         <v>${table:offerProductValidation.SKU}</v>
@@ -1159,7 +1159,7 @@
         <v>${table:offerProductValidation.NET_PRICE} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" t="str">
         <f>IF(Settings!A19="","",Settings!A19)</f>
         <v/>
@@ -1217,7 +1217,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" t="str">
         <f>IF(Settings!A20="","",Settings!A20)</f>
         <v/>
@@ -1275,7 +1275,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" t="str">
         <f>IF(Settings!A21="","",Settings!A21)</f>
         <v/>
@@ -1333,19 +1333,12 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C18" t="str">
-        <f>IF(Settings!A22="","",Settings!A22)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <f>IF(Settings!B22="","",Settings!B22)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <f>IF(CONCATENATE(Settings!C22," ",Settings!D22,"s")=" s"," ",CONCATENATE(Settings!C22," ",Settings!D22,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
       <c r="F18" t="str">
         <f>IF(Settings!L22="","",Settings!L22)</f>
         <v/>
@@ -1391,7 +1384,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>IF(Settings!A23="","",Settings!A23)</f>
         <v/>
@@ -1449,7 +1442,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>IF(Settings!A24="","",Settings!A24)</f>
         <v/>
@@ -1507,7 +1500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>IF(Settings!A25="","",Settings!A25)</f>
         <v/>
@@ -1565,7 +1558,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" t="str">
         <f>IF(Settings!A26="","",Settings!A26)</f>
         <v/>
@@ -1623,7 +1616,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>IF(Settings!A27="","",Settings!A27)</f>
         <v/>
@@ -1681,7 +1674,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" t="str">
         <f>IF(Settings!A28="","",Settings!A28)</f>
         <v/>
@@ -1739,7 +1732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" t="str">
         <f>IF(Settings!A29="","",Settings!A29)</f>
         <v/>
@@ -1797,7 +1790,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" t="str">
         <f>IF(Settings!A30="","",Settings!A30)</f>
         <v/>
@@ -1855,7 +1848,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" t="str">
         <f>IF(Settings!A31="","",Settings!A31)</f>
         <v/>
@@ -1913,7 +1906,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" t="str">
         <f>IF(Settings!A32="","",Settings!A32)</f>
         <v/>
@@ -1951,7 +1944,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" t="str">
         <f>IF(Settings!A33="","",Settings!A33)</f>
         <v/>
@@ -1996,7 +1989,7 @@
         <v>${offerValidation.AMOUNT_IN_NUMBERS} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" t="str">
         <f>IF(Settings!A34="","",Settings!A34)</f>
         <v/>
@@ -2035,7 +2028,7 @@
       </c>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E31" t="str">
         <f>IF(CONCATENATE(Quotation!C83," ",Quotation!D83,"s")=" s"," ",CONCATENATE(Quotation!C83," ",Quotation!D83,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -2068,7 +2061,7 @@
         <v>${offerValidation.VAT_TOTAL} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E32" t="str">
         <f>IF(CONCATENATE(Quotation!C84," ",Quotation!D84,"s")=" s"," ",CONCATENATE(Quotation!C84," ",Quotation!D84,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -2095,7 +2088,7 @@
       </c>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E33" t="str">
         <f>IF(CONCATENATE(Quotation!C85," ",Quotation!D85,"s")=" s"," ",CONCATENATE(Quotation!C85," ",Quotation!D85,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -2128,7 +2121,7 @@
         <v>${offerValidation.AMOUNT_IN_NUMBERS_VAT} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="34" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E34" t="str">
         <f>IF(CONCATENATE(Quotation!C86," ",Quotation!D86,"s")=" s"," ",CONCATENATE(Quotation!C86," ",Quotation!D86,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -2150,7 +2143,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E35" t="str">
         <f>IF(CONCATENATE(Quotation!C87," ",Quotation!D87,"s")=" s"," ",CONCATENATE(Quotation!C87," ",Quotation!D87,"s"))</f>
         <v xml:space="preserve"> </v>
@@ -2164,14 +2157,15 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E36" t="str">
         <f>IF(CONCATENATE(Quotation!C88," ",Quotation!D88,"s")=" s"," ",CONCATENATE(Quotation!C88," ",Quotation!D88,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="L8:N8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C11:E11"/>
@@ -2181,7 +2175,10 @@
     <mergeCell ref="I11:K11"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2189,32 +2186,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BADA0-6CEF-4001-8243-A13FFD1BF3BE}">
   <dimension ref="A1:U52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="75.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>57</v>
       </c>
@@ -2222,7 +2219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2230,7 +2227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2238,7 +2235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2246,7 +2243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2254,7 +2251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2262,7 +2259,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2270,7 +2267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +2275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2286,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -2294,12 +2291,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>60</v>
       </c>
@@ -2364,7 +2361,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>31</v>
       </c>
@@ -2377,19 +2374,19 @@
       <c r="D18" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>43</v>
       </c>
       <c r="F18" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="19" t="s">
         <v>51</v>
       </c>
       <c r="J18" t="s">
@@ -2430,409 +2427,409 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
-      <c r="E19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
+      <c r="E19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
       <c r="Q19" t="str">
         <f>IF(D19&gt;0,IF(D19="Unit",CONCATENATE(Settings!P19," ",Settings!D19,"s"),CONCATENATE((Settings!P19/Settings!L19)," ",Settings!D19,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
-      <c r="E20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="E20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
       <c r="Q20" t="str">
         <f>IF(D20&gt;0,IF(D20="Unit",CONCATENATE(Settings!P20," ",Settings!D20,"s"),CONCATENATE((Settings!P20/Settings!L20)," ",Settings!D20,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
-      <c r="E21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="E21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
       <c r="Q21" t="str">
         <f>IF(D21&gt;0,IF(D21="Unit",CONCATENATE(Settings!P21," ",Settings!D21,"s"),CONCATENATE((Settings!P21/Settings!L21)," ",Settings!D21,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
-      <c r="E22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="E22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
       <c r="Q22" t="str">
         <f>IF(D22&gt;0,IF(D22="Unit",CONCATENATE(Settings!P22," ",Settings!D22,"s"),CONCATENATE((Settings!P22/Settings!L22)," ",Settings!D22,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
-      <c r="E23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
+      <c r="E23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
       <c r="Q23" t="str">
         <f>IF(D23&gt;0,IF(D23="Unit",CONCATENATE(Settings!P23," ",Settings!D23,"s"),CONCATENATE((Settings!P23/Settings!L23)," ",Settings!D23,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
-      <c r="E24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="E24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
       <c r="Q24" t="str">
         <f>IF(D24&gt;0,IF(D24="Unit",CONCATENATE(Settings!P24," ",Settings!D24,"s"),CONCATENATE((Settings!P24/Settings!L24)," ",Settings!D24,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
-      <c r="E25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
+      <c r="E25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
       <c r="Q25" t="str">
         <f>IF(D25&gt;0,IF(D25="Unit",CONCATENATE(Settings!P25," ",Settings!D25,"s"),CONCATENATE((Settings!P25/Settings!L25)," ",Settings!D25,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
-      <c r="E26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
+      <c r="E26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
       <c r="Q26" t="str">
         <f>IF(D26&gt;0,IF(D26="Unit",CONCATENATE(Settings!P26," ",Settings!D26,"s"),CONCATENATE((Settings!P26/Settings!L26)," ",Settings!D26,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
-      <c r="E27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
+      <c r="E27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
       <c r="Q27" t="str">
         <f>IF(D27&gt;0,IF(D27="Unit",CONCATENATE(Settings!P27," ",Settings!D27,"s"),CONCATENATE((Settings!P27/Settings!L27)," ",Settings!D27,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
-      <c r="E28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="E28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
       <c r="Q28" t="str">
         <f>IF(D28&gt;0,IF(D28="Unit",CONCATENATE(Settings!P28," ",Settings!D28,"s"),CONCATENATE((Settings!P28/Settings!L28)," ",Settings!D28,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
-      <c r="E29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
+      <c r="E29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
       <c r="Q29" t="str">
         <f>IF(D29&gt;0,IF(D29="Unit",CONCATENATE(Settings!P29," ",Settings!D29,"s"),CONCATENATE((Settings!P29/Settings!L29)," ",Settings!D29,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
-      <c r="E30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
+      <c r="E30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
       <c r="Q30" t="str">
         <f>IF(D30&gt;0,IF(D30="Unit",CONCATENATE(Settings!P30," ",Settings!D30,"s"),CONCATENATE((Settings!P30/Settings!L30)," ",Settings!D30,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
-      <c r="E31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
+      <c r="E31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
       <c r="Q31" t="str">
         <f>IF(D31&gt;0,IF(D31="Unit",CONCATENATE(Settings!P31," ",Settings!D31,"s"),CONCATENATE((Settings!P31/Settings!L31)," ",Settings!D31,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
-      <c r="E32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="E32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
       <c r="Q32" t="str">
         <f>IF(D32&gt;0,IF(D32="Unit",CONCATENATE(Settings!P32," ",Settings!D32,"s"),CONCATENATE((Settings!P32/Settings!L32)," ",Settings!D32,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
-      <c r="E33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="E33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
       <c r="Q33" t="str">
         <f>IF(D33&gt;0,IF(D33="Unit",CONCATENATE(Settings!P33," ",Settings!D33,"s"),CONCATENATE((Settings!P33/Settings!L33)," ",Settings!D33,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
-      <c r="E34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="E34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
       <c r="Q34" t="str">
         <f>IF(D34&gt;0,IF(D34="Unit",CONCATENATE(Settings!P34," ",Settings!D34,"s"),CONCATENATE((Settings!P34/Settings!L34)," ",Settings!D34,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
-      <c r="E35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="E35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
       <c r="Q35" t="str">
         <f>IF(D35&gt;0,IF(D35="Unit",CONCATENATE(Settings!P35," ",Settings!D35,"s"),CONCATENATE((Settings!P35/Settings!L35)," ",Settings!D35,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
-      <c r="E36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="E36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
       <c r="Q36" t="str">
         <f>IF(D36&gt;0,IF(D36="Unit",CONCATENATE(Settings!P36," ",Settings!D36,"s"),CONCATENATE((Settings!P36/Settings!L36)," ",Settings!D36,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
-      <c r="E37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
+      <c r="E37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
       <c r="Q37" t="str">
         <f>IF(D37&gt;0,IF(D37="Unit",CONCATENATE(Settings!P37," ",Settings!D37,"s"),CONCATENATE((Settings!P37/Settings!L37)," ",Settings!D37,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
-      <c r="E38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="E38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
       <c r="Q38" t="str">
         <f>IF(D38&gt;0,IF(D38="Unit",CONCATENATE(Settings!P38," ",Settings!D38,"s"),CONCATENATE((Settings!P38/Settings!L38)," ",Settings!D38,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
-      <c r="E39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
+      <c r="E39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
       <c r="Q39" t="str">
         <f>IF(D39&gt;0,IF(D39="Unit",CONCATENATE(Settings!P39," ",Settings!D39,"s"),CONCATENATE((Settings!P39/Settings!L39)," ",Settings!D39,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
-      <c r="E40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="E40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
       <c r="Q40" t="str">
         <f>IF(D40&gt;0,IF(D40="Unit",CONCATENATE(Settings!P40," ",Settings!D40,"s"),CONCATENATE((Settings!P40/Settings!L40)," ",Settings!D40,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
-      <c r="E41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="E41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
       <c r="Q41" t="str">
         <f>IF(D41&gt;0,IF(D41="Unit",CONCATENATE(Settings!P41," ",Settings!D41,"s"),CONCATENATE((Settings!P41/Settings!L41)," ",Settings!D41,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
-      <c r="E42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
+      <c r="E42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
       <c r="Q42" t="str">
         <f>IF(D42&gt;0,IF(D42="Unit",CONCATENATE(Settings!P42," ",Settings!D42,"s"),CONCATENATE((Settings!P42/Settings!L42)," ",Settings!D42,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
-      <c r="E43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
+      <c r="E43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
       <c r="Q43" t="str">
         <f>IF(D43&gt;0,IF(D43="Unit",CONCATENATE(Settings!P43," ",Settings!D43,"s"),CONCATENATE((Settings!P43/Settings!L43)," ",Settings!D43,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
-      <c r="E44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
+      <c r="E44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
       <c r="Q44" t="str">
         <f>IF(D44&gt;0,IF(D44="Unit",CONCATENATE(Settings!P44," ",Settings!D44,"s"),CONCATENATE((Settings!P44/Settings!L44)," ",Settings!D44,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
-      <c r="E45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
+      <c r="E45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
       <c r="Q45" t="str">
         <f>IF(D45&gt;0,IF(D45="Unit",CONCATENATE(Settings!P45," ",Settings!D45,"s"),CONCATENATE((Settings!P45/Settings!L45)," ",Settings!D45,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
-      <c r="E46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
+      <c r="E46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
       <c r="Q46" t="str">
         <f>IF(D46&gt;0,IF(D46="Unit",CONCATENATE(Settings!P46," ",Settings!D46,"s"),CONCATENATE((Settings!P46/Settings!L46)," ",Settings!D46,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
-      <c r="E47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
+      <c r="E47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
       <c r="Q47" t="str">
         <f>IF(D47&gt;0,IF(D47="Unit",CONCATENATE(Settings!P47," ",Settings!D47,"s"),CONCATENATE((Settings!P47/Settings!L47)," ",Settings!D47,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
-      <c r="E48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
+      <c r="E48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
       <c r="Q48" t="str">
         <f>IF(D48&gt;0,IF(D48="Unit",CONCATENATE(Settings!P48," ",Settings!D48,"s"),CONCATENATE((Settings!P48/Settings!L48)," ",Settings!D48,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
-      <c r="E49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="E49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
       <c r="Q49" t="str">
         <f>IF(D49&gt;0,IF(D49="Unit",CONCATENATE(Settings!P49," ",Settings!D49,"s"),CONCATENATE((Settings!P49/Settings!L49)," ",Settings!D49,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
-      <c r="E50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
+      <c r="E50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
       <c r="Q50" t="str">
         <f>IF(D50&gt;0,IF(D50="Unit",CONCATENATE(Settings!P50," ",Settings!D50,"s"),CONCATENATE((Settings!P50/Settings!L50)," ",Settings!D50,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
-      <c r="E51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
+      <c r="E51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
       <c r="Q51" t="str">
         <f>IF(D51&gt;0,IF(D51="Unit",CONCATENATE(Settings!P51," ",Settings!D51,"s"),CONCATENATE((Settings!P51/Settings!L51)," ",Settings!D51,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
       <c r="B52" s="16"/>
-      <c r="E52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
+      <c r="E52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
       <c r="Q52" t="str">
         <f>IF(D52&gt;0,IF(D52="Unit",CONCATENATE(Settings!P52," ",Settings!D52,"s"),CONCATENATE((Settings!P52/Settings!L52)," ",Settings!D52,"s")),"")</f>
         <v/>
@@ -2841,6 +2838,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
   <tableParts count="2">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -2863,6 +2863,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3059,15 +3068,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>
@@ -3079,6 +3079,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3095,12 +3103,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\Bayer\fastCAPv2\fastCAP-backend\srv\xlsx-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCD3417-AF0E-4A8F-8E07-6B52F4321981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7200DF03-987D-482C-B2FD-80CEBBDB3E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
-    <sheet name="Quotation" sheetId="1" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" r:id="rId2"/>
+    <sheet name="Quotation_old" sheetId="1" r:id="rId1"/>
+    <sheet name="Quotation" sheetId="3" r:id="rId2"/>
+    <sheet name="Settings" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Quotation!$B$2:$R$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Quotation!$2:$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Quotation_old!$B$2:$R$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Quotation_old!$2:$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="122">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -264,16 +265,161 @@
   </si>
   <si>
     <t>${table:offerProductValidation.TOTAL_QUANTITY_UNITS}</t>
+  </si>
+  <si>
+    <t>Offered Party</t>
+  </si>
+  <si>
+    <t>Selling Company</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Quotation Request Information</t>
+  </si>
+  <si>
+    <t>FAST Request ID</t>
+  </si>
+  <si>
+    <t>Material Group</t>
+  </si>
+  <si>
+    <t>Requestor Name</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Offer Approval Date</t>
+  </si>
+  <si>
+    <t>Contact Information</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Bayer Representative</t>
+  </si>
+  <si>
+    <t>Price Quotation</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Material Code</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Product Generic Name</t>
+  </si>
+  <si>
+    <t>Offer QTY 
+/UoM</t>
+  </si>
+  <si>
+    <t>Unit Dosge</t>
+  </si>
+  <si>
+    <t>FOC/
+Discount</t>
+  </si>
+  <si>
+    <t>Total Offer Value</t>
+  </si>
+  <si>
+    <t>excl. vat.</t>
+  </si>
+  <si>
+    <t>incl. vat.</t>
+  </si>
+  <si>
+    <t>Product Offer Information</t>
+  </si>
+  <si>
+    <t>Offer Pack Description</t>
+  </si>
+  <si>
+    <t>TPU</t>
+  </si>
+  <si>
+    <t>GPU</t>
+  </si>
+  <si>
+    <t>THCC 
+(24 Digit Code)</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Country of Origin</t>
+  </si>
+  <si>
+    <t>Customer Request Information</t>
+  </si>
+  <si>
+    <t>Quotation Delivery Channels</t>
+  </si>
+  <si>
+    <t>Receiver Information (Name, Phone, Address and/or Email)</t>
+  </si>
+  <si>
+    <t>Quotation Date (วันที่)</t>
+  </si>
+  <si>
+    <t>DKSH Quotation Office</t>
+  </si>
+  <si>
+    <t>Attention to (เรียน)</t>
+  </si>
+  <si>
+    <t>Send to Bayer</t>
+  </si>
+  <si>
+    <t>Validity Period (กำหนดยืนราคา)</t>
+  </si>
+  <si>
+    <t>years (ปี)</t>
+  </si>
+  <si>
+    <t>Email/ Fax</t>
+  </si>
+  <si>
+    <t>Delivery Due (กำหนดส่งสินค้า)</t>
+  </si>
+  <si>
+    <t>Send to Customer</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>With reference to the above tender, you must not on-sell the above mentioned products at a price higher than those listed above. However, you are always free to sell at a price lower, at your discretion.</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Position</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,8 +467,75 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,8 +548,26 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -408,11 +639,182 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -434,18 +836,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -455,26 +914,240 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#\.###\.###.00"/>
+      <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
     </dxf>
     <dxf>
       <font>
@@ -583,6 +1256,105 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>458098</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>100462</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{539850F2-A92E-4910-A645-FF78E9FA7011}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10560050" y="101600"/>
+          <a:ext cx="585098" cy="570362"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>24880</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>7997</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>790842</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>19691</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31CDDEB-371C-4DF3-A3BA-E535456AD3BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4968355" y="5675372"/>
+          <a:ext cx="1519495" cy="773694"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}" name="Tabel1" displayName="Tabel1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:B13" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}"/>
@@ -600,11 +1372,11 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{6E1F8ECB-E862-46B4-998C-BE8E89C238BA}" name="PAID VOLUME"/>
     <tableColumn id="2" xr3:uid="{6497AF92-63C8-4790-818D-6E5BE819E8D6}" name="UNIT"/>
-    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{1CB5E955-18ED-4738-ACA1-E270D15916F8}" name="CURRENCY"/>
-    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{06958303-4A18-40AA-8AD0-9A7EEFDCAF3E}" name="OFFER_ID"/>
     <tableColumn id="9" xr3:uid="{A1218AAF-0481-41A2-9C10-3038D1BF8C7D}" name="SORTER"/>
     <tableColumn id="10" xr3:uid="{5A7FFAC3-1C22-44BF-8C52-F3578967B0F3}" name="Pack Factor"/>
@@ -922,19 +1694,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F4731A-D70B-4034-AE07-DF495FD0B95B}">
   <dimension ref="C3:Q36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="10" width="20.6640625" customWidth="1"/>
-    <col min="16" max="17" width="20.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="1" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="10" width="20.7109375" customWidth="1"/>
+    <col min="16" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -943,7 +1715,7 @@
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
@@ -953,7 +1725,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -970,7 +1742,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -984,33 +1756,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C8" s="20" t="str">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C8" s="47" t="str">
         <f>Settings!A2</f>
         <v>${offerValidation.OFFERID}</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="19" t="str">
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="46" t="str">
         <f>Settings!A3</f>
         <v>${offerValidation.TENDERID}</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19" t="str">
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46" t="str">
         <f>Settings!A4</f>
         <v>${offerValidation.OFFERDATE}</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19" t="str">
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46" t="str">
         <f>Settings!A5</f>
         <v>${offerValidation.OFFERVALIDITY}</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-    </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -1027,7 +1799,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,28 +1810,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C11" s="21" t="str">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C11" s="48" t="str">
         <f>Settings!A6</f>
         <v>${offerValidation.SHIPMENTTERMS}</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21" t="str">
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-    </row>
-    <row r="12" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+    </row>
+    <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
         <v>10</v>
@@ -1101,7 +1873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" t="str">
         <f>IF(Settings!A18="","",Settings!A18)</f>
         <v>${table:offerProductValidation.SKU}</v>
@@ -1159,7 +1931,7 @@
         <v>${table:offerProductValidation.NET_PRICE} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" t="str">
         <f>IF(Settings!A19="","",Settings!A19)</f>
         <v/>
@@ -1217,7 +1989,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" t="str">
         <f>IF(Settings!A20="","",Settings!A20)</f>
         <v/>
@@ -1275,7 +2047,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" t="str">
         <f>IF(Settings!A21="","",Settings!A21)</f>
         <v/>
@@ -1333,7 +2105,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" t="str">
         <f>IF(Settings!A22="","",Settings!A22)</f>
         <v/>
@@ -1391,7 +2163,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>IF(Settings!A23="","",Settings!A23)</f>
         <v/>
@@ -1449,7 +2221,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>IF(Settings!A24="","",Settings!A24)</f>
         <v/>
@@ -1507,7 +2279,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>IF(Settings!A25="","",Settings!A25)</f>
         <v/>
@@ -1565,7 +2337,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" t="str">
         <f>IF(Settings!A26="","",Settings!A26)</f>
         <v/>
@@ -1623,7 +2395,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>IF(Settings!A27="","",Settings!A27)</f>
         <v/>
@@ -1681,7 +2453,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" t="str">
         <f>IF(Settings!A28="","",Settings!A28)</f>
         <v/>
@@ -1739,7 +2511,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" t="str">
         <f>IF(Settings!A29="","",Settings!A29)</f>
         <v/>
@@ -1797,7 +2569,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" t="str">
         <f>IF(Settings!A30="","",Settings!A30)</f>
         <v/>
@@ -1855,7 +2627,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" t="str">
         <f>IF(Settings!A31="","",Settings!A31)</f>
         <v/>
@@ -1913,7 +2685,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" t="str">
         <f>IF(Settings!A32="","",Settings!A32)</f>
         <v/>
@@ -1951,7 +2723,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" t="str">
         <f>IF(Settings!A33="","",Settings!A33)</f>
         <v/>
@@ -1996,7 +2768,7 @@
         <v>${offerValidation.AMOUNT_IN_NUMBERS} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" t="str">
         <f>IF(Settings!A34="","",Settings!A34)</f>
         <v/>
@@ -2035,9 +2807,9 @@
       </c>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E31" t="str">
-        <f>IF(CONCATENATE(Quotation!C83," ",Quotation!D83,"s")=" s"," ",CONCATENATE(Quotation!C83," ",Quotation!D83,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s")=" s"," ",CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G31" t="str">
@@ -2068,9 +2840,9 @@
         <v>${offerValidation.VAT_TOTAL} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E32" t="str">
-        <f>IF(CONCATENATE(Quotation!C84," ",Quotation!D84,"s")=" s"," ",CONCATENATE(Quotation!C84," ",Quotation!D84,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s")=" s"," ",CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G32" t="str">
@@ -2095,9 +2867,9 @@
       </c>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E33" t="str">
-        <f>IF(CONCATENATE(Quotation!C85," ",Quotation!D85,"s")=" s"," ",CONCATENATE(Quotation!C85," ",Quotation!D85,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s")=" s"," ",CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G33" t="str">
@@ -2128,9 +2900,9 @@
         <v>${offerValidation.AMOUNT_IN_NUMBERS_VAT} ${table:offerProductValidation.CURRENCY}</v>
       </c>
     </row>
-    <row r="34" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E34" t="str">
-        <f>IF(CONCATENATE(Quotation!C86," ",Quotation!D86,"s")=" s"," ",CONCATENATE(Quotation!C86," ",Quotation!D86,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s")=" s"," ",CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="G34" t="str">
@@ -2150,9 +2922,9 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E35" t="str">
-        <f>IF(CONCATENATE(Quotation!C87," ",Quotation!D87,"s")=" s"," ",CONCATENATE(Quotation!C87," ",Quotation!D87,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s")=" s"," ",CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H35" t="str">
@@ -2164,9 +2936,9 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="36" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E36" t="str">
-        <f>IF(CONCATENATE(Quotation!C88," ",Quotation!D88,"s")=" s"," ",CONCATENATE(Quotation!C88," ",Quotation!D88,"s"))</f>
+        <f>IF(CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s")=" s"," ",CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s"))</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -2181,40 +2953,1083 @@
     <mergeCell ref="I11:K11"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
+  <dimension ref="B2:S44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B3" s="91" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="91" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B4" s="91" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="81"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="91" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B5" s="23"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B7" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="94"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B8" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="105"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="50"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B9" s="105" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="105"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="88"/>
+      <c r="K9" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B10" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="105"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="90"/>
+      <c r="K10" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
+    </row>
+    <row r="11" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="105" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="105"/>
+      <c r="D11" s="106" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="50"/>
+      <c r="K11" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B12" s="105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="105"/>
+      <c r="D12" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B14" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+    </row>
+    <row r="15" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="77"/>
+      <c r="F15" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="71"/>
+      <c r="H15" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="77"/>
+      <c r="M15" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="77"/>
+      <c r="P15" s="76" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q15" s="77"/>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="73"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="79"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B17" s="74"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M17" s="68"/>
+      <c r="N17" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="26">
+        <v>1</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="31"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B19" s="26">
+        <v>2</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="31"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" s="26">
+        <v>3</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="31"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="109"/>
+      <c r="E23" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="113"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="L23" s="77"/>
+      <c r="M23" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+    </row>
+    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="73"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="74"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="78"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="32">
+        <v>1</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B27" s="32">
+        <v>2</v>
+      </c>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="32">
+        <v>3</v>
+      </c>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B30" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="96" t="s">
+        <v>106</v>
+      </c>
+      <c r="I30" s="97"/>
+      <c r="J30" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B31" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="98" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" s="99"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B32" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="101"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B33" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="20"/>
+      <c r="H33" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="101"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B34" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="20"/>
+      <c r="H34" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="I34" s="103"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="20"/>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="L42" s="33"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="20"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="L43" s="33"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="D15:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="F15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K15:L16"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="P15:Q16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="K23:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="J33:O33"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G42"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
+      <formula1>"กล่อง, เม็ด, ไวอัล, แอมพูล, ขวด, box, tablet, vial, ampoul, bottle"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33:F34" xr:uid="{2CF9FB64-438B-485F-A115-633E3AF0704D}">
+      <formula1>"Days (วัน), Months (เดือน), Years (ปี)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BADA0-6CEF-4001-8243-A13FFD1BF3BE}">
   <dimension ref="A1:U52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="75.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>57</v>
       </c>
@@ -2222,7 +4037,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2230,7 +4045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2238,7 +4053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2246,7 +4061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2254,7 +4069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2262,7 +4077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2270,7 +4085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +4093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2286,7 +4101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -2294,12 +4109,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>60</v>
       </c>
@@ -2364,7 +4179,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>31</v>
       </c>
@@ -2377,19 +4192,19 @@
       <c r="D18" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>43</v>
       </c>
       <c r="F18" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="19" t="s">
         <v>51</v>
       </c>
       <c r="J18" t="s">
@@ -2430,409 +4245,409 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
-      <c r="E19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
+      <c r="E19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
       <c r="Q19" t="str">
         <f>IF(D19&gt;0,IF(D19="Unit",CONCATENATE(Settings!P19," ",Settings!D19,"s"),CONCATENATE((Settings!P19/Settings!L19)," ",Settings!D19,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
-      <c r="E20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="E20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
       <c r="Q20" t="str">
         <f>IF(D20&gt;0,IF(D20="Unit",CONCATENATE(Settings!P20," ",Settings!D20,"s"),CONCATENATE((Settings!P20/Settings!L20)," ",Settings!D20,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
-      <c r="E21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="E21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
       <c r="Q21" t="str">
         <f>IF(D21&gt;0,IF(D21="Unit",CONCATENATE(Settings!P21," ",Settings!D21,"s"),CONCATENATE((Settings!P21/Settings!L21)," ",Settings!D21,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
-      <c r="E22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="E22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
       <c r="Q22" t="str">
         <f>IF(D22&gt;0,IF(D22="Unit",CONCATENATE(Settings!P22," ",Settings!D22,"s"),CONCATENATE((Settings!P22/Settings!L22)," ",Settings!D22,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
-      <c r="E23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
+      <c r="E23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
       <c r="Q23" t="str">
         <f>IF(D23&gt;0,IF(D23="Unit",CONCATENATE(Settings!P23," ",Settings!D23,"s"),CONCATENATE((Settings!P23/Settings!L23)," ",Settings!D23,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
-      <c r="E24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="E24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
       <c r="Q24" t="str">
         <f>IF(D24&gt;0,IF(D24="Unit",CONCATENATE(Settings!P24," ",Settings!D24,"s"),CONCATENATE((Settings!P24/Settings!L24)," ",Settings!D24,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
-      <c r="E25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
+      <c r="E25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
       <c r="Q25" t="str">
         <f>IF(D25&gt;0,IF(D25="Unit",CONCATENATE(Settings!P25," ",Settings!D25,"s"),CONCATENATE((Settings!P25/Settings!L25)," ",Settings!D25,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
-      <c r="E26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
+      <c r="E26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
       <c r="Q26" t="str">
         <f>IF(D26&gt;0,IF(D26="Unit",CONCATENATE(Settings!P26," ",Settings!D26,"s"),CONCATENATE((Settings!P26/Settings!L26)," ",Settings!D26,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
-      <c r="E27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
+      <c r="E27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
       <c r="Q27" t="str">
         <f>IF(D27&gt;0,IF(D27="Unit",CONCATENATE(Settings!P27," ",Settings!D27,"s"),CONCATENATE((Settings!P27/Settings!L27)," ",Settings!D27,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
-      <c r="E28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="E28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
       <c r="Q28" t="str">
         <f>IF(D28&gt;0,IF(D28="Unit",CONCATENATE(Settings!P28," ",Settings!D28,"s"),CONCATENATE((Settings!P28/Settings!L28)," ",Settings!D28,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
-      <c r="E29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
+      <c r="E29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
       <c r="Q29" t="str">
         <f>IF(D29&gt;0,IF(D29="Unit",CONCATENATE(Settings!P29," ",Settings!D29,"s"),CONCATENATE((Settings!P29/Settings!L29)," ",Settings!D29,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
-      <c r="E30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
+      <c r="E30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
       <c r="Q30" t="str">
         <f>IF(D30&gt;0,IF(D30="Unit",CONCATENATE(Settings!P30," ",Settings!D30,"s"),CONCATENATE((Settings!P30/Settings!L30)," ",Settings!D30,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
-      <c r="E31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
+      <c r="E31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
       <c r="Q31" t="str">
         <f>IF(D31&gt;0,IF(D31="Unit",CONCATENATE(Settings!P31," ",Settings!D31,"s"),CONCATENATE((Settings!P31/Settings!L31)," ",Settings!D31,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
-      <c r="E32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="E32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
       <c r="Q32" t="str">
         <f>IF(D32&gt;0,IF(D32="Unit",CONCATENATE(Settings!P32," ",Settings!D32,"s"),CONCATENATE((Settings!P32/Settings!L32)," ",Settings!D32,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
-      <c r="E33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="E33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
       <c r="Q33" t="str">
         <f>IF(D33&gt;0,IF(D33="Unit",CONCATENATE(Settings!P33," ",Settings!D33,"s"),CONCATENATE((Settings!P33/Settings!L33)," ",Settings!D33,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
-      <c r="E34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="E34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
       <c r="Q34" t="str">
         <f>IF(D34&gt;0,IF(D34="Unit",CONCATENATE(Settings!P34," ",Settings!D34,"s"),CONCATENATE((Settings!P34/Settings!L34)," ",Settings!D34,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
-      <c r="E35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="E35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
       <c r="Q35" t="str">
         <f>IF(D35&gt;0,IF(D35="Unit",CONCATENATE(Settings!P35," ",Settings!D35,"s"),CONCATENATE((Settings!P35/Settings!L35)," ",Settings!D35,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
-      <c r="E36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="E36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
       <c r="Q36" t="str">
         <f>IF(D36&gt;0,IF(D36="Unit",CONCATENATE(Settings!P36," ",Settings!D36,"s"),CONCATENATE((Settings!P36/Settings!L36)," ",Settings!D36,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
-      <c r="E37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
+      <c r="E37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
       <c r="Q37" t="str">
         <f>IF(D37&gt;0,IF(D37="Unit",CONCATENATE(Settings!P37," ",Settings!D37,"s"),CONCATENATE((Settings!P37/Settings!L37)," ",Settings!D37,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
-      <c r="E38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="E38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
       <c r="Q38" t="str">
         <f>IF(D38&gt;0,IF(D38="Unit",CONCATENATE(Settings!P38," ",Settings!D38,"s"),CONCATENATE((Settings!P38/Settings!L38)," ",Settings!D38,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
-      <c r="E39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
+      <c r="E39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
       <c r="Q39" t="str">
         <f>IF(D39&gt;0,IF(D39="Unit",CONCATENATE(Settings!P39," ",Settings!D39,"s"),CONCATENATE((Settings!P39/Settings!L39)," ",Settings!D39,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
-      <c r="E40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="E40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
       <c r="Q40" t="str">
         <f>IF(D40&gt;0,IF(D40="Unit",CONCATENATE(Settings!P40," ",Settings!D40,"s"),CONCATENATE((Settings!P40/Settings!L40)," ",Settings!D40,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
-      <c r="E41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="E41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
       <c r="Q41" t="str">
         <f>IF(D41&gt;0,IF(D41="Unit",CONCATENATE(Settings!P41," ",Settings!D41,"s"),CONCATENATE((Settings!P41/Settings!L41)," ",Settings!D41,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
-      <c r="E42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
+      <c r="E42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
       <c r="Q42" t="str">
         <f>IF(D42&gt;0,IF(D42="Unit",CONCATENATE(Settings!P42," ",Settings!D42,"s"),CONCATENATE((Settings!P42/Settings!L42)," ",Settings!D42,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
-      <c r="E43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
+      <c r="E43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
       <c r="Q43" t="str">
         <f>IF(D43&gt;0,IF(D43="Unit",CONCATENATE(Settings!P43," ",Settings!D43,"s"),CONCATENATE((Settings!P43/Settings!L43)," ",Settings!D43,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
-      <c r="E44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
+      <c r="E44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
       <c r="Q44" t="str">
         <f>IF(D44&gt;0,IF(D44="Unit",CONCATENATE(Settings!P44," ",Settings!D44,"s"),CONCATENATE((Settings!P44/Settings!L44)," ",Settings!D44,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
-      <c r="E45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
+      <c r="E45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
       <c r="Q45" t="str">
         <f>IF(D45&gt;0,IF(D45="Unit",CONCATENATE(Settings!P45," ",Settings!D45,"s"),CONCATENATE((Settings!P45/Settings!L45)," ",Settings!D45,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
-      <c r="E46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
+      <c r="E46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
       <c r="Q46" t="str">
         <f>IF(D46&gt;0,IF(D46="Unit",CONCATENATE(Settings!P46," ",Settings!D46,"s"),CONCATENATE((Settings!P46/Settings!L46)," ",Settings!D46,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
-      <c r="E47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
+      <c r="E47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
       <c r="Q47" t="str">
         <f>IF(D47&gt;0,IF(D47="Unit",CONCATENATE(Settings!P47," ",Settings!D47,"s"),CONCATENATE((Settings!P47/Settings!L47)," ",Settings!D47,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
-      <c r="E48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
+      <c r="E48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
       <c r="Q48" t="str">
         <f>IF(D48&gt;0,IF(D48="Unit",CONCATENATE(Settings!P48," ",Settings!D48,"s"),CONCATENATE((Settings!P48/Settings!L48)," ",Settings!D48,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
-      <c r="E49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="E49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
       <c r="Q49" t="str">
         <f>IF(D49&gt;0,IF(D49="Unit",CONCATENATE(Settings!P49," ",Settings!D49,"s"),CONCATENATE((Settings!P49/Settings!L49)," ",Settings!D49,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
-      <c r="E50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
+      <c r="E50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
       <c r="Q50" t="str">
         <f>IF(D50&gt;0,IF(D50="Unit",CONCATENATE(Settings!P50," ",Settings!D50,"s"),CONCATENATE((Settings!P50/Settings!L50)," ",Settings!D50,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
-      <c r="E51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
+      <c r="E51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
       <c r="Q51" t="str">
         <f>IF(D51&gt;0,IF(D51="Unit",CONCATENATE(Settings!P51," ",Settings!D51,"s"),CONCATENATE((Settings!P51/Settings!L51)," ",Settings!D51,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
       <c r="B52" s="16"/>
-      <c r="E52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
+      <c r="E52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
       <c r="Q52" t="str">
         <f>IF(D52&gt;0,IF(D52="Unit",CONCATENATE(Settings!P52," ",Settings!D52,"s"),CONCATENATE((Settings!P52/Settings!L52)," ",Settings!D52,"s")),"")</f>
         <v/>
@@ -2841,6 +4656,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
   <tableParts count="2">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -2849,20 +4667,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3059,7 +4863,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3068,17 +4872,21 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3097,10 +4905,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7200DF03-987D-482C-B2FD-80CEBBDB3E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642F709E-8617-4C04-8BCA-6DCF9ED3FB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="124">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -409,6 +409,12 @@
   </si>
   <si>
     <t>Position</t>
+  </si>
+  <si>
+    <t>=Settings!A4</t>
+  </si>
+  <si>
+    <t>=Settings!A5</t>
   </si>
 </sst>
 </file>
@@ -419,7 +425,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,6 +536,13 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -814,7 +827,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -905,6 +918,24 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -914,12 +945,177 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -935,104 +1131,8 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1040,93 +1140,7 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1210,7 +1224,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>1348740</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1715,14 +1729,11 @@
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="str">
-        <f>Settings!A10</f>
-        <v>${offerValidation.PROCUREMENT_REASON}</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.25">
@@ -1757,30 +1768,30 @@
       </c>
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C8" s="47" t="str">
+      <c r="C8" s="53" t="str">
         <f>Settings!A2</f>
         <v>${offerValidation.OFFERID}</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="46" t="str">
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="52" t="str">
         <f>Settings!A3</f>
         <v>${offerValidation.TENDERID}</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46" t="str">
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52" t="str">
         <f>Settings!A4</f>
         <v>${offerValidation.OFFERDATE}</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46" t="str">
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52" t="str">
         <f>Settings!A5</f>
         <v>${offerValidation.OFFERVALIDITY}</v>
       </c>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
@@ -1811,24 +1822,24 @@
       </c>
     </row>
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C11" s="48" t="str">
+      <c r="C11" s="54" t="str">
         <f>Settings!A6</f>
         <v>${offerValidation.SHIPMENTTERMS}</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48" t="str">
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48" t="str">
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
     </row>
     <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2990,47 +3001,48 @@
       <c r="Q2" s="20"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
+      <c r="C3" s="78" t="str">
+        <f>Settings!A9</f>
+        <v>${offerValidation.INSTITUTENAME}</v>
+      </c>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
       <c r="H3" s="21"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="91" t="s">
+      <c r="J3" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="83"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="81"/>
       <c r="H4" s="22"/>
       <c r="I4" s="20"/>
-      <c r="J4" s="91" t="s">
+      <c r="J4" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="86"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
@@ -3072,151 +3084,153 @@
       <c r="Q6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="94"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="111"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="49" t="s">
+      <c r="C8" s="85"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="116"/>
       <c r="O8" s="44" t="s">
         <v>81</v>
       </c>
       <c r="P8" s="45"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="52"/>
-      <c r="S8" s="52"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="105"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="87" t="s">
+      <c r="C9" s="85"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="88"/>
-      <c r="K9" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="117" t="s">
+        <v>122</v>
+      </c>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
       <c r="O9" s="44" t="s">
         <v>84</v>
       </c>
       <c r="P9" s="45"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="52"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="89" t="s">
+      <c r="C10" s="85"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="90"/>
-      <c r="K10" s="104" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="117" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
       <c r="O10" s="44" t="s">
         <v>86</v>
       </c>
       <c r="P10" s="45"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+      <c r="S10" s="113"/>
     </row>
     <row r="11" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="105"/>
-      <c r="D11" s="106" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="49" t="s">
+      <c r="C11" s="85"/>
+      <c r="D11" s="55" t="str">
+        <f>Settings!A6</f>
+        <v>${offerValidation.SHIPMENTTERMS}</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="50"/>
-      <c r="K11" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="112" t="str">
+        <f>Settings!A7</f>
+        <v>${offerValidation.PAYMENTTERMS}</v>
+      </c>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
       <c r="O11" s="44" t="s">
         <v>84</v>
       </c>
       <c r="P11" s="45"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="113"/>
+      <c r="S11" s="113"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="105"/>
-      <c r="D12" s="106" t="s">
+      <c r="C12" s="85"/>
+      <c r="D12" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="108"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="57"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
@@ -3246,100 +3260,100 @@
       <c r="Q13" s="20"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
     </row>
     <row r="15" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="77"/>
-      <c r="F15" s="71" t="s">
+      <c r="E15" s="69"/>
+      <c r="F15" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="67" t="s">
+      <c r="G15" s="92"/>
+      <c r="H15" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="67" t="s">
+      <c r="I15" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="67" t="s">
+      <c r="J15" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="76" t="s">
+      <c r="K15" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="L15" s="77"/>
-      <c r="M15" s="67" t="s">
+      <c r="L15" s="69"/>
+      <c r="M15" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="76" t="s">
+      <c r="N15" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="77"/>
-      <c r="P15" s="76" t="s">
+      <c r="O15" s="69"/>
+      <c r="P15" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="Q15" s="77"/>
+      <c r="Q15" s="69"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="73"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="75"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="79"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="75"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="74"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="25" t="s">
         <v>96</v>
       </c>
       <c r="L17" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="M17" s="68"/>
+      <c r="M17" s="63"/>
       <c r="N17" s="25" t="s">
         <v>96</v>
       </c>
@@ -3358,10 +3372,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="26"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
       <c r="H18" s="26"/>
       <c r="I18" s="14" t="s">
         <v>32</v>
@@ -3382,10 +3396,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="26"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
       <c r="H19" s="26"/>
       <c r="I19" s="27"/>
       <c r="J19" s="26"/>
@@ -3402,10 +3416,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
       <c r="H20" s="26"/>
       <c r="I20" s="27"/>
       <c r="J20" s="26"/>
@@ -3436,90 +3450,90 @@
       <c r="Q21" s="20"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
       <c r="N22" s="20"/>
       <c r="O22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="109"/>
-      <c r="E23" s="69" t="s">
+      <c r="D23" s="49"/>
+      <c r="E23" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="76" t="s">
+      <c r="H23" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="113"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="76" t="s">
+      <c r="I23" s="68"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="L23" s="77"/>
-      <c r="M23" s="67" t="s">
+      <c r="L23" s="69"/>
+      <c r="M23" s="61" t="s">
         <v>104</v>
       </c>
       <c r="N23" s="20"/>
       <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
+      <c r="P23" s="120"/>
       <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="73"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="114"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="114"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="75"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="62"/>
       <c r="N24" s="20"/>
       <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
+      <c r="P24" s="120"/>
       <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="74"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="68"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="63"/>
       <c r="N25" s="20"/>
       <c r="O25" s="20"/>
       <c r="P25" s="20"/>
@@ -3534,11 +3548,11 @@
       <c r="E26" s="32"/>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
       <c r="M26" s="32"/>
       <c r="N26" s="20"/>
       <c r="O26" s="20"/>
@@ -3554,11 +3568,11 @@
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
       <c r="M27" s="32"/>
       <c r="N27" s="20"/>
       <c r="O27" s="20"/>
@@ -3574,11 +3588,11 @@
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="56"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
       <c r="M28" s="32"/>
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
@@ -3603,26 +3617,26 @@
       <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
       <c r="G30" s="34"/>
-      <c r="H30" s="96" t="s">
+      <c r="H30" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="I30" s="97"/>
-      <c r="J30" s="61" t="s">
+      <c r="I30" s="48"/>
+      <c r="J30" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="101"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
     </row>
@@ -3632,19 +3646,19 @@
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="98" t="s">
+      <c r="H31" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="99"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="56"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95"/>
       <c r="P31" s="20"/>
       <c r="Q31" s="20"/>
     </row>
@@ -3654,19 +3668,19 @@
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
+      <c r="E32" s="95"/>
+      <c r="F32" s="95"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="100" t="s">
+      <c r="H32" s="105" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="101"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="95"/>
       <c r="P32" s="20"/>
       <c r="Q32" s="20"/>
     </row>
@@ -3681,16 +3695,16 @@
         <v>113</v>
       </c>
       <c r="G33" s="20"/>
-      <c r="H33" s="100" t="s">
+      <c r="H33" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="I33" s="101"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="56"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95"/>
       <c r="P33" s="20"/>
       <c r="Q33" s="20"/>
     </row>
@@ -3705,16 +3719,16 @@
         <v>113</v>
       </c>
       <c r="G34" s="20"/>
-      <c r="H34" s="102" t="s">
+      <c r="H34" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="I34" s="103"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="57"/>
-      <c r="O34" s="57"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="97"/>
+      <c r="M34" s="97"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="97"/>
       <c r="P34" s="20"/>
       <c r="Q34" s="20"/>
     </row>
@@ -3755,14 +3769,14 @@
       <c r="Q36" s="20"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="58" t="s">
+      <c r="B37" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
@@ -3775,14 +3789,14 @@
       <c r="Q37" s="20"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
@@ -3795,12 +3809,12 @@
       <c r="Q38" s="20"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
+      <c r="B39" s="99"/>
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
@@ -3813,12 +3827,12 @@
       <c r="Q39" s="20"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
+      <c r="B40" s="99"/>
+      <c r="C40" s="99"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="99"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="99"/>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
@@ -3831,12 +3845,12 @@
       <c r="Q40" s="20"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="99"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
       <c r="H41" s="42"/>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
@@ -3849,12 +3863,12 @@
       <c r="Q41" s="20"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
+      <c r="B42" s="99"/>
+      <c r="C42" s="99"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="99"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99"/>
       <c r="H42" s="20"/>
       <c r="I42" s="43" t="s">
         <v>119</v>
@@ -3910,53 +3924,14 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="D15:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="F15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="K15:L16"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="P15:Q16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B22:M22"/>
-    <mergeCell ref="K23:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="J33:O33"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
     <mergeCell ref="J34:O34"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G42"/>
@@ -3970,20 +3945,59 @@
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="J33:O33"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="K23:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="P15:Q16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K15:L16"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="D15:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -4667,6 +4681,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -4863,30 +4900,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4903,22 +4935,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642F709E-8617-4C04-8BCA-6DCF9ED3FB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F15527-F757-4F1F-97A3-2716F63C79B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
-    <sheet name="Quotation_old" sheetId="1" r:id="rId1"/>
-    <sheet name="Quotation" sheetId="3" r:id="rId2"/>
+    <sheet name="Quotation" sheetId="3" r:id="rId1"/>
+    <sheet name="Quotation_old" sheetId="1" r:id="rId2"/>
     <sheet name="Settings" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Quotation_old!$B$2:$R$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Quotation_old!$2:$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Quotation_old!$B$2:$R$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">Quotation_old!$2:$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -936,6 +936,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -945,6 +946,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -963,15 +1114,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -981,166 +1123,24 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1213,64 +1213,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1348740</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{185028B1-20BB-4225-B9A8-E12CBCF93FCC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17545050" y="514350"/>
-          <a:ext cx="790575" cy="790575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1358,6 +1300,64 @@
         <a:xfrm>
           <a:off x="4968355" y="5675372"/>
           <a:ext cx="1519495" cy="773694"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1348740</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{185028B1-20BB-4225-B9A8-E12CBCF93FCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17545050" y="514350"/>
+          <a:ext cx="790575" cy="790575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1706,1273 +1706,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F4731A-D70B-4034-AE07-DF495FD0B95B}">
-  <dimension ref="C3:Q36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="10" width="20.7109375" customWidth="1"/>
-    <col min="16" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <f>Settings!A9</f>
-        <v>${offerValidation.INSTITUTENAME}</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C8" s="53" t="str">
-        <f>Settings!A2</f>
-        <v>${offerValidation.OFFERID}</v>
-      </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="52" t="str">
-        <f>Settings!A3</f>
-        <v>${offerValidation.TENDERID}</v>
-      </c>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52" t="str">
-        <f>Settings!A4</f>
-        <v>${offerValidation.OFFERDATE}</v>
-      </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52" t="str">
-        <f>Settings!A5</f>
-        <v>${offerValidation.OFFERVALIDITY}</v>
-      </c>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-    </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C11" s="54" t="str">
-        <f>Settings!A6</f>
-        <v>${offerValidation.SHIPMENTTERMS}</v>
-      </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54" t="str">
-        <f>Settings!A7</f>
-        <v>${offerValidation.PAYMENTTERMS}</v>
-      </c>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54" t="str">
-        <f>Settings!A8</f>
-        <v>${offerValidation.DELIVERYTERMS}</v>
-      </c>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-    </row>
-    <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="9"/>
-      <c r="D13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C14" t="str">
-        <f>IF(Settings!A18="","",Settings!A18)</f>
-        <v>${table:offerProductValidation.SKU}</v>
-      </c>
-      <c r="D14" t="str">
-        <f>IF(Settings!B18="","",Settings!B18)</f>
-        <v>${table:offerProductValidation.PRODUCT_UNIT_NAME}</v>
-      </c>
-      <c r="E14" t="str">
-        <f>IF(CONCATENATE(Settings!C18," ",Settings!D18,"s")=" s"," ",CONCATENATE(Settings!C18," ",Settings!D18,"s"))</f>
-        <v>${table:offerProductValidation.PAID_VOLUME} ${table:offerProductValidation.UNIT}s</v>
-      </c>
-      <c r="F14" t="str">
-        <f>IF(Settings!L18="","",Settings!L18)</f>
-        <v>${table:offerProductValidation.PACKSIZE}</v>
-      </c>
-      <c r="G14" t="str">
-        <f>CONCATENATE(Settings!E18," ",Settings!F18)</f>
-        <v>${table:offerProductValidation.OFFER_PRICE} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-      <c r="H14" t="str">
-        <f>CONCATENATE(Settings!G18," ",Settings!F18)</f>
-        <v>${table:offerProductValidation.OFFER_PRICE_VAT} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-      <c r="I14" t="str">
-        <f>CONCATENATE(Settings!H18," ",Settings!F18)</f>
-        <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-      <c r="J14" t="str">
-        <f>CONCATENATE(Settings!I18," ",Settings!F18)</f>
-        <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY_VAT} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-      <c r="L14" t="str">
-        <f>IF(Settings!M18="","",Settings!M18)</f>
-        <v>${table:offerProductValidation.SAMPLES}</v>
-      </c>
-      <c r="M14" t="str">
-        <f>IF(Settings!N18="","",Settings!N18)</f>
-        <v>${table:offerProductValidation.COUNTRYOFORIGIN}</v>
-      </c>
-      <c r="N14" t="str">
-        <f>IF(CONCATENATE(Settings!J18,"-",Settings!K18) = "-","",CONCATENATE(Settings!J18,"-",Settings!K18))</f>
-        <v>${table:offerProductValidation.OFFER_ID}-${table:offerProductValidation.SORTER}</v>
-      </c>
-      <c r="O14" t="str">
-        <f>IF(Settings!O18="","",Settings!O18)</f>
-        <v>${table:offerProductValidation.FOC}</v>
-      </c>
-      <c r="P14" t="e">
-        <f>Settings!Q18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q14" t="str">
-        <f>_xlfn.CONCAT(Settings!R18," ",Settings!F18)</f>
-        <v>${table:offerProductValidation.NET_PRICE} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-    </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C15" t="str">
-        <f>IF(Settings!A19="","",Settings!A19)</f>
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <f>IF(Settings!B19="","",Settings!B19)</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <f>IF(CONCATENATE(Settings!C19," ",Settings!D19,"s")=" s"," ",CONCATENATE(Settings!C19," ",Settings!D19,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F15" t="str">
-        <f>IF(Settings!L19="","",Settings!L19)</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <f>CONCATENATE(Settings!E19," ",Settings!F19)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H15" t="str">
-        <f>CONCATENATE(Settings!G19," ",Settings!F19)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I15" t="str">
-        <f>CONCATENATE(Settings!H19," ",Settings!F19)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J15" t="str">
-        <f>CONCATENATE(Settings!I19," ",Settings!F19)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L15" t="str">
-        <f>IF(Settings!M19="","",Settings!M19)</f>
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <f>IF(Settings!N19="","",Settings!N19)</f>
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <f>IF(CONCATENATE(Settings!J19,"-",Settings!K19) = "-","",CONCATENATE(Settings!J19,"-",Settings!K19))</f>
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <f>IF(Settings!O19="","",Settings!O19)</f>
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <f>Settings!Q19</f>
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <f>_xlfn.CONCAT(Settings!R19," ",Settings!F19)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C16" t="str">
-        <f>IF(Settings!A20="","",Settings!A20)</f>
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <f>IF(Settings!B20="","",Settings!B20)</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <f>IF(CONCATENATE(Settings!C20," ",Settings!D20,"s")=" s"," ",CONCATENATE(Settings!C20," ",Settings!D20,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F16" t="str">
-        <f>IF(Settings!L20="","",Settings!L20)</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <f>CONCATENATE(Settings!E20," ",Settings!F20)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H16" t="str">
-        <f>CONCATENATE(Settings!G20," ",Settings!F20)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I16" t="str">
-        <f>CONCATENATE(Settings!H20," ",Settings!F20)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J16" t="str">
-        <f>CONCATENATE(Settings!I20," ",Settings!F20)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L16" t="str">
-        <f>IF(Settings!M20="","",Settings!M20)</f>
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <f>IF(Settings!N20="","",Settings!N20)</f>
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <f>IF(CONCATENATE(Settings!J20,"-",Settings!K20) = "-","",CONCATENATE(Settings!J20,"-",Settings!K20))</f>
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <f>IF(Settings!O20="","",Settings!O20)</f>
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <f>Settings!Q20</f>
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <f>_xlfn.CONCAT(Settings!R20," ",Settings!F20)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C17" t="str">
-        <f>IF(Settings!A21="","",Settings!A21)</f>
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <f>IF(Settings!B21="","",Settings!B21)</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <f>IF(CONCATENATE(Settings!C21," ",Settings!D21,"s")=" s"," ",CONCATENATE(Settings!C21," ",Settings!D21,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F17" t="str">
-        <f>IF(Settings!L21="","",Settings!L21)</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <f>CONCATENATE(Settings!E21," ",Settings!F21)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H17" t="str">
-        <f>CONCATENATE(Settings!G21," ",Settings!F21)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I17" t="str">
-        <f>CONCATENATE(Settings!H21," ",Settings!F21)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J17" t="str">
-        <f>CONCATENATE(Settings!I21," ",Settings!F21)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L17" t="str">
-        <f>IF(Settings!M21="","",Settings!M21)</f>
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <f>IF(Settings!N21="","",Settings!N21)</f>
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <f>IF(CONCATENATE(Settings!J21,"-",Settings!K21) = "-","",CONCATENATE(Settings!J21,"-",Settings!K21))</f>
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <f>IF(Settings!O21="","",Settings!O21)</f>
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <f>Settings!Q21</f>
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <f>_xlfn.CONCAT(Settings!R21," ",Settings!F21)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C18" t="str">
-        <f>IF(Settings!A22="","",Settings!A22)</f>
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <f>IF(Settings!B22="","",Settings!B22)</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <f>IF(CONCATENATE(Settings!C22," ",Settings!D22,"s")=" s"," ",CONCATENATE(Settings!C22," ",Settings!D22,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F18" t="str">
-        <f>IF(Settings!L22="","",Settings!L22)</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <f>CONCATENATE(Settings!E22," ",Settings!F22)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H18" t="str">
-        <f>CONCATENATE(Settings!G22," ",Settings!F22)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I18" t="str">
-        <f>CONCATENATE(Settings!H22," ",Settings!F22)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J18" t="str">
-        <f>CONCATENATE(Settings!I22," ",Settings!F22)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L18" t="str">
-        <f>IF(Settings!M22="","",Settings!M22)</f>
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <f>IF(Settings!N22="","",Settings!N22)</f>
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <f>IF(CONCATENATE(Settings!J22,"-",Settings!K22) = "-","",CONCATENATE(Settings!J22,"-",Settings!K22))</f>
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <f>IF(Settings!O22="","",Settings!O22)</f>
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <f>Settings!Q22</f>
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <f>_xlfn.CONCAT(Settings!R22," ",Settings!F22)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C19" t="str">
-        <f>IF(Settings!A23="","",Settings!A23)</f>
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <f>IF(Settings!B23="","",Settings!B23)</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <f>IF(CONCATENATE(Settings!C23," ",Settings!D23,"s")=" s"," ",CONCATENATE(Settings!C23," ",Settings!D23,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F19" t="str">
-        <f>IF(Settings!L23="","",Settings!L23)</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <f>CONCATENATE(Settings!E23," ",Settings!F23)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H19" t="str">
-        <f>CONCATENATE(Settings!G23," ",Settings!F23)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I19" t="str">
-        <f>CONCATENATE(Settings!H23," ",Settings!F23)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J19" t="str">
-        <f>CONCATENATE(Settings!I23," ",Settings!F23)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L19" t="str">
-        <f>IF(Settings!M23="","",Settings!M23)</f>
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <f>IF(Settings!N23="","",Settings!N23)</f>
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <f>IF(CONCATENATE(Settings!J23,"-",Settings!K23) = "-","",CONCATENATE(Settings!J23,"-",Settings!K23))</f>
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <f>IF(Settings!O23="","",Settings!O23)</f>
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <f>Settings!Q23</f>
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <f>_xlfn.CONCAT(Settings!R23," ",Settings!F23)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C20" t="str">
-        <f>IF(Settings!A24="","",Settings!A24)</f>
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <f>IF(Settings!B24="","",Settings!B24)</f>
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <f>IF(CONCATENATE(Settings!C24," ",Settings!D24,"s")=" s"," ",CONCATENATE(Settings!C24," ",Settings!D24,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F20" t="str">
-        <f>IF(Settings!L24="","",Settings!L24)</f>
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <f>CONCATENATE(Settings!E24," ",Settings!F24)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H20" t="str">
-        <f>CONCATENATE(Settings!G24," ",Settings!F24)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I20" t="str">
-        <f>CONCATENATE(Settings!H24," ",Settings!F24)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J20" t="str">
-        <f>CONCATENATE(Settings!I24," ",Settings!F24)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L20" t="str">
-        <f>IF(Settings!M24="","",Settings!M24)</f>
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <f>IF(Settings!N24="","",Settings!N24)</f>
-        <v/>
-      </c>
-      <c r="N20" t="str">
-        <f>IF(CONCATENATE(Settings!J24,"-",Settings!K24) = "-","",CONCATENATE(Settings!J24,"-",Settings!K24))</f>
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <f>IF(Settings!O24="","",Settings!O24)</f>
-        <v/>
-      </c>
-      <c r="P20" t="str">
-        <f>Settings!Q24</f>
-        <v/>
-      </c>
-      <c r="Q20" t="str">
-        <f>_xlfn.CONCAT(Settings!R24," ",Settings!F24)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C21" t="str">
-        <f>IF(Settings!A25="","",Settings!A25)</f>
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <f>IF(Settings!B25="","",Settings!B25)</f>
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <f>IF(CONCATENATE(Settings!C25," ",Settings!D25,"s")=" s"," ",CONCATENATE(Settings!C25," ",Settings!D25,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F21" t="str">
-        <f>IF(Settings!L25="","",Settings!L25)</f>
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <f>CONCATENATE(Settings!E25," ",Settings!F25)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H21" t="str">
-        <f>CONCATENATE(Settings!G25," ",Settings!F25)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I21" t="str">
-        <f>CONCATENATE(Settings!H25," ",Settings!F25)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J21" t="str">
-        <f>CONCATENATE(Settings!I25," ",Settings!F25)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L21" t="str">
-        <f>IF(Settings!M25="","",Settings!M25)</f>
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <f>IF(Settings!N25="","",Settings!N25)</f>
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <f>IF(CONCATENATE(Settings!J25,"-",Settings!K25) = "-","",CONCATENATE(Settings!J25,"-",Settings!K25))</f>
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <f>IF(Settings!O25="","",Settings!O25)</f>
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <f>Settings!Q25</f>
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <f>_xlfn.CONCAT(Settings!R25," ",Settings!F25)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C22" t="str">
-        <f>IF(Settings!A26="","",Settings!A26)</f>
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <f>IF(Settings!B26="","",Settings!B26)</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <f>IF(CONCATENATE(Settings!C26," ",Settings!D26,"s")=" s"," ",CONCATENATE(Settings!C26," ",Settings!D26,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F22" t="str">
-        <f>IF(Settings!L26="","",Settings!L26)</f>
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <f>CONCATENATE(Settings!E26," ",Settings!F26)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H22" t="str">
-        <f>CONCATENATE(Settings!G26," ",Settings!F26)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I22" t="str">
-        <f>CONCATENATE(Settings!H26," ",Settings!F26)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J22" t="str">
-        <f>CONCATENATE(Settings!I26," ",Settings!F26)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L22" t="str">
-        <f>IF(Settings!M26="","",Settings!M26)</f>
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <f>IF(Settings!N26="","",Settings!N26)</f>
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <f>IF(CONCATENATE(Settings!J26,"-",Settings!K26) = "-","",CONCATENATE(Settings!J26,"-",Settings!K26))</f>
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <f>IF(Settings!O26="","",Settings!O26)</f>
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <f>Settings!Q26</f>
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <f>_xlfn.CONCAT(Settings!R26," ",Settings!F26)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C23" t="str">
-        <f>IF(Settings!A27="","",Settings!A27)</f>
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <f>IF(Settings!B27="","",Settings!B27)</f>
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <f>IF(CONCATENATE(Settings!C27," ",Settings!D27,"s")=" s"," ",CONCATENATE(Settings!C27," ",Settings!D27,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F23" t="str">
-        <f>IF(Settings!L27="","",Settings!L27)</f>
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <f>CONCATENATE(Settings!E27," ",Settings!F27)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H23" t="str">
-        <f>CONCATENATE(Settings!G27," ",Settings!F27)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I23" t="str">
-        <f>CONCATENATE(Settings!H27," ",Settings!F27)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J23" t="str">
-        <f>CONCATENATE(Settings!I27," ",Settings!F27)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L23" t="str">
-        <f>IF(Settings!M27="","",Settings!M27)</f>
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <f>IF(Settings!N27="","",Settings!N27)</f>
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <f>IF(CONCATENATE(Settings!J27,"-",Settings!K27) = "-","",CONCATENATE(Settings!J27,"-",Settings!K27))</f>
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <f>IF(Settings!O27="","",Settings!O27)</f>
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <f>Settings!Q27</f>
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <f>_xlfn.CONCAT(Settings!R27," ",Settings!F27)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C24" t="str">
-        <f>IF(Settings!A28="","",Settings!A28)</f>
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <f>IF(Settings!B28="","",Settings!B28)</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <f>IF(CONCATENATE(Settings!C28," ",Settings!D28,"s")=" s"," ",CONCATENATE(Settings!C28," ",Settings!D28,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F24" t="str">
-        <f>IF(Settings!L28="","",Settings!L28)</f>
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <f>CONCATENATE(Settings!E28," ",Settings!F28)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H24" t="str">
-        <f>CONCATENATE(Settings!G28," ",Settings!F28)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I24" t="str">
-        <f>CONCATENATE(Settings!H28," ",Settings!F28)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J24" t="str">
-        <f>CONCATENATE(Settings!I28," ",Settings!F28)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L24" t="str">
-        <f>IF(Settings!M28="","",Settings!M28)</f>
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <f>IF(Settings!N28="","",Settings!N28)</f>
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <f>IF(CONCATENATE(Settings!J28,"-",Settings!K28) = "-","",CONCATENATE(Settings!J28,"-",Settings!K28))</f>
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <f>IF(Settings!O28="","",Settings!O28)</f>
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <f>Settings!Q28</f>
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <f>_xlfn.CONCAT(Settings!R28," ",Settings!F28)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C25" t="str">
-        <f>IF(Settings!A29="","",Settings!A29)</f>
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <f>IF(Settings!B29="","",Settings!B29)</f>
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <f>IF(CONCATENATE(Settings!C29," ",Settings!D29,"s")=" s"," ",CONCATENATE(Settings!C29," ",Settings!D29,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F25" t="str">
-        <f>IF(Settings!L29="","",Settings!L29)</f>
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <f>CONCATENATE(Settings!E29," ",Settings!F29)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H25" t="str">
-        <f>CONCATENATE(Settings!G29," ",Settings!F29)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I25" t="str">
-        <f>CONCATENATE(Settings!H29," ",Settings!F29)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J25" t="str">
-        <f>CONCATENATE(Settings!I29," ",Settings!F29)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L25" t="str">
-        <f>IF(Settings!M29="","",Settings!M29)</f>
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <f>IF(Settings!N29="","",Settings!N29)</f>
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <f>IF(CONCATENATE(Settings!J29,"-",Settings!K29) = "-","",CONCATENATE(Settings!J29,"-",Settings!K29))</f>
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <f>IF(Settings!O29="","",Settings!O29)</f>
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <f>Settings!Q29</f>
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <f>_xlfn.CONCAT(Settings!R29," ",Settings!F29)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C26" t="str">
-        <f>IF(Settings!A30="","",Settings!A30)</f>
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <f>IF(Settings!B30="","",Settings!B30)</f>
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <f>IF(CONCATENATE(Settings!C30," ",Settings!D30,"s")=" s"," ",CONCATENATE(Settings!C30," ",Settings!D30,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F26" t="str">
-        <f>IF(Settings!L30="","",Settings!L30)</f>
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <f>CONCATENATE(Settings!E30," ",Settings!F30)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H26" t="str">
-        <f>CONCATENATE(Settings!G30," ",Settings!F30)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I26" t="str">
-        <f>CONCATENATE(Settings!H30," ",Settings!F30)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J26" t="str">
-        <f>CONCATENATE(Settings!I30," ",Settings!F30)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L26" t="str">
-        <f>IF(Settings!M30="","",Settings!M30)</f>
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <f>IF(Settings!N30="","",Settings!N30)</f>
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <f>IF(CONCATENATE(Settings!J30,"-",Settings!K30) = "-","",CONCATENATE(Settings!J30,"-",Settings!K30))</f>
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <f>IF(Settings!O30="","",Settings!O30)</f>
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <f>Settings!Q30</f>
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <f>_xlfn.CONCAT(Settings!R30," ",Settings!F30)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C27" t="str">
-        <f>IF(Settings!A31="","",Settings!A31)</f>
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <f>IF(Settings!B31="","",Settings!B31)</f>
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <f>IF(CONCATENATE(Settings!C31," ",Settings!D31,"s")=" s"," ",CONCATENATE(Settings!C31," ",Settings!D31,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F27" t="str">
-        <f>IF(Settings!L31="","",Settings!L31)</f>
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <f>CONCATENATE(Settings!E31," ",Settings!F31)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H27" t="str">
-        <f>CONCATENATE(Settings!G31," ",Settings!F31)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I27" t="str">
-        <f>CONCATENATE(Settings!H31," ",Settings!F31)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J27" t="str">
-        <f>CONCATENATE(Settings!I31," ",Settings!F31)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="L27" t="str">
-        <f>IF(Settings!M31="","",Settings!M31)</f>
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <f>IF(Settings!N31="","",Settings!N31)</f>
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <f>IF(CONCATENATE(Settings!J31,"-",Settings!K31) = "-","",CONCATENATE(Settings!J31,"-",Settings!K31))</f>
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <f>IF(Settings!O31="","",Settings!O31)</f>
-        <v/>
-      </c>
-      <c r="P27" t="str">
-        <f>Settings!Q31</f>
-        <v/>
-      </c>
-      <c r="Q27" t="str">
-        <f>_xlfn.CONCAT(Settings!R31," ",Settings!F31)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C28" t="str">
-        <f>IF(Settings!A32="","",Settings!A32)</f>
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <f>IF(Settings!B32="","",Settings!B32)</f>
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <f>IF(CONCATENATE(Settings!C32," ",Settings!D32,"s")=" s"," ",CONCATENATE(Settings!C32," ",Settings!D32,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F28" t="str">
-        <f>IF(Settings!L32="","",Settings!L32)</f>
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <f>CONCATENATE(Settings!E32," ",Settings!F32)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H28" t="str">
-        <f>CONCATENATE(Settings!G32," ",Settings!F32)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I28" t="str">
-        <f>CONCATENATE(Settings!H32," ",Settings!F32)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J28" t="str">
-        <f>CONCATENATE(Settings!I32," ",Settings!F32)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N28" t="str">
-        <f t="shared" ref="N28:N33" si="0">IF(CONCATENATE(J80,"-",K80) = "-","",CONCATENATE(J80,"-",K80))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C29" t="str">
-        <f>IF(Settings!A33="","",Settings!A33)</f>
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <f>IF(Settings!B33="","",Settings!B33)</f>
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <f>IF(CONCATENATE(Settings!C33," ",Settings!D33,"s")=" s"," ",CONCATENATE(Settings!C33," ",Settings!D33,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F29" t="str">
-        <f>IF(Settings!L33="","",Settings!L33)</f>
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <f>CONCATENATE(Settings!E33," ",Settings!F33)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H29" t="str">
-        <f>CONCATENATE(Settings!G33," ",Settings!F33)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I29" t="str">
-        <f>CONCATENATE(Settings!H33," ",Settings!F33)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J29" t="str">
-        <f>CONCATENATE(Settings!I33," ",Settings!F33)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N29" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q29" t="str">
-        <f>_xlfn.CONCAT(Settings!S18," ",Settings!F18)</f>
-        <v>${offerValidation.AMOUNT_IN_NUMBERS} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C30" t="str">
-        <f>IF(Settings!A34="","",Settings!A34)</f>
-        <v/>
-      </c>
-      <c r="D30" t="str">
-        <f>IF(Settings!B34="","",Settings!B34)</f>
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <f>IF(CONCATENATE(Settings!C34," ",Settings!D34,"s")=" s"," ",CONCATENATE(Settings!C34," ",Settings!D34,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F30" t="str">
-        <f>IF(Settings!L34="","",Settings!L34)</f>
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <f>CONCATENATE(Settings!E34," ",Settings!F34)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H30" t="str">
-        <f>CONCATENATE(Settings!G34," ",Settings!F34)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I30" t="str">
-        <f>CONCATENATE(Settings!H34," ",Settings!F34)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J30" t="str">
-        <f>CONCATENATE(Settings!I34," ",Settings!F34)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P30" s="8"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E31" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s")=" s"," ",CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G31" t="str">
-        <f>CONCATENATE(Settings!E35," ",Settings!F35)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" ref="H31:H35" si="1">CONCATENATE(G83," ",F83)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I31" t="str">
-        <f t="shared" ref="I31:I35" si="2">CONCATENATE(H83," ",F83)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J31" t="str">
-        <f t="shared" ref="J31:J34" si="3">CONCATENATE(I83," ",F83)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q31" t="str">
-        <f>_xlfn.CONCAT(Settings!T18," ",Settings!F18)</f>
-        <v>${offerValidation.VAT_TOTAL} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E32" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s")=" s"," ",CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G32" t="str">
-        <f>CONCATENATE(Settings!E36," ",Settings!F36)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H32" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I32" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J32" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N32" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P32" s="8"/>
-    </row>
-    <row r="33" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E33" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s")=" s"," ",CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G33" t="str">
-        <f>CONCATENATE(Settings!E37," ",Settings!F37)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="N33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q33" t="str">
-        <f>_xlfn.CONCAT(Settings!U18," ",Settings!F18)</f>
-        <v>${offerValidation.AMOUNT_IN_NUMBERS_VAT} ${table:offerProductValidation.CURRENCY}</v>
-      </c>
-    </row>
-    <row r="34" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E34" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s")=" s"," ",CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="G34" t="str">
-        <f>CONCATENATE(Settings!E38," ",Settings!F38)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H34" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I34" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J34" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="35" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E35" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s")=" s"," ",CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I35" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="36" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E36" t="str">
-        <f>IF(CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s")=" s"," ",CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I11:K11"/>
-  </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
   <dimension ref="B2:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3004,23 +1737,23 @@
       <c r="B3" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="78" t="str">
+      <c r="C3" s="99" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
       <c r="H3" s="21"/>
       <c r="I3" s="20"/>
       <c r="J3" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
@@ -3029,20 +1762,20 @@
       <c r="B4" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="81"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
       <c r="H4" s="22"/>
       <c r="I4" s="20"/>
       <c r="J4" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="82"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="84"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="102"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
@@ -3084,153 +1817,153 @@
       <c r="Q6" s="20"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="111"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
+      <c r="S7" s="105"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="86" t="s">
+      <c r="C8" s="89"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="87"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="116"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="60"/>
       <c r="O8" s="44" t="s">
         <v>81</v>
       </c>
       <c r="P8" s="45"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="88" t="s">
+      <c r="C9" s="89"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="89"/>
-      <c r="K9" s="117" t="s">
+      <c r="J9" s="93"/>
+      <c r="K9" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
       <c r="O9" s="44" t="s">
         <v>84</v>
       </c>
       <c r="P9" s="45"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="118" t="s">
+      <c r="C10" s="89"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="119"/>
-      <c r="K10" s="117" t="s">
+      <c r="J10" s="95"/>
+      <c r="K10" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
       <c r="O10" s="44" t="s">
         <v>86</v>
       </c>
       <c r="P10" s="45"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="57"/>
     </row>
     <row r="11" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="55" t="str">
+      <c r="C11" s="89"/>
+      <c r="D11" s="106" t="str">
         <f>Settings!A6</f>
         <v>${offerValidation.SHIPMENTTERMS}</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="86" t="s">
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="87"/>
-      <c r="K11" s="112" t="str">
+      <c r="J11" s="91"/>
+      <c r="K11" s="56" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
       <c r="O11" s="44" t="s">
         <v>84</v>
       </c>
       <c r="P11" s="45"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="113"/>
-      <c r="S11" s="113"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="55" t="s">
+      <c r="C12" s="89"/>
+      <c r="D12" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="108"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
@@ -3260,100 +1993,100 @@
       <c r="Q13" s="20"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="120"/>
     </row>
     <row r="15" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="92" t="s">
+      <c r="E15" s="78"/>
+      <c r="F15" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="92"/>
-      <c r="H15" s="61" t="s">
+      <c r="G15" s="88"/>
+      <c r="H15" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="61" t="s">
+      <c r="I15" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="61" t="s">
+      <c r="J15" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="67" t="s">
+      <c r="K15" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="L15" s="69"/>
-      <c r="M15" s="61" t="s">
+      <c r="L15" s="78"/>
+      <c r="M15" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="67" t="s">
+      <c r="N15" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="69"/>
-      <c r="P15" s="67" t="s">
+      <c r="O15" s="78"/>
+      <c r="P15" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="Q15" s="69"/>
+      <c r="Q15" s="78"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="59"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="73"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="75"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="82"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="60"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
       <c r="K17" s="25" t="s">
         <v>96</v>
       </c>
       <c r="L17" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="M17" s="63"/>
+      <c r="M17" s="85"/>
       <c r="N17" s="25" t="s">
         <v>96</v>
       </c>
@@ -3372,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="26"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="90"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
       <c r="H18" s="26"/>
       <c r="I18" s="14" t="s">
         <v>32</v>
@@ -3396,10 +2129,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="26"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
       <c r="H19" s="26"/>
       <c r="I19" s="27"/>
       <c r="J19" s="26"/>
@@ -3416,10 +2149,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
       <c r="H20" s="26"/>
       <c r="I20" s="27"/>
       <c r="J20" s="26"/>
@@ -3450,90 +2183,90 @@
       <c r="Q21" s="20"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
       <c r="N22" s="20"/>
       <c r="O22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="83" t="s">
         <v>89</v>
       </c>
       <c r="D23" s="49"/>
-      <c r="E23" s="64" t="s">
+      <c r="E23" s="112" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="61" t="s">
+      <c r="F23" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="67" t="s">
+      <c r="H23" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="68"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="67" t="s">
+      <c r="I23" s="115"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="L23" s="69"/>
-      <c r="M23" s="61" t="s">
+      <c r="L23" s="78"/>
+      <c r="M23" s="83" t="s">
         <v>104</v>
       </c>
       <c r="N23" s="20"/>
       <c r="O23" s="20"/>
-      <c r="P23" s="120"/>
+      <c r="P23" s="52"/>
       <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="59"/>
-      <c r="C24" s="62"/>
+      <c r="B24" s="110"/>
+      <c r="C24" s="84"/>
       <c r="D24" s="50"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="62"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="84"/>
       <c r="N24" s="20"/>
       <c r="O24" s="20"/>
-      <c r="P24" s="120"/>
+      <c r="P24" s="52"/>
       <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="60"/>
-      <c r="C25" s="63"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="51"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="63"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="85"/>
       <c r="N25" s="20"/>
       <c r="O25" s="20"/>
       <c r="P25" s="20"/>
@@ -3548,11 +2281,11 @@
       <c r="E26" s="32"/>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="95"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
       <c r="M26" s="32"/>
       <c r="N26" s="20"/>
       <c r="O26" s="20"/>
@@ -3568,11 +2301,11 @@
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
       <c r="M27" s="32"/>
       <c r="N27" s="20"/>
       <c r="O27" s="20"/>
@@ -3588,11 +2321,11 @@
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
       <c r="M28" s="32"/>
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
@@ -3617,26 +2350,26 @@
       <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="100" t="s">
+      <c r="B30" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
       <c r="G30" s="34"/>
       <c r="H30" s="47" t="s">
         <v>106</v>
       </c>
       <c r="I30" s="48"/>
-      <c r="J30" s="101" t="s">
+      <c r="J30" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="K30" s="101"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="101"/>
-      <c r="O30" s="101"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
     </row>
@@ -3646,19 +2379,19 @@
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="103" t="s">
+      <c r="H31" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="104"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="95"/>
-      <c r="O31" s="95"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="68"/>
       <c r="P31" s="20"/>
       <c r="Q31" s="20"/>
     </row>
@@ -3668,19 +2401,19 @@
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="95"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="105" t="s">
+      <c r="H32" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="106"/>
-      <c r="J32" s="95"/>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="95"/>
-      <c r="N32" s="95"/>
-      <c r="O32" s="95"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68"/>
+      <c r="O32" s="68"/>
       <c r="P32" s="20"/>
       <c r="Q32" s="20"/>
     </row>
@@ -3695,16 +2428,16 @@
         <v>113</v>
       </c>
       <c r="G33" s="20"/>
-      <c r="H33" s="105" t="s">
+      <c r="H33" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="I33" s="106"/>
-      <c r="J33" s="95"/>
-      <c r="K33" s="95"/>
-      <c r="L33" s="95"/>
-      <c r="M33" s="95"/>
-      <c r="N33" s="95"/>
-      <c r="O33" s="95"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="68"/>
+      <c r="M33" s="68"/>
+      <c r="N33" s="68"/>
+      <c r="O33" s="68"/>
       <c r="P33" s="20"/>
       <c r="Q33" s="20"/>
     </row>
@@ -3719,16 +2452,16 @@
         <v>113</v>
       </c>
       <c r="G34" s="20"/>
-      <c r="H34" s="107" t="s">
+      <c r="H34" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="I34" s="108"/>
-      <c r="J34" s="97"/>
-      <c r="K34" s="97"/>
-      <c r="L34" s="97"/>
-      <c r="M34" s="97"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
       <c r="P34" s="20"/>
       <c r="Q34" s="20"/>
     </row>
@@ -3769,14 +2502,14 @@
       <c r="Q36" s="20"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="98" t="s">
+      <c r="B37" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="98"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
@@ -3789,14 +2522,14 @@
       <c r="Q37" s="20"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="99" t="s">
+      <c r="B38" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="99"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="99"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
@@ -3809,12 +2542,12 @@
       <c r="Q38" s="20"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="99"/>
-      <c r="C39" s="99"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="99"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
@@ -3827,12 +2560,12 @@
       <c r="Q39" s="20"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="99"/>
-      <c r="C40" s="99"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="99"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="99"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
@@ -3845,12 +2578,12 @@
       <c r="Q40" s="20"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="99"/>
-      <c r="C41" s="99"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="99"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="99"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
       <c r="H41" s="42"/>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
@@ -3863,12 +2596,12 @@
       <c r="Q41" s="20"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="99"/>
-      <c r="C42" s="99"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="99"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
       <c r="H42" s="20"/>
       <c r="I42" s="43" t="s">
         <v>119</v>
@@ -3924,14 +2657,59 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="P15:Q16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K15:L16"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="K23:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="J33:O33"/>
     <mergeCell ref="J34:O34"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G42"/>
@@ -3945,59 +2723,14 @@
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="J33:O33"/>
-    <mergeCell ref="B22:M22"/>
-    <mergeCell ref="K23:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="P15:Q16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="K15:L16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="D15:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -4012,6 +2745,1273 @@
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F4731A-D70B-4034-AE07-DF495FD0B95B}">
+  <dimension ref="C3:Q36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="10" width="20.7109375" customWidth="1"/>
+    <col min="16" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="str">
+        <f>Settings!A9</f>
+        <v>${offerValidation.INSTITUTENAME}</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C8" s="54" t="str">
+        <f>Settings!A2</f>
+        <v>${offerValidation.OFFERID}</v>
+      </c>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="53" t="str">
+        <f>Settings!A3</f>
+        <v>${offerValidation.TENDERID}</v>
+      </c>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53" t="str">
+        <f>Settings!A4</f>
+        <v>${offerValidation.OFFERDATE}</v>
+      </c>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53" t="str">
+        <f>Settings!A5</f>
+        <v>${offerValidation.OFFERVALIDITY}</v>
+      </c>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C11" s="55" t="str">
+        <f>Settings!A6</f>
+        <v>${offerValidation.SHIPMENTTERMS}</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55" t="str">
+        <f>Settings!A7</f>
+        <v>${offerValidation.PAYMENTTERMS}</v>
+      </c>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55" t="str">
+        <f>Settings!A8</f>
+        <v>${offerValidation.DELIVERYTERMS}</v>
+      </c>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+    </row>
+    <row r="12" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C14" t="str">
+        <f>IF(Settings!A18="","",Settings!A18)</f>
+        <v>${table:offerProductValidation.SKU}</v>
+      </c>
+      <c r="D14" t="str">
+        <f>IF(Settings!B18="","",Settings!B18)</f>
+        <v>${table:offerProductValidation.PRODUCT_UNIT_NAME}</v>
+      </c>
+      <c r="E14" t="str">
+        <f>IF(CONCATENATE(Settings!C18," ",Settings!D18,"s")=" s"," ",CONCATENATE(Settings!C18," ",Settings!D18,"s"))</f>
+        <v>${table:offerProductValidation.PAID_VOLUME} ${table:offerProductValidation.UNIT}s</v>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(Settings!L18="","",Settings!L18)</f>
+        <v>${table:offerProductValidation.PACKSIZE}</v>
+      </c>
+      <c r="G14" t="str">
+        <f>CONCATENATE(Settings!E18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.OFFER_PRICE} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+      <c r="H14" t="str">
+        <f>CONCATENATE(Settings!G18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.OFFER_PRICE_VAT} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+      <c r="I14" t="str">
+        <f>CONCATENATE(Settings!H18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+      <c r="J14" t="str">
+        <f>CONCATENATE(Settings!I18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.GROSS_SALES_OFFER_CURRENCY_VAT} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+      <c r="L14" t="str">
+        <f>IF(Settings!M18="","",Settings!M18)</f>
+        <v>${table:offerProductValidation.SAMPLES}</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IF(Settings!N18="","",Settings!N18)</f>
+        <v>${table:offerProductValidation.COUNTRYOFORIGIN}</v>
+      </c>
+      <c r="N14" t="str">
+        <f>IF(CONCATENATE(Settings!J18,"-",Settings!K18) = "-","",CONCATENATE(Settings!J18,"-",Settings!K18))</f>
+        <v>${table:offerProductValidation.OFFER_ID}-${table:offerProductValidation.SORTER}</v>
+      </c>
+      <c r="O14" t="str">
+        <f>IF(Settings!O18="","",Settings!O18)</f>
+        <v>${table:offerProductValidation.FOC}</v>
+      </c>
+      <c r="P14" t="e">
+        <f>Settings!Q18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>_xlfn.CONCAT(Settings!R18," ",Settings!F18)</f>
+        <v>${table:offerProductValidation.NET_PRICE} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C15" t="str">
+        <f>IF(Settings!A19="","",Settings!A19)</f>
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <f>IF(Settings!B19="","",Settings!B19)</f>
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <f>IF(CONCATENATE(Settings!C19," ",Settings!D19,"s")=" s"," ",CONCATENATE(Settings!C19," ",Settings!D19,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F15" t="str">
+        <f>IF(Settings!L19="","",Settings!L19)</f>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <f>CONCATENATE(Settings!E19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H15" t="str">
+        <f>CONCATENATE(Settings!G19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I15" t="str">
+        <f>CONCATENATE(Settings!H19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J15" t="str">
+        <f>CONCATENATE(Settings!I19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L15" t="str">
+        <f>IF(Settings!M19="","",Settings!M19)</f>
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <f>IF(Settings!N19="","",Settings!N19)</f>
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <f>IF(CONCATENATE(Settings!J19,"-",Settings!K19) = "-","",CONCATENATE(Settings!J19,"-",Settings!K19))</f>
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <f>IF(Settings!O19="","",Settings!O19)</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <f>Settings!Q19</f>
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <f>_xlfn.CONCAT(Settings!R19," ",Settings!F19)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C16" t="str">
+        <f>IF(Settings!A20="","",Settings!A20)</f>
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(Settings!B20="","",Settings!B20)</f>
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <f>IF(CONCATENATE(Settings!C20," ",Settings!D20,"s")=" s"," ",CONCATENATE(Settings!C20," ",Settings!D20,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(Settings!L20="","",Settings!L20)</f>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <f>CONCATENATE(Settings!E20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H16" t="str">
+        <f>CONCATENATE(Settings!G20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I16" t="str">
+        <f>CONCATENATE(Settings!H20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J16" t="str">
+        <f>CONCATENATE(Settings!I20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L16" t="str">
+        <f>IF(Settings!M20="","",Settings!M20)</f>
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <f>IF(Settings!N20="","",Settings!N20)</f>
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <f>IF(CONCATENATE(Settings!J20,"-",Settings!K20) = "-","",CONCATENATE(Settings!J20,"-",Settings!K20))</f>
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <f>IF(Settings!O20="","",Settings!O20)</f>
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <f>Settings!Q20</f>
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <f>_xlfn.CONCAT(Settings!R20," ",Settings!F20)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C17" t="str">
+        <f>IF(Settings!A21="","",Settings!A21)</f>
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <f>IF(Settings!B21="","",Settings!B21)</f>
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(CONCATENATE(Settings!C21," ",Settings!D21,"s")=" s"," ",CONCATENATE(Settings!C21," ",Settings!D21,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(Settings!L21="","",Settings!L21)</f>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <f>CONCATENATE(Settings!E21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H17" t="str">
+        <f>CONCATENATE(Settings!G21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I17" t="str">
+        <f>CONCATENATE(Settings!H21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J17" t="str">
+        <f>CONCATENATE(Settings!I21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L17" t="str">
+        <f>IF(Settings!M21="","",Settings!M21)</f>
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <f>IF(Settings!N21="","",Settings!N21)</f>
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <f>IF(CONCATENATE(Settings!J21,"-",Settings!K21) = "-","",CONCATENATE(Settings!J21,"-",Settings!K21))</f>
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <f>IF(Settings!O21="","",Settings!O21)</f>
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <f>Settings!Q21</f>
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <f>_xlfn.CONCAT(Settings!R21," ",Settings!F21)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C18" t="str">
+        <f>IF(Settings!A22="","",Settings!A22)</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f>IF(Settings!B22="","",Settings!B22)</f>
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(CONCATENATE(Settings!C22," ",Settings!D22,"s")=" s"," ",CONCATENATE(Settings!C22," ",Settings!D22,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(Settings!L22="","",Settings!L22)</f>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <f>CONCATENATE(Settings!E22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H18" t="str">
+        <f>CONCATENATE(Settings!G22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I18" t="str">
+        <f>CONCATENATE(Settings!H22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J18" t="str">
+        <f>CONCATENATE(Settings!I22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L18" t="str">
+        <f>IF(Settings!M22="","",Settings!M22)</f>
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <f>IF(Settings!N22="","",Settings!N22)</f>
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <f>IF(CONCATENATE(Settings!J22,"-",Settings!K22) = "-","",CONCATENATE(Settings!J22,"-",Settings!K22))</f>
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <f>IF(Settings!O22="","",Settings!O22)</f>
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <f>Settings!Q22</f>
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <f>_xlfn.CONCAT(Settings!R22," ",Settings!F22)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C19" t="str">
+        <f>IF(Settings!A23="","",Settings!A23)</f>
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <f>IF(Settings!B23="","",Settings!B23)</f>
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <f>IF(CONCATENATE(Settings!C23," ",Settings!D23,"s")=" s"," ",CONCATENATE(Settings!C23," ",Settings!D23,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F19" t="str">
+        <f>IF(Settings!L23="","",Settings!L23)</f>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <f>CONCATENATE(Settings!E23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H19" t="str">
+        <f>CONCATENATE(Settings!G23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I19" t="str">
+        <f>CONCATENATE(Settings!H23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J19" t="str">
+        <f>CONCATENATE(Settings!I23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L19" t="str">
+        <f>IF(Settings!M23="","",Settings!M23)</f>
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <f>IF(Settings!N23="","",Settings!N23)</f>
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <f>IF(CONCATENATE(Settings!J23,"-",Settings!K23) = "-","",CONCATENATE(Settings!J23,"-",Settings!K23))</f>
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <f>IF(Settings!O23="","",Settings!O23)</f>
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <f>Settings!Q23</f>
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <f>_xlfn.CONCAT(Settings!R23," ",Settings!F23)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C20" t="str">
+        <f>IF(Settings!A24="","",Settings!A24)</f>
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <f>IF(Settings!B24="","",Settings!B24)</f>
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <f>IF(CONCATENATE(Settings!C24," ",Settings!D24,"s")=" s"," ",CONCATENATE(Settings!C24," ",Settings!D24,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F20" t="str">
+        <f>IF(Settings!L24="","",Settings!L24)</f>
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <f>CONCATENATE(Settings!E24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H20" t="str">
+        <f>CONCATENATE(Settings!G24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I20" t="str">
+        <f>CONCATENATE(Settings!H24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J20" t="str">
+        <f>CONCATENATE(Settings!I24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L20" t="str">
+        <f>IF(Settings!M24="","",Settings!M24)</f>
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <f>IF(Settings!N24="","",Settings!N24)</f>
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <f>IF(CONCATENATE(Settings!J24,"-",Settings!K24) = "-","",CONCATENATE(Settings!J24,"-",Settings!K24))</f>
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <f>IF(Settings!O24="","",Settings!O24)</f>
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <f>Settings!Q24</f>
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <f>_xlfn.CONCAT(Settings!R24," ",Settings!F24)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C21" t="str">
+        <f>IF(Settings!A25="","",Settings!A25)</f>
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(Settings!B25="","",Settings!B25)</f>
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(CONCATENATE(Settings!C25," ",Settings!D25,"s")=" s"," ",CONCATENATE(Settings!C25," ",Settings!D25,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(Settings!L25="","",Settings!L25)</f>
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <f>CONCATENATE(Settings!E25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H21" t="str">
+        <f>CONCATENATE(Settings!G25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I21" t="str">
+        <f>CONCATENATE(Settings!H25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J21" t="str">
+        <f>CONCATENATE(Settings!I25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(Settings!M25="","",Settings!M25)</f>
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(Settings!N25="","",Settings!N25)</f>
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <f>IF(CONCATENATE(Settings!J25,"-",Settings!K25) = "-","",CONCATENATE(Settings!J25,"-",Settings!K25))</f>
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <f>IF(Settings!O25="","",Settings!O25)</f>
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <f>Settings!Q25</f>
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <f>_xlfn.CONCAT(Settings!R25," ",Settings!F25)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C22" t="str">
+        <f>IF(Settings!A26="","",Settings!A26)</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <f>IF(Settings!B26="","",Settings!B26)</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(CONCATENATE(Settings!C26," ",Settings!D26,"s")=" s"," ",CONCATENATE(Settings!C26," ",Settings!D26,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(Settings!L26="","",Settings!L26)</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>CONCATENATE(Settings!E26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H22" t="str">
+        <f>CONCATENATE(Settings!G26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I22" t="str">
+        <f>CONCATENATE(Settings!H26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J22" t="str">
+        <f>CONCATENATE(Settings!I26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(Settings!M26="","",Settings!M26)</f>
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(Settings!N26="","",Settings!N26)</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <f>IF(CONCATENATE(Settings!J26,"-",Settings!K26) = "-","",CONCATENATE(Settings!J26,"-",Settings!K26))</f>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <f>IF(Settings!O26="","",Settings!O26)</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <f>Settings!Q26</f>
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <f>_xlfn.CONCAT(Settings!R26," ",Settings!F26)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C23" t="str">
+        <f>IF(Settings!A27="","",Settings!A27)</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <f>IF(Settings!B27="","",Settings!B27)</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(CONCATENATE(Settings!C27," ",Settings!D27,"s")=" s"," ",CONCATENATE(Settings!C27," ",Settings!D27,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(Settings!L27="","",Settings!L27)</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>CONCATENATE(Settings!E27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H23" t="str">
+        <f>CONCATENATE(Settings!G27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I23" t="str">
+        <f>CONCATENATE(Settings!H27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J23" t="str">
+        <f>CONCATENATE(Settings!I27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(Settings!M27="","",Settings!M27)</f>
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(Settings!N27="","",Settings!N27)</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <f>IF(CONCATENATE(Settings!J27,"-",Settings!K27) = "-","",CONCATENATE(Settings!J27,"-",Settings!K27))</f>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <f>IF(Settings!O27="","",Settings!O27)</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <f>Settings!Q27</f>
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <f>_xlfn.CONCAT(Settings!R27," ",Settings!F27)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C24" t="str">
+        <f>IF(Settings!A28="","",Settings!A28)</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <f>IF(Settings!B28="","",Settings!B28)</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(CONCATENATE(Settings!C28," ",Settings!D28,"s")=" s"," ",CONCATENATE(Settings!C28," ",Settings!D28,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(Settings!L28="","",Settings!L28)</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>CONCATENATE(Settings!E28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H24" t="str">
+        <f>CONCATENATE(Settings!G28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I24" t="str">
+        <f>CONCATENATE(Settings!H28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J24" t="str">
+        <f>CONCATENATE(Settings!I28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(Settings!M28="","",Settings!M28)</f>
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(Settings!N28="","",Settings!N28)</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <f>IF(CONCATENATE(Settings!J28,"-",Settings!K28) = "-","",CONCATENATE(Settings!J28,"-",Settings!K28))</f>
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <f>IF(Settings!O28="","",Settings!O28)</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <f>Settings!Q28</f>
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <f>_xlfn.CONCAT(Settings!R28," ",Settings!F28)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C25" t="str">
+        <f>IF(Settings!A29="","",Settings!A29)</f>
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <f>IF(Settings!B29="","",Settings!B29)</f>
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(CONCATENATE(Settings!C29," ",Settings!D29,"s")=" s"," ",CONCATENATE(Settings!C29," ",Settings!D29,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F25" t="str">
+        <f>IF(Settings!L29="","",Settings!L29)</f>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <f>CONCATENATE(Settings!E29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H25" t="str">
+        <f>CONCATENATE(Settings!G29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I25" t="str">
+        <f>CONCATENATE(Settings!H29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J25" t="str">
+        <f>CONCATENATE(Settings!I29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L25" t="str">
+        <f>IF(Settings!M29="","",Settings!M29)</f>
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <f>IF(Settings!N29="","",Settings!N29)</f>
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <f>IF(CONCATENATE(Settings!J29,"-",Settings!K29) = "-","",CONCATENATE(Settings!J29,"-",Settings!K29))</f>
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <f>IF(Settings!O29="","",Settings!O29)</f>
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <f>Settings!Q29</f>
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <f>_xlfn.CONCAT(Settings!R29," ",Settings!F29)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C26" t="str">
+        <f>IF(Settings!A30="","",Settings!A30)</f>
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <f>IF(Settings!B30="","",Settings!B30)</f>
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <f>IF(CONCATENATE(Settings!C30," ",Settings!D30,"s")=" s"," ",CONCATENATE(Settings!C30," ",Settings!D30,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F26" t="str">
+        <f>IF(Settings!L30="","",Settings!L30)</f>
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <f>CONCATENATE(Settings!E30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H26" t="str">
+        <f>CONCATENATE(Settings!G30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I26" t="str">
+        <f>CONCATENATE(Settings!H30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J26" t="str">
+        <f>CONCATENATE(Settings!I30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(Settings!M30="","",Settings!M30)</f>
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(Settings!N30="","",Settings!N30)</f>
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <f>IF(CONCATENATE(Settings!J30,"-",Settings!K30) = "-","",CONCATENATE(Settings!J30,"-",Settings!K30))</f>
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <f>IF(Settings!O30="","",Settings!O30)</f>
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <f>Settings!Q30</f>
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <f>_xlfn.CONCAT(Settings!R30," ",Settings!F30)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C27" t="str">
+        <f>IF(Settings!A31="","",Settings!A31)</f>
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <f>IF(Settings!B31="","",Settings!B31)</f>
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(CONCATENATE(Settings!C31," ",Settings!D31,"s")=" s"," ",CONCATENATE(Settings!C31," ",Settings!D31,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F27" t="str">
+        <f>IF(Settings!L31="","",Settings!L31)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>CONCATENATE(Settings!E31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H27" t="str">
+        <f>CONCATENATE(Settings!G31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I27" t="str">
+        <f>CONCATENATE(Settings!H31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J27" t="str">
+        <f>CONCATENATE(Settings!I31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(Settings!M31="","",Settings!M31)</f>
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <f>IF(Settings!N31="","",Settings!N31)</f>
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <f>IF(CONCATENATE(Settings!J31,"-",Settings!K31) = "-","",CONCATENATE(Settings!J31,"-",Settings!K31))</f>
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <f>IF(Settings!O31="","",Settings!O31)</f>
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <f>Settings!Q31</f>
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <f>_xlfn.CONCAT(Settings!R31," ",Settings!F31)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C28" t="str">
+        <f>IF(Settings!A32="","",Settings!A32)</f>
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <f>IF(Settings!B32="","",Settings!B32)</f>
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(CONCATENATE(Settings!C32," ",Settings!D32,"s")=" s"," ",CONCATENATE(Settings!C32," ",Settings!D32,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F28" t="str">
+        <f>IF(Settings!L32="","",Settings!L32)</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>CONCATENATE(Settings!E32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H28" t="str">
+        <f>CONCATENATE(Settings!G32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I28" t="str">
+        <f>CONCATENATE(Settings!H32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J28" t="str">
+        <f>CONCATENATE(Settings!I32," ",Settings!F32)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" ref="N28:N33" si="0">IF(CONCATENATE(J80,"-",K80) = "-","",CONCATENATE(J80,"-",K80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C29" t="str">
+        <f>IF(Settings!A33="","",Settings!A33)</f>
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <f>IF(Settings!B33="","",Settings!B33)</f>
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(CONCATENATE(Settings!C33," ",Settings!D33,"s")=" s"," ",CONCATENATE(Settings!C33," ",Settings!D33,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F29" t="str">
+        <f>IF(Settings!L33="","",Settings!L33)</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>CONCATENATE(Settings!E33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H29" t="str">
+        <f>CONCATENATE(Settings!G33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I29" t="str">
+        <f>CONCATENATE(Settings!H33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J29" t="str">
+        <f>CONCATENATE(Settings!I33," ",Settings!F33)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q29" t="str">
+        <f>_xlfn.CONCAT(Settings!S18," ",Settings!F18)</f>
+        <v>${offerValidation.AMOUNT_IN_NUMBERS} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C30" t="str">
+        <f>IF(Settings!A34="","",Settings!A34)</f>
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <f>IF(Settings!B34="","",Settings!B34)</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF(CONCATENATE(Settings!C34," ",Settings!D34,"s")=" s"," ",CONCATENATE(Settings!C34," ",Settings!D34,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F30" t="str">
+        <f>IF(Settings!L34="","",Settings!L34)</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>CONCATENATE(Settings!E34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H30" t="str">
+        <f>CONCATENATE(Settings!G34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I30" t="str">
+        <f>CONCATENATE(Settings!H34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J30" t="str">
+        <f>CONCATENATE(Settings!I34," ",Settings!F34)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E31" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s")=" s"," ",CONCATENATE(Quotation_old!C83," ",Quotation_old!D83,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G31" t="str">
+        <f>CONCATENATE(Settings!E35," ",Settings!F35)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" ref="H31:H35" si="1">CONCATENATE(G83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" ref="I31:I35" si="2">CONCATENATE(H83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" ref="J31:J34" si="3">CONCATENATE(I83," ",F83)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q31" t="str">
+        <f>_xlfn.CONCAT(Settings!T18," ",Settings!F18)</f>
+        <v>${offerValidation.VAT_TOTAL} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E32" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s")=" s"," ",CONCATENATE(Quotation_old!C84," ",Quotation_old!D84,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G32" t="str">
+        <f>CONCATENATE(Settings!E36," ",Settings!F36)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P32" s="8"/>
+    </row>
+    <row r="33" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E33" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s")=" s"," ",CONCATENATE(Quotation_old!C85," ",Quotation_old!D85,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G33" t="str">
+        <f>CONCATENATE(Settings!E37," ",Settings!F37)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q33" t="str">
+        <f>_xlfn.CONCAT(Settings!U18," ",Settings!F18)</f>
+        <v>${offerValidation.AMOUNT_IN_NUMBERS_VAT} ${table:offerProductValidation.CURRENCY}</v>
+      </c>
+    </row>
+    <row r="34" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E34" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s")=" s"," ",CONCATENATE(Quotation_old!C86," ",Quotation_old!D86,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="G34" t="str">
+        <f>CONCATENATE(Settings!E38," ",Settings!F38)</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="35" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E35" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s")=" s"," ",CONCATENATE(Quotation_old!C87," ",Quotation_old!D87,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="36" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E36" t="str">
+        <f>IF(CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s")=" s"," ",CONCATENATE(Quotation_old!C88," ",Quotation_old!D88,"s"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I11:K11"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="4294967294" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4681,29 +4681,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -4900,25 +4877,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4935,4 +4917,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F5D0EE-04D5-4DC3-9DF3-07A3D550A529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73333E37-04FD-4197-8192-532B6D370846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="115">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>${offerValidation.SHIPMENTTERMS}</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.PRODUCT_UNIT_NAME}</t>
   </si>
   <si>
     <t>${table:offerProductValidation.SKU}</t>
@@ -291,9 +288,6 @@
 Discount</t>
   </si>
   <si>
-    <t>Total Offer Value</t>
-  </si>
-  <si>
     <t>excl. vat.</t>
   </si>
   <si>
@@ -373,10 +367,22 @@
     <t>Position</t>
   </si>
   <si>
-    <t>=Settings!A4</t>
-  </si>
-  <si>
-    <t>=Settings!A5</t>
+    <t>${offerValidation.SELLINGCOMPANY}</t>
+  </si>
+  <si>
+    <t>${offerValidation.DISTRIBUTORNAME}</t>
+  </si>
+  <si>
+    <t>${offerValidation.DISTRIBUTORADDRESS}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PRODUCTNAME}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PAID_VOLUME} / ${table:offerProductValidation.UNIT}</t>
+  </si>
+  <si>
+    <t>${offerValidation.CUSTOMER_CODE}</t>
   </si>
 </sst>
 </file>
@@ -754,7 +760,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -790,7 +796,6 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -840,7 +845,112 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -852,55 +962,58 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -933,107 +1046,35 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1206,8 +1247,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}" name="Tabel1" displayName="Tabel1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:B13" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}" name="Tabel1" displayName="Tabel1" ref="A1:B14" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:B14" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{22EAB7A2-53F9-497F-A4B5-CA34E48AC441}" name="Header fields"/>
     <tableColumn id="2" xr3:uid="{331DD14B-B263-41D9-B2C5-D198B6F2436E}" name="Description"/>
@@ -1543,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
-  <dimension ref="B2:S44"/>
+  <dimension ref="B2:T44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
@@ -1551,7 +1592,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1569,54 +1610,59 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="59" t="str">
-        <f>Settings!A9</f>
-        <v>${offerValidation.INSTITUTENAME}</v>
-      </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
+      <c r="J3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" s="97" t="str">
+        <f>Settings!A11</f>
+        <v>${offerValidation.SELLINGCOMPANY}</v>
+      </c>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="62"/>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B4" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="94" t="str">
+        <f>Settings!A13</f>
+        <v>${offerValidation.DISTRIBUTORADDRESS}</v>
+      </c>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="96"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="63"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
+      <c r="J4" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="98"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="100"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -1634,7 +1680,7 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1652,154 +1698,158 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="67" t="s">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B7" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="104"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="69"/>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="66" t="s">
+      <c r="C8" s="101"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="70" t="s">
+      <c r="J8" s="106"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="71"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="106"/>
-      <c r="O8" s="34" t="s">
+      <c r="P8" s="34"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B9" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="103"/>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="66" t="s">
+      <c r="C9" s="101"/>
+      <c r="D9" s="94" t="str">
+        <f>Settings!A14</f>
+        <v>${offerValidation.CUSTOMER_CODE}</v>
+      </c>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="72" t="s">
+      <c r="J9" s="108"/>
+      <c r="K9" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="73"/>
-      <c r="K9" s="107" t="s">
-        <v>111</v>
-      </c>
-      <c r="L9" s="107"/>
-      <c r="M9" s="107"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="34" t="s">
+      <c r="P9" s="34"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B10" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="66" t="s">
+      <c r="C10" s="101"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="93"/>
+      <c r="K10" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="75"/>
-      <c r="K10" s="107" t="s">
-        <v>112</v>
-      </c>
-      <c r="L10" s="107"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="103"/>
-    </row>
-    <row r="11" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="66" t="s">
+      <c r="P10" s="34"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+    </row>
+    <row r="11" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="76" t="str">
-        <f>Settings!A6</f>
-        <v>${offerValidation.SHIPMENTTERMS}</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="70" t="s">
+      <c r="C11" s="101"/>
+      <c r="D11" s="89" t="str">
+        <f>Settings!A12</f>
+        <v>${offerValidation.DISTRIBUTORNAME}</v>
+      </c>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="71"/>
-      <c r="K11" s="102" t="str">
+      <c r="J11" s="106"/>
+      <c r="K11" s="47" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
-      <c r="S11" s="103"/>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="66" t="s">
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B12" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="89" t="str">
+        <f>Settings!A8</f>
+        <v>${offerValidation.DELIVERYTERMS}</v>
+      </c>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="91"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1810,7 +1860,7 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1828,179 +1878,198 @@
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="43" t="s">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B14" s="114" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="115"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+    </row>
+    <row r="15" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="78" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-    </row>
-    <row r="15" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="44" t="s">
+      <c r="C15" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="D15" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="79" t="s">
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="47" t="s">
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="88"/>
+      <c r="O15" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="47" t="s">
+      <c r="P15" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="K15" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="51"/>
-      <c r="M15" s="47" t="s">
+      <c r="S15" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="T15" s="69"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B16" s="79"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="75"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="73"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B17" s="80"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="N15" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="O15" s="51"/>
-      <c r="P15" s="50" t="s">
+      <c r="Q17" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="51"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="45"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="55"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="46"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="76"/>
+      <c r="S17" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="16">
         <v>1</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="C18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="110" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="111"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="116" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="116"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="117" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="118"/>
+      <c r="O18" s="16"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="21"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q18" s="19"/>
+      <c r="R18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="16">
         <v>2</v>
       </c>
       <c r="C19" s="16"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="21"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="16">
         <v>3</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="21"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -2018,165 +2087,165 @@
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="80" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B22" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="44" t="s">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B23" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="83" t="s">
+      <c r="D23" s="38"/>
+      <c r="E23" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="H23" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="I23" s="84"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="L23" s="69"/>
+      <c r="M23" s="74" t="s">
         <v>91</v>
-      </c>
-      <c r="I23" s="86"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="L23" s="51"/>
-      <c r="M23" s="47" t="s">
-        <v>93</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
-      <c r="P23" s="42"/>
+      <c r="P23" s="41"/>
       <c r="Q23" s="10"/>
     </row>
-    <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="45"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="48"/>
+    <row r="24" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="79"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="75"/>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
-      <c r="P24" s="42"/>
+      <c r="P24" s="41"/>
       <c r="Q24" s="10"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="46"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="49"/>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" s="80"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="76"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="22">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="21">
         <v>1</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="22"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="21"/>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="10"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="22">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" s="21">
         <v>2</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="89"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="82"/>
-      <c r="M27" s="22"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="21"/>
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="22">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B28" s="21">
         <v>3</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="22"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="21"/>
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="23"/>
+      <c r="E29" s="22"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
-      <c r="J29" s="23"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
@@ -2185,130 +2254,130 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="93" t="s">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B30" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" s="37"/>
+      <c r="J30" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="I30" s="38"/>
-      <c r="J30" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="K30" s="94"/>
-      <c r="L30" s="94"/>
-      <c r="M30" s="94"/>
-      <c r="N30" s="94"/>
-      <c r="O30" s="94"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B31" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B31" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="96" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="97"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="82"/>
-      <c r="N31" s="82"/>
-      <c r="O31" s="82"/>
+      <c r="H31" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="61"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="59"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="59"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B32" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="99"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="82"/>
-      <c r="O32" s="82"/>
+      <c r="H32" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="63"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="59"/>
+      <c r="O32" s="59"/>
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="98" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="99"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
-      <c r="N33" s="82"/>
-      <c r="O33" s="82"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="59"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="59"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="59"/>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="27" t="s">
+      <c r="B34" s="27" t="s">
         <v>102</v>
       </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="26" t="s">
+        <v>100</v>
+      </c>
       <c r="G34" s="10"/>
-      <c r="H34" s="100" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" s="101"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="90"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="90"/>
+      <c r="H34" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="I34" s="65"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="23"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="22"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="31"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -2338,14 +2407,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="91"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
+      <c r="B37" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2358,14 +2427,14 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="92"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="92"/>
+      <c r="B38" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -2378,12 +2447,12 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="92"/>
-      <c r="C39" s="92"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2396,12 +2465,12 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -2414,13 +2483,13 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="32"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="31"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
@@ -2432,21 +2501,21 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="92"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
       <c r="H42" s="10"/>
-      <c r="I42" s="33" t="s">
-        <v>108</v>
+      <c r="I42" s="32" t="s">
+        <v>106</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="L42" s="23"/>
+        <v>107</v>
+      </c>
+      <c r="L42" s="22"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
       <c r="O42" s="10"/>
@@ -2455,8 +2524,8 @@
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
@@ -2464,9 +2533,9 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="L43" s="23"/>
+        <v>108</v>
+      </c>
+      <c r="L43" s="22"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
       <c r="O43" s="10"/>
@@ -2481,7 +2550,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
-      <c r="I44" s="23"/>
+      <c r="I44" s="22"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
@@ -2492,15 +2561,61 @@
       <c r="Q44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
+  <mergeCells count="75">
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="R15:R17"/>
+    <mergeCell ref="S15:T16"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B14:R14"/>
+    <mergeCell ref="O15:O17"/>
+    <mergeCell ref="J15:L17"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="M15:N17"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="K23:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="J33:O33"/>
     <mergeCell ref="J34:O34"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G42"/>
@@ -2514,59 +2629,14 @@
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="J33:O33"/>
-    <mergeCell ref="B22:M22"/>
-    <mergeCell ref="K23:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="P15:Q16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="K15:L16"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:E17"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2612,15 +2682,15 @@
     <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2628,7 +2698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2636,7 +2706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2644,7 +2714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2652,7 +2722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2660,7 +2730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2668,7 +2738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2676,7 +2746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2684,52 +2754,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="46"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>9</v>
@@ -2744,88 +2847,88 @@
         <v>13</v>
       </c>
       <c r="P17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="S17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>24</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>25</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>26</v>
       </c>
-      <c r="O18" t="s">
-        <v>27</v>
-      </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q18" t="e">
         <f>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
       <c r="R18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3250,29 +3353,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3469,25 +3549,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3504,4 +3589,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73333E37-04FD-4197-8192-532B6D370846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B43A2E5-11FD-4D26-8BA1-92408C8EBC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -275,10 +275,6 @@
   </si>
   <si>
     <t>Product Generic Name</t>
-  </si>
-  <si>
-    <t>Offer QTY 
-/UoM</t>
   </si>
   <si>
     <t>Unit Dosge</t>
@@ -379,10 +375,21 @@
     <t>${table:offerProductValidation.PRODUCTNAME}</t>
   </si>
   <si>
-    <t>${table:offerProductValidation.PAID_VOLUME} / ${table:offerProductValidation.UNIT}</t>
-  </si>
-  <si>
     <t>${offerValidation.CUSTOMER_CODE}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer QTY 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+UoM</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.DOSAGE}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.MANUFACTURER}</t>
   </si>
 </sst>
 </file>
@@ -393,7 +400,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#\.###\.###.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,13 +496,6 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -760,7 +760,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -784,17 +784,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,19 +827,96 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -857,7 +926,85 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -878,204 +1025,99 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1201,14 +1243,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>24880</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>554047</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>7997</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>790842</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>536843</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>19691</xdr:rowOff>
     </xdr:to>
@@ -1233,8 +1275,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4968355" y="5675372"/>
-          <a:ext cx="1519495" cy="773694"/>
+          <a:off x="6353714" y="6865997"/>
+          <a:ext cx="1527962" cy="773694"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1584,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
-  <dimension ref="B2:T44"/>
+  <dimension ref="B2:Y44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
@@ -1592,7 +1634,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1610,59 +1652,59 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B3" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
+      <c r="C3" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="97" t="str">
+      <c r="K3" s="41" t="str">
         <f>Settings!A11</f>
         <v>${offerValidation.SELLINGCOMPANY}</v>
       </c>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="94" t="str">
+      <c r="C4" s="42" t="str">
         <f>Settings!A13</f>
         <v>${offerValidation.DISTRIBUTORADDRESS}</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="96"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="98"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="100"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="47"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -1680,7 +1722,7 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1698,158 +1740,161 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="102" t="s">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="104"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="101" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="51"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B8" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="105" t="s">
+      <c r="C8" s="48"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="106"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="33" t="s">
+      <c r="J8" s="53"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="101" t="s">
+      <c r="P8" s="30"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="94" t="str">
+      <c r="C9" s="48"/>
+      <c r="D9" s="42" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="107" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="108"/>
-      <c r="K9" s="52" t="s">
+      <c r="J9" s="55"/>
+      <c r="K9" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="33" t="s">
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="101" t="s">
+      <c r="P9" s="30"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+      <c r="S9" s="95"/>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="92" t="s">
+      <c r="C10" s="48"/>
+      <c r="D10" s="42" t="str">
+        <f>Settings!A9</f>
+        <v>${offerValidation.INSTITUTENAME}</v>
+      </c>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="52" t="s">
+      <c r="J10" s="57"/>
+      <c r="K10" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="33" t="s">
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-    </row>
-    <row r="11" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="101" t="s">
+      <c r="P10" s="30"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+    </row>
+    <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="89" t="str">
+      <c r="C11" s="48"/>
+      <c r="D11" s="58" t="str">
         <f>Settings!A12</f>
         <v>${offerValidation.DISTRIBUTORNAME}</v>
       </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="105" t="s">
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="106"/>
-      <c r="K11" s="47" t="str">
+      <c r="J11" s="53"/>
+      <c r="K11" s="94" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="33" t="s">
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="101" t="s">
+      <c r="P11" s="30"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B12" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="101"/>
-      <c r="D12" s="89" t="str">
+      <c r="C12" s="48"/>
+      <c r="D12" s="58" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="91"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1860,7 +1905,7 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1878,198 +1923,236 @@
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="114" t="s">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="115"/>
-    </row>
-    <row r="15" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="78" t="s">
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="120"/>
+    </row>
+    <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="88" t="s">
+      <c r="D15" s="101"/>
+      <c r="E15" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="68" t="s">
+      <c r="F15" s="37"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="88" t="s">
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="112" t="s">
+        <v>113</v>
+      </c>
+      <c r="L15" s="113"/>
+      <c r="M15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="N15" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88" t="s">
-        <v>9</v>
-      </c>
-      <c r="N15" s="88"/>
-      <c r="O15" s="74" t="s">
+      <c r="Q15" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="P15" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="74" t="s">
+      <c r="V15" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+    </row>
+    <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="68"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="70"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="70"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B17" s="69"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="S15" s="68" t="s">
-        <v>14</v>
-      </c>
-      <c r="T15" s="69"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B16" s="79"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="88"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="73"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="80"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="15" t="s">
+      <c r="R17" s="111"/>
+      <c r="S17" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="Q17" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="R17" s="76"/>
-      <c r="S17" s="15" t="s">
+      <c r="T17" s="111"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="W17" s="111"/>
+      <c r="X17" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B18" s="16">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="Y17" s="127"/>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="110" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="111"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="116" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="117" t="s">
+      <c r="D18" s="73"/>
+      <c r="E18" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="105"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="108"/>
+      <c r="M18" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="N18" s="118"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="4" t="s">
+      <c r="O18" s="108"/>
+      <c r="P18" s="110" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q18" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="40"/>
+      <c r="S18" s="119" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="119"/>
+      <c r="U18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="16">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="16">
-        <v>3</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="113"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="V18" s="123" t="s">
+        <v>53</v>
+      </c>
+      <c r="W18" s="124"/>
+      <c r="X18" s="107"/>
+      <c r="Y18" s="108"/>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="103"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="103"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="119"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="121"/>
+      <c r="W19" s="122"/>
+      <c r="X19" s="107"/>
+      <c r="Y19" s="108"/>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="102"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="103"/>
+      <c r="S20" s="119"/>
+      <c r="T20" s="119"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="121"/>
+      <c r="W20" s="122"/>
+      <c r="X20" s="107"/>
+      <c r="Y20" s="108"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -2087,165 +2170,155 @@
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B22" s="67" t="s">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B22" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+    </row>
+    <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="64"/>
+      <c r="E23" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="81" t="s">
+      <c r="F23" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="74" t="s">
+      <c r="G23" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="H23" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="68" t="s">
+      <c r="I23" s="37"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="84"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="68" t="s">
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="L23" s="69"/>
-      <c r="M23" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="10"/>
-    </row>
-    <row r="24" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="79"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="71"/>
+    </row>
+    <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="68"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="74"/>
       <c r="K24" s="70"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="10"/>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B25" s="80"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="73"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B26" s="21">
-        <v>1</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B27" s="21">
-        <v>2</v>
-      </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B28" s="21">
-        <v>3</v>
-      </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B25" s="69"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="70"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="107" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="108"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="132" t="s">
+        <v>116</v>
+      </c>
+      <c r="L26" s="132"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="125"/>
+      <c r="O26" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B27" s="17"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="17"/>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B28" s="17"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="17"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="22"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
-      <c r="J29" s="22"/>
+      <c r="J29" s="18"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
@@ -2254,130 +2327,130 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B30" s="85" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="36" t="s">
+      <c r="I30" s="33"/>
+      <c r="J30" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="37"/>
-      <c r="J30" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="57"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="86"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B31" s="24" t="s">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="I31" s="61"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="59"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="59"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B32" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="I32" s="63"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="59"/>
-      <c r="N32" s="59"/>
-      <c r="O32" s="59"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="76"/>
+      <c r="M32" s="76"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="76"/>
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="26" t="s">
+      <c r="G33" s="10"/>
+      <c r="H33" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="I33" s="63"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="59"/>
-      <c r="M33" s="59"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="59"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="76"/>
+      <c r="N33" s="76"/>
+      <c r="O33" s="76"/>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="I34" s="65"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="22"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="30"/>
+      <c r="H35" s="26"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -2407,14 +2480,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
+      <c r="B37" s="83" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2427,14 +2500,14 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
+      <c r="B38" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -2447,12 +2520,12 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2465,12 +2538,12 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -2483,13 +2556,13 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="31"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="27"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
@@ -2501,43 +2574,37 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
       <c r="H42" s="10"/>
-      <c r="I42" s="32" t="s">
+      <c r="L42" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L42" s="22"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="L43" s="22"/>
+      <c r="L43" s="10"/>
       <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
+      <c r="N43" s="10" t="s">
+        <v>107</v>
+      </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
@@ -2550,7 +2617,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
-      <c r="I44" s="22"/>
+      <c r="I44" s="18"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
@@ -2561,19 +2628,78 @@
       <c r="Q44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G15:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
+  <mergeCells count="101">
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B22:O22"/>
+    <mergeCell ref="K23:N25"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="V15:Y16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G42"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="J33:O33"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D25"/>
+    <mergeCell ref="O23:O25"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E15:G17"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B14:R14"/>
+    <mergeCell ref="N15:O17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="K15:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N19:O19"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -2587,56 +2713,23 @@
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D12:H12"/>
-    <mergeCell ref="R15:R17"/>
-    <mergeCell ref="S15:T16"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B14:R14"/>
-    <mergeCell ref="O15:O17"/>
-    <mergeCell ref="J15:L17"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="M15:N17"/>
-    <mergeCell ref="B22:M22"/>
-    <mergeCell ref="K23:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="J33:O33"/>
-    <mergeCell ref="J34:O34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G42"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="J30:O30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="J31:O31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="Q15:T16"/>
+    <mergeCell ref="S17:T17"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2764,7 +2857,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
         <v>64</v>
@@ -2772,7 +2865,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
@@ -2780,7 +2873,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
         <v>65</v>
@@ -2788,12 +2881,12 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="46"/>
+      <c r="C14" s="34"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2870,7 +2963,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -3078,6 +3171,7 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
+      <c r="C31" s="109"/>
       <c r="E31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -3090,6 +3184,7 @@
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
+      <c r="C32" s="109"/>
       <c r="E32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3353,6 +3448,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3549,30 +3667,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3589,22 +3702,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B43A2E5-11FD-4D26-8BA1-92408C8EBC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4825E7-914D-441F-BFED-1DA523471156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -533,7 +533,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -641,19 +641,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -673,61 +660,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -736,31 +668,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -830,56 +744,147 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -893,231 +898,15 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1244,22 +1033,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>554047</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>7997</xdr:rowOff>
+      <xdr:colOff>31751</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>52916</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>536843</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>19691</xdr:rowOff>
+      <xdr:colOff>10717</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>65175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31CDDEB-371C-4DF3-A3BA-E535456AD3BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAB78DC-B8BD-201A-CBFF-1F60D61D4715}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1275,8 +1064,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6353714" y="6865997"/>
-          <a:ext cx="1527962" cy="773694"/>
+          <a:off x="5831418" y="7101416"/>
+          <a:ext cx="1524132" cy="774259"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1656,25 +1445,25 @@
       <c r="B3" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="41" t="str">
+      <c r="K3" s="58" t="str">
         <f>Settings!A11</f>
         <v>${offerValidation.SELLINGCOMPANY}</v>
       </c>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -1683,23 +1472,23 @@
       <c r="B4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="42" t="str">
+      <c r="C4" s="52" t="str">
         <f>Settings!A13</f>
         <v>${offerValidation.DISTRIBUTORADDRESS}</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
       <c r="J4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="47"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1741,160 +1530,160 @@
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="51"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="47"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="52" t="s">
+      <c r="C8" s="62"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="53"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="97"/>
-      <c r="M8" s="97"/>
-      <c r="N8" s="98"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="78"/>
       <c r="O8" s="29" t="s">
         <v>69</v>
       </c>
       <c r="P8" s="30"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="95"/>
-      <c r="S8" s="95"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="42" t="str">
+      <c r="C9" s="62"/>
+      <c r="D9" s="52" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="54" t="s">
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="55"/>
-      <c r="K9" s="99" t="s">
+      <c r="J9" s="86"/>
+      <c r="K9" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
       <c r="O9" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P9" s="30"/>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="95"/>
-      <c r="S9" s="95"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="42" t="str">
+      <c r="C10" s="62"/>
+      <c r="D10" s="52" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="56" t="s">
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="57"/>
-      <c r="K10" s="99" t="s">
+      <c r="J10" s="51"/>
+      <c r="K10" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="99"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
       <c r="O10" s="29" t="s">
         <v>74</v>
       </c>
       <c r="P10" s="30"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="95"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
     </row>
     <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="58" t="str">
+      <c r="C11" s="62"/>
+      <c r="D11" s="55" t="str">
         <f>Settings!A12</f>
         <v>${offerValidation.DISTRIBUTORNAME}</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="52" t="s">
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="94" t="str">
+      <c r="J11" s="84"/>
+      <c r="K11" s="75" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
       <c r="O11" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P11" s="30"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="95"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="58" t="str">
+      <c r="C12" s="62"/>
+      <c r="D12" s="55" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="60"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="57"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1924,233 +1713,240 @@
       <c r="Q13" s="10"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="89"/>
+      <c r="O14" s="89"/>
+      <c r="P14" s="89"/>
+      <c r="Q14" s="89"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="89"/>
+      <c r="W14" s="89"/>
+      <c r="X14" s="89"/>
+      <c r="Y14" s="89"/>
     </row>
     <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="36" t="s">
+      <c r="D15" s="63"/>
+      <c r="E15" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="36" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="112" t="s">
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="113"/>
-      <c r="M15" s="61" t="s">
+      <c r="L15" s="66"/>
+      <c r="M15" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="N15" s="70" t="s">
+      <c r="N15" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70" t="s">
+      <c r="O15" s="43"/>
+      <c r="P15" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="Q15" s="70" t="s">
+      <c r="Q15" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="61" t="s">
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="V15" s="70" t="s">
+      <c r="V15" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="43"/>
     </row>
     <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="68"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="70"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="70"/>
-      <c r="X16" s="70"/>
-      <c r="Y16" s="70"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="69"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="111" t="s">
+      <c r="B17" s="82"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111" t="s">
+      <c r="R17" s="44"/>
+      <c r="S17" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="111"/>
-      <c r="U17" s="63"/>
-      <c r="V17" s="111" t="s">
+      <c r="T17" s="44"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="111"/>
-      <c r="X17" s="126" t="s">
+      <c r="W17" s="44"/>
+      <c r="X17" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="Y17" s="127"/>
+      <c r="Y17" s="44"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="73" t="s">
+      <c r="C18" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="104" t="s">
+      <c r="D18" s="64"/>
+      <c r="E18" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="105"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="107" t="s">
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="108"/>
-      <c r="M18" s="109" t="s">
+      <c r="L18" s="42"/>
+      <c r="M18" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="107" t="s">
+      <c r="N18" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="O18" s="108"/>
-      <c r="P18" s="110" t="s">
+      <c r="O18" s="42"/>
+      <c r="P18" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="Q18" s="40" t="s">
+      <c r="Q18" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="R18" s="40"/>
-      <c r="S18" s="119" t="s">
+      <c r="R18" s="41"/>
+      <c r="S18" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="119"/>
-      <c r="U18" s="4" t="s">
+      <c r="T18" s="88"/>
+      <c r="U18" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="123" t="s">
+      <c r="V18" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="W18" s="124"/>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="108"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="103"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="102"/>
-      <c r="R19" s="103"/>
-      <c r="S19" s="119"/>
-      <c r="T19" s="119"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
       <c r="U19" s="16"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="122"/>
-      <c r="X19" s="107"/>
-      <c r="Y19" s="108"/>
+      <c r="V19" s="87"/>
+      <c r="W19" s="87"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="42"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="108"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="102"/>
-      <c r="R20" s="103"/>
-      <c r="S20" s="119"/>
-      <c r="T20" s="119"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="121"/>
-      <c r="W20" s="122"/>
-      <c r="X20" s="107"/>
-      <c r="Y20" s="108"/>
+      <c r="V20" s="87"/>
+      <c r="W20" s="87"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
@@ -2171,143 +1967,149 @@
       <c r="Q21" s="10"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="49"/>
     </row>
     <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="77" t="s">
+      <c r="D23" s="43"/>
+      <c r="E23" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="61" t="s">
+      <c r="F23" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="37"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="70" t="s">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="70" t="s">
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43" t="s">
         <v>90</v>
       </c>
+      <c r="P23" s="43"/>
     </row>
     <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="68"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="69"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="70"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="107" t="s">
+      <c r="C26" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="108"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="132" t="s">
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="L26" s="132"/>
-      <c r="M26" s="125"/>
-      <c r="N26" s="125"/>
-      <c r="O26" s="17" t="s">
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48" t="s">
         <v>25</v>
       </c>
+      <c r="P26" s="48"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="81"/>
       <c r="I27" s="81"/>
       <c r="J27" s="81"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="17"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="17"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="129"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="81"/>
       <c r="I28" s="81"/>
       <c r="J28" s="81"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="10"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
       <c r="Q28" s="10"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.25">
@@ -2328,28 +2130,26 @@
       <c r="Q29" s="10"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
       <c r="G30" s="19"/>
-      <c r="H30" s="32" t="s">
+      <c r="I30" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="33"/>
-      <c r="J30" s="86" t="s">
+      <c r="J30" s="33"/>
+      <c r="K30" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
@@ -2357,21 +2157,19 @@
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="87"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="88" t="s">
+      <c r="I31" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="I31" s="89"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
@@ -2379,21 +2177,19 @@
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="90" t="s">
+      <c r="I32" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="I32" s="91"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="76"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="48"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
@@ -2406,18 +2202,16 @@
         <v>99</v>
       </c>
       <c r="G33" s="10"/>
-      <c r="H33" s="90" t="s">
+      <c r="I33" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="91"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="76"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -2430,18 +2224,16 @@
         <v>99</v>
       </c>
       <c r="G34" s="10"/>
-      <c r="H34" s="92" t="s">
+      <c r="I34" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="I34" s="93"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="82"/>
-      <c r="N34" s="82"/>
-      <c r="O34" s="82"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="80"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
@@ -2480,14 +2272,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2500,18 +2292,18 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="84" t="s">
+      <c r="B38" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84"/>
-      <c r="G38" s="84"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="74"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -2520,16 +2312,16 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="84"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -2538,16 +2330,16 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="74"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -2556,16 +2348,16 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
       <c r="H41" s="27"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
+      <c r="J41" s="74"/>
+      <c r="K41" s="74"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2574,12 +2366,12 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
       <c r="H42" s="10"/>
       <c r="L42" s="28" t="s">
         <v>105</v>
@@ -2628,10 +2420,12 @@
       <c r="Q44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
+  <mergeCells count="104">
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="B22:O22"/>
     <mergeCell ref="K23:N25"/>
     <mergeCell ref="K28:N28"/>
     <mergeCell ref="K27:N27"/>
@@ -2649,6 +2443,21 @@
     <mergeCell ref="S20:T20"/>
     <mergeCell ref="U15:U17"/>
     <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G23:G25"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="Q9:S9"/>
@@ -2657,56 +2466,21 @@
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="K9:N9"/>
     <mergeCell ref="K10:N10"/>
-    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="K34:P34"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G42"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="K30:P30"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="K31:P31"/>
     <mergeCell ref="E32:F32"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="J33:O33"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C23:D25"/>
-    <mergeCell ref="O23:O25"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E15:G17"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B14:R14"/>
-    <mergeCell ref="N15:O17"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="K15:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="J38:K41"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
@@ -2719,17 +2493,38 @@
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:S7"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D25"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E15:G17"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="N15:O17"/>
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q19:R19"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="Q15:T16"/>
     <mergeCell ref="S17:T17"/>
+    <mergeCell ref="B14:Y14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="O23:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="K15:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="N20:O20"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -3171,7 +2966,7 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="109"/>
+      <c r="C31" s="39"/>
       <c r="E31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -3184,7 +2979,7 @@
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="109"/>
+      <c r="C32" s="39"/>
       <c r="E32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4825E7-914D-441F-BFED-1DA523471156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04E3D32-2D67-4ED3-B5D9-2D9C06DF910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -745,12 +745,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -760,152 +754,152 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1445,25 +1439,25 @@
       <c r="B3" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="58" t="str">
+      <c r="K3" s="75" t="str">
         <f>Settings!A11</f>
         <v>${offerValidation.SELLINGCOMPANY}</v>
       </c>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -1472,23 +1466,23 @@
       <c r="B4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="52" t="str">
+      <c r="C4" s="69" t="str">
         <f>Settings!A13</f>
         <v>${offerValidation.DISTRIBUTORADDRESS}</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
       <c r="J4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="59"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="78"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1530,160 +1524,160 @@
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="47"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="81"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="83" t="s">
+      <c r="C8" s="52"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="78"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
       <c r="O8" s="29" t="s">
         <v>69</v>
       </c>
       <c r="P8" s="30"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="52" t="str">
+      <c r="C9" s="52"/>
+      <c r="D9" s="69" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="85" t="s">
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="79" t="s">
+      <c r="J9" s="42"/>
+      <c r="K9" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="79"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
       <c r="O9" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P9" s="30"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="52" t="str">
+      <c r="C10" s="52"/>
+      <c r="D10" s="69" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="50" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="51"/>
-      <c r="K10" s="79" t="s">
+      <c r="J10" s="68"/>
+      <c r="K10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
       <c r="O10" s="29" t="s">
         <v>74</v>
       </c>
       <c r="P10" s="30"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
     </row>
     <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="55" t="str">
+      <c r="C11" s="52"/>
+      <c r="D11" s="72" t="str">
         <f>Settings!A12</f>
         <v>${offerValidation.DISTRIBUTORNAME}</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="83" t="s">
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="84"/>
-      <c r="K11" s="75" t="str">
+      <c r="J11" s="40"/>
+      <c r="K11" s="53" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P11" s="30"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="55" t="str">
+      <c r="C12" s="52"/>
+      <c r="D12" s="72" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="74"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1713,240 +1707,240 @@
       <c r="Q13" s="10"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="89"/>
-      <c r="P14" s="89"/>
-      <c r="Q14" s="89"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="89"/>
-      <c r="T14" s="89"/>
-      <c r="U14" s="89"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="89"/>
-      <c r="X14" s="89"/>
-      <c r="Y14" s="89"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
     </row>
     <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="43" t="s">
+      <c r="D15" s="82"/>
+      <c r="E15" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="66" t="s">
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="66"/>
-      <c r="M15" s="43" t="s">
+      <c r="L15" s="87"/>
+      <c r="M15" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="N15" s="43" t="s">
+      <c r="N15" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43" t="s">
+      <c r="O15" s="44"/>
+      <c r="P15" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="Q15" s="43" t="s">
+      <c r="Q15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43" t="s">
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="V15" s="43" t="s">
+      <c r="V15" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
     </row>
     <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="82"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="82"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44" t="s">
+      <c r="B17" s="51"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44" t="s">
+      <c r="R17" s="45"/>
+      <c r="S17" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="44"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="44" t="s">
+      <c r="T17" s="45"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="44"/>
-      <c r="X17" s="44" t="s">
+      <c r="W17" s="45"/>
+      <c r="X17" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="Y17" s="44"/>
+      <c r="Y17" s="45"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="65" t="s">
+      <c r="D18" s="83"/>
+      <c r="E18" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42" t="s">
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="42"/>
-      <c r="M18" s="39" t="s">
+      <c r="L18" s="47"/>
+      <c r="M18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="42" t="s">
+      <c r="N18" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="O18" s="42"/>
-      <c r="P18" s="40" t="s">
+      <c r="O18" s="47"/>
+      <c r="P18" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="Q18" s="41" t="s">
+      <c r="Q18" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="R18" s="41"/>
-      <c r="S18" s="88" t="s">
+      <c r="R18" s="84"/>
+      <c r="S18" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="88"/>
-      <c r="U18" s="39" t="s">
+      <c r="T18" s="48"/>
+      <c r="U18" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="87" t="s">
+      <c r="V18" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="W18" s="87"/>
-      <c r="X18" s="42"/>
-      <c r="Y18" s="42"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="47"/>
+      <c r="Y18" s="47"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
       <c r="U19" s="16"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="87"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="47"/>
+      <c r="Y20" s="47"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
@@ -1967,149 +1961,149 @@
       <c r="Q21" s="10"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="86"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="86"/>
     </row>
     <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43" t="s">
+      <c r="D23" s="44"/>
+      <c r="E23" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="43" t="s">
+      <c r="G23" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="43" t="s">
+      <c r="H23" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43" t="s">
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43" t="s">
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="P23" s="43"/>
+      <c r="P23" s="44"/>
     </row>
     <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="82"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="82"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="42"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="48" t="s">
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48" t="s">
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="P26" s="48"/>
+      <c r="P26" s="43"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="17"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
       <c r="Q28" s="10"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.25">
@@ -2130,26 +2124,26 @@
       <c r="Q29" s="10"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
       <c r="G30" s="19"/>
       <c r="I30" s="32" t="s">
         <v>92</v>
       </c>
       <c r="J30" s="33"/>
-      <c r="K30" s="70" t="s">
+      <c r="K30" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="70"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
@@ -2157,19 +2151,19 @@
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
       <c r="G31" s="10"/>
-      <c r="I31" s="72" t="s">
+      <c r="I31" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="J31" s="73"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
@@ -2177,19 +2171,19 @@
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
       <c r="G32" s="10"/>
-      <c r="I32" s="72" t="s">
+      <c r="I32" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="J32" s="73"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
@@ -2202,16 +2196,16 @@
         <v>99</v>
       </c>
       <c r="G33" s="10"/>
-      <c r="I33" s="35" t="s">
+      <c r="I33" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="36"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -2224,16 +2218,16 @@
         <v>99</v>
       </c>
       <c r="G34" s="10"/>
-      <c r="I34" s="37" t="s">
+      <c r="I34" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="80"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
@@ -2272,14 +2266,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="67" t="s">
+      <c r="B37" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2292,18 +2286,18 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="74"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -2312,16 +2306,16 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="74"/>
-      <c r="K39" s="74"/>
+      <c r="J39" s="66"/>
+      <c r="K39" s="66"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -2330,16 +2324,16 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="74"/>
-      <c r="K40" s="74"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -2348,16 +2342,16 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
       <c r="H41" s="27"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="74"/>
-      <c r="K41" s="74"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2366,12 +2360,12 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
       <c r="H42" s="10"/>
       <c r="L42" s="28" t="s">
         <v>105</v>
@@ -2420,7 +2414,88 @@
       <c r="Q44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="105">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D25"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E15:G17"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="N15:O17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="Q15:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="B14:Y14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="B38:G42"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="J38:K41"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="O23:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="K15:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="N20:O20"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I11:J11"/>
@@ -2445,86 +2520,6 @@
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E23:E25"/>
     <mergeCell ref="F23:F25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G42"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="J38:K41"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C23:D25"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E15:G17"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="N15:O17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="Q15:T16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="B14:Y14"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="B22:P22"/>
-    <mergeCell ref="O23:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="K15:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="N20:O20"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2966,7 +2961,7 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="39"/>
+      <c r="C31" s="37"/>
       <c r="E31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -2979,7 +2974,7 @@
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="39"/>
+      <c r="C32" s="37"/>
       <c r="E32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3243,29 +3238,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3462,25 +3434,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3497,4 +3474,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04E3D32-2D67-4ED3-B5D9-2D9C06DF910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBCEEE5-133E-43D4-9BBC-A63B0C795C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="117">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -754,6 +754,135 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -766,140 +895,11 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1439,25 +1439,25 @@
       <c r="B3" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="75" t="str">
+      <c r="K3" s="39" t="str">
         <f>Settings!A11</f>
         <v>${offerValidation.SELLINGCOMPANY}</v>
       </c>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -1466,23 +1466,23 @@
       <c r="B4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="69" t="str">
+      <c r="C4" s="40" t="str">
         <f>Settings!A13</f>
         <v>${offerValidation.DISTRIBUTORADDRESS}</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
       <c r="J4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="76"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="78"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="45"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1524,160 +1524,160 @@
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="80"/>
-      <c r="Q7" s="80"/>
-      <c r="R7" s="80"/>
-      <c r="S7" s="81"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="49"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="39" t="s">
+      <c r="C8" s="46"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="56"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="68"/>
       <c r="O8" s="29" t="s">
         <v>69</v>
       </c>
       <c r="P8" s="30"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="69" t="str">
+      <c r="C9" s="46"/>
+      <c r="D9" s="40" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="41" t="s">
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="57" t="s">
+      <c r="J9" s="85"/>
+      <c r="K9" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
       <c r="O9" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P9" s="30"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="69" t="str">
+      <c r="C10" s="46"/>
+      <c r="D10" s="40" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="67" t="s">
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="68"/>
-      <c r="K10" s="57" t="s">
+      <c r="J10" s="73"/>
+      <c r="K10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
       <c r="O10" s="29" t="s">
         <v>74</v>
       </c>
       <c r="P10" s="30"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
     </row>
     <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="72" t="str">
+      <c r="C11" s="46"/>
+      <c r="D11" s="74" t="str">
         <f>Settings!A12</f>
         <v>${offerValidation.DISTRIBUTORNAME}</v>
       </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="39" t="s">
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="40"/>
-      <c r="K11" s="53" t="str">
+      <c r="J11" s="83"/>
+      <c r="K11" s="81" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="81"/>
       <c r="O11" s="29" t="s">
         <v>72</v>
       </c>
       <c r="P11" s="30"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="72" t="str">
+      <c r="C12" s="46"/>
+      <c r="D12" s="74" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="76"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1707,240 +1707,244 @@
       <c r="Q13" s="10"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="85"/>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="85"/>
-      <c r="R14" s="85"/>
-      <c r="S14" s="85"/>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="85"/>
-      <c r="W14" s="85"/>
-      <c r="X14" s="85"/>
-      <c r="Y14" s="85"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
     </row>
     <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="44" t="s">
+      <c r="D15" s="52"/>
+      <c r="E15" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="87" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="87"/>
-      <c r="M15" s="44" t="s">
+      <c r="L15" s="78"/>
+      <c r="M15" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="N15" s="44" t="s">
+      <c r="N15" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44" t="s">
+      <c r="O15" s="51"/>
+      <c r="P15" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="Q15" s="44" t="s">
+      <c r="Q15" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44" t="s">
+      <c r="R15" s="51"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="51"/>
+      <c r="U15" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="V15" s="44" t="s">
+      <c r="V15" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
+      <c r="W15" s="51"/>
+      <c r="X15" s="51"/>
+      <c r="Y15" s="51"/>
     </row>
     <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="51"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="44"/>
-      <c r="U16" s="44"/>
-      <c r="V16" s="44"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="44"/>
-      <c r="Y16" s="44"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="51"/>
+      <c r="S16" s="51"/>
+      <c r="T16" s="51"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="51"/>
+      <c r="W16" s="51"/>
+      <c r="X16" s="51"/>
+      <c r="Y16" s="51"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="51"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45" t="s">
+      <c r="B17" s="80"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45" t="s">
+      <c r="R17" s="56"/>
+      <c r="S17" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="45"/>
-      <c r="U17" s="44"/>
-      <c r="V17" s="45" t="s">
+      <c r="T17" s="56"/>
+      <c r="U17" s="51"/>
+      <c r="V17" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="45"/>
-      <c r="X17" s="45" t="s">
+      <c r="W17" s="56"/>
+      <c r="X17" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="Y17" s="45"/>
+      <c r="Y17" s="56"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="83" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="47" t="s">
+      <c r="C18" s="53" t="str">
+        <f>IF(Settings!A18="","",Settings!A18)</f>
+        <v>${table:offerProductValidation.SKU}</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54" t="str">
+        <f>IF(Settings!B18="","",Settings!B18)</f>
+        <v>${table:offerProductValidation.PRODUCTNAME}</v>
+      </c>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="50" t="str">
+        <f>IF(Settings!C18="","",Settings!C18)</f>
+        <v>${table:offerProductValidation.PAID_VOLUME}</v>
+      </c>
+      <c r="L18" s="50"/>
+      <c r="M18" s="37" t="str">
+        <f>IF(Settings!D18="","",Settings!D18)</f>
+        <v>${table:offerProductValidation.UNIT}</v>
+      </c>
+      <c r="N18" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="O18" s="47"/>
+      <c r="O18" s="50"/>
       <c r="P18" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="Q18" s="84" t="s">
+      <c r="Q18" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="R18" s="84"/>
-      <c r="S18" s="48" t="s">
+      <c r="R18" s="55"/>
+      <c r="S18" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="48"/>
+      <c r="T18" s="87"/>
       <c r="U18" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="46" t="s">
+      <c r="V18" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="W18" s="46"/>
-      <c r="X18" s="47"/>
-      <c r="Y18" s="47"/>
+      <c r="W18" s="86"/>
+      <c r="X18" s="50"/>
+      <c r="Y18" s="50"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="84"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="55"/>
       <c r="M19" s="38"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
       <c r="P19" s="38"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="84"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
+      <c r="Q19" s="55"/>
+      <c r="R19" s="55"/>
+      <c r="S19" s="87"/>
+      <c r="T19" s="87"/>
       <c r="U19" s="16"/>
-      <c r="V19" s="46"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
+      <c r="V19" s="86"/>
+      <c r="W19" s="86"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="50"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
       <c r="M20" s="38"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
       <c r="P20" s="38"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
+      <c r="Q20" s="55"/>
+      <c r="R20" s="55"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="87"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="46"/>
-      <c r="W20" s="46"/>
-      <c r="X20" s="47"/>
-      <c r="Y20" s="47"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
@@ -1961,149 +1965,149 @@
       <c r="Q21" s="10"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="86"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="86"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="77"/>
+      <c r="P22" s="77"/>
     </row>
     <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44" t="s">
+      <c r="D23" s="51"/>
+      <c r="E23" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44" t="s">
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44" t="s">
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="P23" s="44"/>
+      <c r="P23" s="51"/>
     </row>
     <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="51"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="44"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="51"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="51"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="51"/>
+      <c r="P25" s="51"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="47"/>
+      <c r="D26" s="50"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="43" t="s">
+      <c r="H26" s="79"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43" t="s">
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="P26" s="43"/>
+      <c r="P26" s="58"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="17"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
       <c r="Q28" s="10"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.25">
@@ -2124,26 +2128,26 @@
       <c r="Q29" s="10"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
       <c r="G30" s="19"/>
       <c r="I30" s="32" t="s">
         <v>92</v>
       </c>
       <c r="J30" s="33"/>
-      <c r="K30" s="62" t="s">
+      <c r="K30" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="L30" s="62"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="62"/>
-      <c r="P30" s="62"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
@@ -2151,19 +2155,19 @@
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
       <c r="G31" s="10"/>
-      <c r="I31" s="64" t="s">
+      <c r="I31" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="J31" s="65"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
@@ -2171,19 +2175,19 @@
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
       <c r="G32" s="10"/>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="J32" s="65"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
@@ -2196,16 +2200,16 @@
         <v>99</v>
       </c>
       <c r="G33" s="10"/>
-      <c r="I33" s="64" t="s">
+      <c r="I33" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="65"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="58"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -2222,12 +2226,12 @@
         <v>102</v>
       </c>
       <c r="J34" s="36"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="58"/>
-      <c r="O34" s="58"/>
-      <c r="P34" s="58"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="70"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
@@ -2266,14 +2270,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="59" t="s">
+      <c r="B37" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2286,18 +2290,18 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="66"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -2306,16 +2310,16 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="66"/>
-      <c r="K39" s="66"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -2324,16 +2328,16 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="60"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -2342,16 +2346,16 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="60"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
       <c r="H41" s="27"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2360,12 +2364,12 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
       <c r="H42" s="10"/>
       <c r="L42" s="28" t="s">
         <v>105</v>
@@ -2415,6 +2419,87 @@
     </row>
   </sheetData>
   <mergeCells count="105">
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="K23:N25"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="V15:Y16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="O23:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="K15:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="B38:G42"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="J38:K41"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="C4:G4"/>
@@ -2439,87 +2524,6 @@
     <mergeCell ref="S17:T17"/>
     <mergeCell ref="B14:Y14"/>
     <mergeCell ref="K26:N26"/>
-    <mergeCell ref="B38:G42"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="J38:K41"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B22:P22"/>
-    <mergeCell ref="O23:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="K15:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="K23:N25"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="V15:Y16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -3238,6 +3242,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3434,30 +3461,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3474,22 +3496,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBCEEE5-133E-43D4-9BBC-A63B0C795C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A4229B-28F4-4104-978F-EF4BEE8B5F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -725,7 +725,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -754,19 +753,127 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -775,9 +882,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -787,118 +891,16 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -983,7 +985,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>458098</xdr:colOff>
+      <xdr:colOff>458097</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>100462</xdr:rowOff>
     </xdr:to>
@@ -1027,15 +1029,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>52916</xdr:rowOff>
+      <xdr:colOff>603251</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>10717</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>65175</xdr:rowOff>
+      <xdr:colOff>582217</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>86342</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1058,7 +1060,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5831418" y="7101416"/>
+          <a:off x="6402918" y="7313083"/>
           <a:ext cx="1524132" cy="774259"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1415,6 +1417,7 @@
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="13" max="13" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:25" x14ac:dyDescent="0.25">
@@ -1436,53 +1439,53 @@
       <c r="Q2" s="10"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="39" t="str">
+      <c r="K3" s="77" t="str">
         <f>Settings!A11</f>
         <v>${offerValidation.SELLINGCOMPANY}</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="40" t="str">
+      <c r="C4" s="62" t="str">
         <f>Settings!A13</f>
         <v>${offerValidation.DISTRIBUTORADDRESS}</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="42"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
       <c r="H4" s="12"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="45"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="80"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1524,160 +1527,160 @@
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="49"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="83"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="82" t="s">
+      <c r="C8" s="51"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="83"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="29" t="s">
+      <c r="J8" s="39"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="40" t="str">
+      <c r="C9" s="51"/>
+      <c r="D9" s="62" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="84" t="s">
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="69" t="s">
+      <c r="J9" s="41"/>
+      <c r="K9" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="29" t="s">
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="40" t="str">
+      <c r="C10" s="51"/>
+      <c r="D10" s="62" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="72" t="s">
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="73"/>
-      <c r="K10" s="69" t="s">
+      <c r="J10" s="61"/>
+      <c r="K10" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="29" t="s">
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
     </row>
     <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="74" t="str">
+      <c r="C11" s="51"/>
+      <c r="D11" s="65" t="str">
         <f>Settings!A12</f>
         <v>${offerValidation.DISTRIBUTORNAME}</v>
       </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="82" t="s">
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="83"/>
-      <c r="K11" s="81" t="str">
+      <c r="J11" s="39"/>
+      <c r="K11" s="52" t="str">
         <f>Settings!A7</f>
         <v>${offerValidation.PAYMENTTERMS}</v>
       </c>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="29" t="s">
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="74" t="str">
+      <c r="C12" s="51"/>
+      <c r="D12" s="65" t="str">
         <f>Settings!A8</f>
         <v>${offerValidation.DELIVERYTERMS}</v>
       </c>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="76"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1707,244 +1710,240 @@
       <c r="Q13" s="10"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="57"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="57"/>
-      <c r="U14" s="57"/>
-      <c r="V14" s="57"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="57"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
     </row>
     <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="80" t="s">
+      <c r="B15" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="51" t="s">
+      <c r="D15" s="84"/>
+      <c r="E15" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="78" t="s">
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="78"/>
-      <c r="M15" s="51" t="s">
+      <c r="L15" s="69"/>
+      <c r="M15" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N15" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51" t="s">
+      <c r="O15" s="43"/>
+      <c r="P15" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="Q15" s="51" t="s">
+      <c r="Q15" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="51"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="51" t="s">
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="V15" s="51" t="s">
+      <c r="V15" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="43"/>
     </row>
     <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="80"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="51"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="80"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="56" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="R17" s="56"/>
-      <c r="S17" s="56" t="s">
+      <c r="R17" s="44"/>
+      <c r="S17" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="56"/>
-      <c r="U17" s="51"/>
-      <c r="V17" s="56" t="s">
+      <c r="T17" s="44"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="W17" s="56"/>
-      <c r="X17" s="56" t="s">
+      <c r="W17" s="44"/>
+      <c r="X17" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="Y17" s="56"/>
+      <c r="Y17" s="44"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="53" t="str">
-        <f>IF(Settings!A18="","",Settings!A18)</f>
-        <v>${table:offerProductValidation.SKU}</v>
-      </c>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54" t="str">
-        <f>IF(Settings!B18="","",Settings!B18)</f>
-        <v>${table:offerProductValidation.PRODUCTNAME}</v>
-      </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="50" t="str">
-        <f>IF(Settings!C18="","",Settings!C18)</f>
-        <v>${table:offerProductValidation.PAID_VOLUME}</v>
-      </c>
-      <c r="L18" s="50"/>
-      <c r="M18" s="37" t="str">
-        <f>IF(Settings!D18="","",Settings!D18)</f>
-        <v>${table:offerProductValidation.UNIT}</v>
-      </c>
-      <c r="N18" s="50" t="s">
+      <c r="C18" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="52"/>
+      <c r="E18" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="46"/>
+      <c r="M18" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="O18" s="50"/>
-      <c r="P18" s="38" t="s">
+      <c r="O18" s="46"/>
+      <c r="P18" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="Q18" s="55" t="s">
+      <c r="Q18" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="R18" s="55"/>
-      <c r="S18" s="87" t="s">
+      <c r="R18" s="53"/>
+      <c r="S18" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="87"/>
-      <c r="U18" s="37" t="s">
+      <c r="T18" s="47"/>
+      <c r="U18" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="86" t="s">
+      <c r="V18" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="W18" s="86"/>
-      <c r="X18" s="50"/>
-      <c r="Y18" s="50"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="46"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
       <c r="U19" s="16"/>
-      <c r="V19" s="86"/>
-      <c r="W19" s="86"/>
-      <c r="X19" s="50"/>
-      <c r="Y19" s="50"/>
+      <c r="V19" s="45"/>
+      <c r="W19" s="45"/>
+      <c r="X19" s="46"/>
+      <c r="Y19" s="46"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="86"/>
-      <c r="W20" s="86"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
+      <c r="V20" s="45"/>
+      <c r="W20" s="45"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
@@ -1965,149 +1964,149 @@
       <c r="Q21" s="10"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="77" t="s">
+      <c r="B22" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="77"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="68"/>
     </row>
     <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51" t="s">
+      <c r="D23" s="43"/>
+      <c r="E23" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51" t="s">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51" t="s">
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="P23" s="51"/>
+      <c r="P23" s="43"/>
     </row>
     <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="80"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="80"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="50"/>
+      <c r="D26" s="46"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="58" t="s">
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58" t="s">
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="P26" s="58"/>
+      <c r="P26" s="42"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="17"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
       <c r="Q28" s="10"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.25">
@@ -2128,26 +2127,26 @@
       <c r="Q29" s="10"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
       <c r="G30" s="19"/>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="J30" s="33"/>
-      <c r="K30" s="61" t="s">
+      <c r="J30" s="32"/>
+      <c r="K30" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
@@ -2155,19 +2154,19 @@
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
       <c r="G31" s="10"/>
-      <c r="I31" s="63" t="s">
+      <c r="I31" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="J31" s="64"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
@@ -2175,19 +2174,19 @@
       </c>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
       <c r="G32" s="10"/>
-      <c r="I32" s="63" t="s">
+      <c r="I32" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="J32" s="64"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
@@ -2200,16 +2199,16 @@
         <v>99</v>
       </c>
       <c r="G33" s="10"/>
-      <c r="I33" s="63" t="s">
+      <c r="I33" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="64"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="58"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -2222,16 +2221,16 @@
         <v>99</v>
       </c>
       <c r="G34" s="10"/>
-      <c r="I34" s="35" t="s">
+      <c r="I34" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="J34" s="36"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
@@ -2270,14 +2269,14 @@
       <c r="Q36" s="10"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="71" t="s">
+      <c r="B37" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2290,18 +2289,18 @@
       <c r="Q37" s="10"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -2310,16 +2309,16 @@
       <c r="Q38" s="10"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -2328,16 +2327,16 @@
       <c r="Q39" s="10"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
+      <c r="J40" s="76"/>
+      <c r="K40" s="76"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -2346,16 +2345,16 @@
       <c r="Q40" s="10"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
       <c r="H41" s="27"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2364,17 +2363,17 @@
       <c r="Q41" s="10"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
       <c r="H42" s="10"/>
-      <c r="L42" s="28" t="s">
+      <c r="L42" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="M42" s="10"/>
+      <c r="M42" s="87"/>
       <c r="N42" s="10" t="s">
         <v>106</v>
       </c>
@@ -2418,7 +2417,89 @@
       <c r="Q44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="106">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D25"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E15:G17"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="N15:O17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="Q15:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="B14:Y14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="B38:G42"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="J38:K41"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="O23:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="K15:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H23:J25"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="N20:O20"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I11:J11"/>
@@ -2443,87 +2524,6 @@
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E23:E25"/>
     <mergeCell ref="F23:F25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B22:P22"/>
-    <mergeCell ref="O23:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="K15:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="B38:G42"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="J38:K41"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C23:D25"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E15:G17"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="N15:O17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="Q15:T16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="B14:Y14"/>
-    <mergeCell ref="K26:N26"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2680,7 +2680,7 @@
       <c r="B14" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2965,7 +2965,7 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="37"/>
+      <c r="C31" s="36"/>
       <c r="E31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -2978,7 +2978,7 @@
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="37"/>
+      <c r="C32" s="36"/>
       <c r="E32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3242,29 +3242,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3461,25 +3438,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3496,4 +3478,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Desktop\Thailand Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A4229B-28F4-4104-978F-EF4BEE8B5F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36469226-B408-44E2-8967-0597E3B00D5F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>${offerValidation.SHIPMENTTERMS}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PRODUCT_UNIT_NAME}</t>
   </si>
   <si>
     <t>${table:offerProductValidation.SKU}</t>
@@ -284,6 +287,9 @@
 Discount</t>
   </si>
   <si>
+    <t>Total Offer Value</t>
+  </si>
+  <si>
     <t>excl. vat.</t>
   </si>
   <si>
@@ -351,9 +357,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>With reference to the above tender, you must not on-sell the above mentioned products at a price higher than those listed above. However, you are always free to sell at a price lower, at your discretion.</t>
-  </si>
-  <si>
     <t>Approved by</t>
   </si>
   <si>
@@ -363,33 +366,56 @@
     <t>Position</t>
   </si>
   <si>
+    <t>${offerValidation.DISTRIBUTORNAME}</t>
+  </si>
+  <si>
     <t>${offerValidation.SELLINGCOMPANY}</t>
   </si>
   <si>
-    <t>${offerValidation.DISTRIBUTORNAME}</t>
-  </si>
-  <si>
     <t>${offerValidation.DISTRIBUTORADDRESS}</t>
   </si>
   <si>
+    <t>${offerValidation.CUSTOMER_CODE}</t>
+  </si>
+  <si>
     <t>${table:offerProductValidation.PRODUCTNAME}</t>
   </si>
   <si>
-    <t>${offerValidation.CUSTOMER_CODE}</t>
+    <t>UOM</t>
   </si>
   <si>
     <t xml:space="preserve">Offer QTY 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">
-UoM</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.DOSAGE}</t>
   </si>
   <si>
     <t>${table:offerProductValidation.MANUFACTURER}</t>
+  </si>
+  <si>
+    <t>${offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.NET_PRICE_PACK_OFFER_CURRENCY_VAT}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
+  </si>
+  <si>
+    <t>Net Price Pack Vat</t>
+  </si>
+  <si>
+    <t>Net Price Unit Vat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With reference to the above tender, you must not on-sell the above mentioned products at a price higher than those listed above. However, you are always free to sell at a price lower, at your discretion. </t>
+  </si>
+  <si>
+    <t>incl. vat.(Pack)</t>
+  </si>
+  <si>
+    <t>incl. vat.(Unit)</t>
   </si>
 </sst>
 </file>
@@ -501,7 +527,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,12 +538,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +553,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -641,6 +661,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -660,11 +693,66 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -674,7 +762,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -689,142 +777,304 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -834,73 +1084,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -910,6 +1100,24 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -943,24 +1151,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -978,14 +1168,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>482600</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>458097</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>309931</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>100462</xdr:rowOff>
     </xdr:to>
@@ -1026,75 +1216,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>603251</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>74083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>582217</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>86342</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAB78DC-B8BD-201A-CBFF-1F60D61D4715}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6402918" y="7313083"/>
-          <a:ext cx="1524132" cy="774259"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}" name="Tabel1" displayName="Tabel1" ref="A1:B14" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:B14" xr:uid="{5B6DC07E-0020-4B51-98A2-ADA62A91E75D}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{22EAB7A2-53F9-497F-A4B5-CA34E48AC441}" name="Header fields"/>
-    <tableColumn id="2" xr3:uid="{331DD14B-B263-41D9-B2C5-D198B6F2436E}" name="Description"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}" name="Tabel2" displayName="Tabel2" ref="C17:U52" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="C17:U52" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}" name="Tabel2" displayName="Tabel2" ref="C17:W52" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="C17:W52" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}"/>
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{6E1F8ECB-E862-46B4-998C-BE8E89C238BA}" name="PAID VOLUME"/>
     <tableColumn id="2" xr3:uid="{6497AF92-63C8-4790-818D-6E5BE819E8D6}" name="UNIT"/>
-    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{1CB5E955-18ED-4738-ACA1-E270D15916F8}" name="CURRENCY"/>
-    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{77EEA9FC-8FC3-433A-9592-47B0D8B4C67B}" name="OFFER_PRICE_VAT" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{38030720-EDB2-473C-9CF5-2E9C926DF088}" name="GROSS SALES OFFER CURRENCY" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{A1EAF0A4-B4D5-428E-9D86-C12164DF9888}" name="GROSS_SALES_OFFER_CURRENCY_VAT" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{06958303-4A18-40AA-8AD0-9A7EEFDCAF3E}" name="OFFER_ID"/>
     <tableColumn id="9" xr3:uid="{A1218AAF-0481-41A2-9C10-3038D1BF8C7D}" name="SORTER"/>
     <tableColumn id="10" xr3:uid="{5A7FFAC3-1C22-44BF-8C52-F3578967B0F3}" name="Pack Factor"/>
@@ -1102,15 +1237,28 @@
     <tableColumn id="12" xr3:uid="{4A42B0A1-255A-4E7E-955E-674BA8AAA444}" name="Origin"/>
     <tableColumn id="13" xr3:uid="{7D1379AA-4B8F-4BC6-9726-365EBAE15341}" name="FOC"/>
     <tableColumn id="14" xr3:uid="{DF88A36E-0423-48FC-A1FC-B18BF3BA8D1A}" name="Total Quantity Units"/>
-    <tableColumn id="15" xr3:uid="{6B128E87-63EB-483B-88D7-EA33600F43AB}" name="Total QTY" dataDxfId="0">
+    <tableColumn id="15" xr3:uid="{6B128E87-63EB-483B-88D7-EA33600F43AB}" name="Total QTY" dataDxfId="1">
       <calculatedColumnFormula>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{E4D044B6-D053-487A-AA8C-F40FE34F30A7}" name="Net Price"/>
-    <tableColumn id="17" xr3:uid="{F95E93A8-C80D-4AC7-9526-72374F546CE7}" name="Amount in numbers"/>
-    <tableColumn id="18" xr3:uid="{2DDE85E8-6C8E-4D93-A4E8-1F80D965246B}" name="VAT total"/>
-    <tableColumn id="19" xr3:uid="{F55B5874-4E65-4E44-AEFE-7CFF114E939A}" name="Amount in numbers vat"/>
+    <tableColumn id="17" xr3:uid="{F95E93A8-C80D-4AC7-9526-72374F546CE7}" name="Net Price Pack Vat"/>
+    <tableColumn id="18" xr3:uid="{2DDE85E8-6C8E-4D93-A4E8-1F80D965246B}" name="Net Price Unit Vat"/>
+    <tableColumn id="20" xr3:uid="{CB417A4B-91CA-49CD-9B3D-699005D44488}" name="Amount in numbers"/>
+    <tableColumn id="21" xr3:uid="{07B28F29-5FC9-406A-96FC-77FFBFB88A05}" name="VAT total"/>
+    <tableColumn id="22" xr3:uid="{275B8D63-D363-4D68-BC9C-CB91FD9D0201}" name="Amount in numbers vat"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{13195211-A053-4079-8580-181B8695617E}" name="Tabel14" displayName="Tabel14" ref="A1:B15" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:B15" xr:uid="{13195211-A053-4079-8580-181B8695617E}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{04053350-A8BA-4F7A-9272-32CAE894E561}" name="Header fields"/>
+    <tableColumn id="2" xr3:uid="{91B26FA0-9378-480D-8354-6037F7FF582C}" name="Description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1411,16 +1559,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
-  <dimension ref="B2:Y44"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B2:Q55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="13" max="13" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1436,79 +1598,73 @@
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-    </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="77" t="s">
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="77" t="str">
-        <f>Settings!A11</f>
-        <v>${offerValidation.SELLINGCOMPANY}</v>
-      </c>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-    </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="62" t="str">
-        <f>Settings!A13</f>
-        <v>${offerValidation.DISTRIBUTORADDRESS}</v>
-      </c>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="78"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="80"/>
+    </row>
+    <row r="4" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="62" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-    </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="63"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="13"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1524,163 +1680,143 @@
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="83"/>
-    </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="125"/>
+    </row>
+    <row r="8" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="28" t="s">
+      <c r="C8" s="52"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-    </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="H8" s="68"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="114"/>
+      <c r="N8" s="105"/>
+      <c r="O8" s="106"/>
+      <c r="P8" s="32"/>
+    </row>
+    <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="62" t="str">
+        <v>71</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="120" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="57" t="s">
+      <c r="E9" s="121"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="70"/>
+      <c r="I9" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-    </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="J9" s="111"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="113" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="114"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="32"/>
+    </row>
+    <row r="10" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="62" t="str">
+        <v>74</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="120" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="60" t="s">
+      <c r="E10" s="121"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="57" t="s">
+      <c r="H10" s="72"/>
+      <c r="I10" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-    </row>
-    <row r="11" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="111"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" s="114"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="32"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="65" t="str">
-        <f>Settings!A12</f>
-        <v>${offerValidation.DISTRIBUTORNAME}</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="38" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="52" t="str">
-        <f>Settings!A7</f>
-        <v>${offerValidation.PAYMENTTERMS}</v>
-      </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="H11" s="68"/>
+      <c r="I11" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="65"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="113" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="114"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="32"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="65" t="str">
-        <f>Settings!A8</f>
-        <v>${offerValidation.DELIVERYTERMS}</v>
-      </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="67"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1688,10 +1824,8 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1707,245 +1841,204 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="85" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="85"/>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="85"/>
-      <c r="R14" s="85"/>
-      <c r="S14" s="85"/>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="85"/>
-      <c r="W14" s="85"/>
-      <c r="X14" s="85"/>
-      <c r="Y14" s="85"/>
-    </row>
-    <row r="15" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="50" t="s">
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="59"/>
+    </row>
+    <row r="15" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="43" t="s">
+      <c r="C15" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43" t="s">
+      <c r="D15" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="69" t="s">
+      <c r="E15" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="77"/>
+      <c r="L15" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15" s="48"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="85"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="50"/>
+    </row>
+    <row r="17" spans="2:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="86"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="75"/>
+      <c r="M17" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="69"/>
-      <c r="M15" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="N15" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="V15" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-    </row>
-    <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="50"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="50"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="T17" s="44"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="W17" s="44"/>
-      <c r="X17" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y17" s="44"/>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="86" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="46" t="s">
+      <c r="E18" s="119"/>
+      <c r="F18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="46"/>
-      <c r="M18" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="46"/>
-      <c r="P18" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q18" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="R18" s="53"/>
-      <c r="S18" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" s="47"/>
-      <c r="U18" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="V18" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="W18" s="45"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="46"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="M18" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="O18" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="P18" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="46"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="20"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="47"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="45"/>
-      <c r="W20" s="45"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="20"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -1961,285 +2054,258 @@
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="68"/>
-    </row>
-    <row r="23" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="43" t="s">
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="43" t="s">
+      <c r="C23" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="43" t="s">
+      <c r="E23" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43" t="s">
+      <c r="F23" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43" t="s">
+      <c r="G23" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="P23" s="43"/>
-    </row>
-    <row r="24" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="50"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="50"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="42"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B27" s="17"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="10"/>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24" s="87"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="105" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="106"/>
+      <c r="L25" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="10"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="92"/>
+      <c r="I29" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="19"/>
-      <c r="I30" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="72" t="s">
-        <v>93</v>
-      </c>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B31" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="10"/>
-      <c r="I31" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="J31" s="75"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B32" s="20" t="s">
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B30" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="21"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="96"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B31" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="96"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B32" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="25"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="10"/>
-      <c r="I32" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J32" s="75"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="21"/>
+      <c r="E32" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="96"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="99"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="28"/>
       <c r="D33" s="21"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="I33" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="J33" s="75"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
+      <c r="E33" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="I34" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="J34" s="35"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="58"/>
-      <c r="O34" s="58"/>
-      <c r="P34" s="58"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="26"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="103" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="104"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="55"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="10"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -2247,303 +2313,376 @@
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
       <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="10"/>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
+      <c r="P35" s="10"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="22"/>
       <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
       <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
       <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="70" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
       <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="101"/>
+      <c r="F40" s="102"/>
+      <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="76"/>
-      <c r="K40" s="76"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="27"/>
+    </row>
+    <row r="41" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="10"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
       <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="117"/>
       <c r="H42" s="10"/>
-      <c r="L42" s="87" t="s">
-        <v>105</v>
-      </c>
-      <c r="M42" s="87"/>
-      <c r="N42" s="10" t="s">
-        <v>106</v>
-      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="10"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K43" s="10"/>
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
-      <c r="N43" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="N43" s="10"/>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="117"/>
       <c r="H44" s="10"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="10"/>
+      <c r="I44" s="10" t="s">
+        <v>108</v>
+      </c>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="117"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="117"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="117"/>
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="117"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="117"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="117"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="117"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="117"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="117"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="117"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="117"/>
+      <c r="C55" s="117"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="117"/>
+      <c r="G55" s="117"/>
     </row>
   </sheetData>
-  <mergeCells count="106">
+  <mergeCells count="72">
+    <mergeCell ref="B7:O7"/>
+    <mergeCell ref="B41:F45"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:I24"/>
+    <mergeCell ref="J23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="J15:K16"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="M15:O16"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="C4:G5"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:S7"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C23:D25"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E15:G17"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="N15:O17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="Q15:T16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="B14:Y14"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="B38:G42"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="J38:K41"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B22:P22"/>
-    <mergeCell ref="O23:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="K15:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H23:J25"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="Q17:R17"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="K23:N25"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="V15:Y16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="I11:K11"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E28" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D27" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
       <formula1>"กล่อง, เม็ด, ไวอัล, แอมพูล, ขวด, box, tablet, vial, ampoul, bottle"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33:F34" xr:uid="{2CF9FB64-438B-485F-A115-633E3AF0704D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E32:E33" xr:uid="{2CF9FB64-438B-485F-A115-633E3AF0704D}">
       <formula1>"Days (วัน), Months (เดือน), Years (ปี)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BADA0-6CEF-4001-8243-A13FFD1BF3BE}">
-  <dimension ref="A1:U52"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
@@ -2567,17 +2706,19 @@
     <col min="19" max="19" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.42578125" customWidth="1"/>
+    <col min="23" max="23" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2585,7 +2726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2593,7 +2734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2601,7 +2742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2609,7 +2750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2617,7 +2758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2625,7 +2766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2633,7 +2774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2641,85 +2782,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="33"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>9</v>
@@ -2734,91 +2882,103 @@
         <v>13</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
         <v>27</v>
       </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" t="s">
-        <v>24</v>
-      </c>
-      <c r="N18" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" t="s">
-        <v>26</v>
-      </c>
       <c r="P18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q18" t="e">
         <f>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
       <c r="R18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S18" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="T18" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="U18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="V18" t="s">
+        <v>62</v>
+      </c>
+      <c r="W18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="E19" s="9"/>
@@ -2830,7 +2990,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
       <c r="E20" s="9"/>
@@ -2842,7 +3002,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
       <c r="E21" s="9"/>
@@ -2854,7 +3014,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
       <c r="E22" s="9"/>
@@ -2866,7 +3026,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
       <c r="E23" s="9"/>
@@ -2878,7 +3038,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
       <c r="E24" s="9"/>
@@ -2890,7 +3050,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
       <c r="E25" s="9"/>
@@ -2902,7 +3062,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="E26" s="9"/>
@@ -2914,7 +3074,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="E27" s="9"/>
@@ -2926,7 +3086,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="E28" s="9"/>
@@ -2938,7 +3098,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="E29" s="9"/>
@@ -2950,7 +3110,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="E30" s="9"/>
@@ -2962,10 +3122,9 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="36"/>
       <c r="E31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -2975,10 +3134,9 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="36"/>
       <c r="E32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3242,6 +3400,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3438,15 +3605,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3462,6 +3620,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3480,14 +3646,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36469226-B408-44E2-8967-0597E3B00D5F}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38EBB158-6A26-4525-A2B7-A4618BC97DB9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -762,7 +762,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -774,9 +774,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -810,12 +807,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -830,11 +821,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -847,18 +870,116 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -868,172 +989,94 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1044,54 +1087,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1217,6 +1212,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1560,7 +1559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:Q55"/>
+  <dimension ref="B2:S50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1600,32 +1599,32 @@
       <c r="P2" s="10"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="H3" s="10"/>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="56"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="60" t="s">
@@ -1636,30 +1635,30 @@
       <c r="F4" s="60"/>
       <c r="G4" s="60"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="58"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="59"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="63"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="10"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -1682,139 +1681,139 @@
       <c r="P6" s="10"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="123" t="s">
+      <c r="B7" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="125"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="114"/>
     </row>
     <row r="8" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="51" t="s">
+      <c r="C8" s="81"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="113" t="s">
+      <c r="H8" s="75"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="114"/>
-      <c r="N8" s="105"/>
-      <c r="O8" s="106"/>
-      <c r="P8" s="32"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="29"/>
     </row>
     <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="120" t="str">
+      <c r="C9" s="81"/>
+      <c r="D9" s="117" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="121"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="69" t="s">
+      <c r="E9" s="118"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="70"/>
-      <c r="I9" s="110" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="113" t="s">
+      <c r="J9" s="110"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="M9" s="114"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="32"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="29"/>
     </row>
     <row r="10" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="120" t="str">
+      <c r="C10" s="81"/>
+      <c r="D10" s="117" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="121"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="71" t="s">
+      <c r="E10" s="118"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="72"/>
-      <c r="I10" s="110" t="s">
+      <c r="H10" s="79"/>
+      <c r="I10" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="111"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="113" t="s">
+      <c r="J10" s="110"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="114"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="32"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="29"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="97" t="s">
+      <c r="C11" s="81"/>
+      <c r="D11" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="51" t="s">
+      <c r="E11" s="107"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="68"/>
-      <c r="I11" s="64" t="s">
+      <c r="H11" s="75"/>
+      <c r="I11" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="65"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="113" t="s">
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="M11" s="114"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="32"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="29"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="97" t="s">
+      <c r="C12" s="81"/>
+      <c r="D12" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="108"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -1843,202 +1842,204 @@
       <c r="P13" s="10"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
     </row>
     <row r="15" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="E15" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="73" t="s">
+      <c r="G15" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="33" t="s">
+      <c r="H15" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="73" t="s">
+      <c r="I15" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="76" t="s">
+      <c r="J15" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="77"/>
-      <c r="L15" s="73" t="s">
+      <c r="K15" s="89"/>
+      <c r="L15" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="76" t="s">
+      <c r="M15" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="47" t="s">
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="Q15" s="48"/>
+      <c r="Q15" s="39"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="85"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
-    </row>
-    <row r="17" spans="2:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="86"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="14" t="s">
+      <c r="B16" s="83"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+    </row>
+    <row r="17" spans="2:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="84"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="75"/>
-      <c r="M17" s="14" t="s">
+      <c r="L17" s="64"/>
+      <c r="M17" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="O17" s="14" t="s">
+      <c r="O17" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="P17" s="14" t="s">
+      <c r="P17" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="Q17" s="14" t="s">
+      <c r="Q17" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
+    <row r="18" spans="2:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="119"/>
-      <c r="F18" s="16" t="s">
+      <c r="E18" s="43"/>
+      <c r="F18" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="41" t="s">
+      <c r="H18" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="43" t="s">
+      <c r="K18" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="41" t="s">
+      <c r="L18" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="42" t="s">
+      <c r="M18" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N18" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="O18" s="36" t="s">
+      <c r="O18" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="P18" s="45" t="s">
+      <c r="P18" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="Q18" s="18" t="s">
+      <c r="Q18" s="53" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="20"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="20"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="19"/>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="19"/>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -2055,124 +2056,124 @@
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="59" t="s">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
       <c r="M22" s="10"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="87" t="s">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="73" t="s">
+      <c r="E23" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="73" t="s">
+      <c r="F23" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67" t="s">
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67" t="s">
+      <c r="K23" s="88"/>
+      <c r="L23" s="88" t="s">
         <v>92</v>
       </c>
       <c r="M23" s="10"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="87"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="67"/>
-      <c r="L24" s="67"/>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B24" s="85"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
       <c r="M24" s="10"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="116"/>
-      <c r="J25" s="105" t="s">
+      <c r="D25" s="34"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="K25" s="106"/>
-      <c r="L25" s="21" t="s">
+      <c r="K25" s="70"/>
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="10"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="94"/>
-      <c r="L26" s="21"/>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="20"/>
       <c r="M26" s="10"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="21"/>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="20"/>
       <c r="M27" s="10"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="22"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="22"/>
+      <c r="H28" s="21"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
@@ -2182,199 +2183,208 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="90" t="s">
+    <row r="29" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="91" t="s">
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="92"/>
-      <c r="I29" s="44" t="s">
+      <c r="H29" s="99"/>
+      <c r="I29" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="95" t="s">
+      <c r="G30" s="102" t="s">
         <v>97</v>
       </c>
-      <c r="H30" s="96"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="99"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="108"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B31" s="24" t="s">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
       <c r="F31" s="10"/>
-      <c r="G31" s="95" t="s">
+      <c r="G31" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="96"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="99"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="108"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B32" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="26" t="s">
+      <c r="C32" s="24"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="25" t="s">
         <v>101</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="95" t="s">
+      <c r="G32" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="H32" s="96"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="99"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="108"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="26" t="s">
+      <c r="C33" s="27"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="25" t="s">
         <v>101</v>
       </c>
       <c r="F33" s="10"/>
-      <c r="G33" s="103" t="s">
+      <c r="G33" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="H33" s="104"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="55"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="56"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="22"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
+      <c r="B35" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
       <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
+    <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="115" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
+      <c r="B37" s="116"/>
+      <c r="C37" s="116"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
+      <c r="B38" s="116"/>
+      <c r="C38" s="116"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="B39" s="116"/>
+      <c r="C39" s="116"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="42"/>
       <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="I39" s="10" t="s">
+        <v>108</v>
+      </c>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
@@ -2383,17 +2393,14 @@
       <c r="P39" s="10"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="100" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="101"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="101"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="10"/>
+      <c r="B40" s="116"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="42"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
@@ -2401,19 +2408,14 @@
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="118" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="K41" s="21"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2421,16 +2423,16 @@
       <c r="P41" s="10"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="10"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="21"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
+      <c r="K42" s="21"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
@@ -2438,159 +2440,74 @@
       <c r="P42" s="10"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="117"/>
-      <c r="H43" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="117"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B46" s="117"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="117"/>
-      <c r="G46" s="117"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="117"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="117"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117"/>
-      <c r="K48" s="10"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="117"/>
-      <c r="C49" s="117"/>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="117"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="117"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="117"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="117"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="117"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="117"/>
-      <c r="E52" s="117"/>
-      <c r="F52" s="117"/>
-      <c r="G52" s="117"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="117"/>
-      <c r="C53" s="117"/>
-      <c r="D53" s="117"/>
-      <c r="E53" s="117"/>
-      <c r="F53" s="117"/>
-      <c r="G53" s="117"/>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="117"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="117"/>
-      <c r="F54" s="117"/>
-      <c r="G54" s="117"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="117"/>
-      <c r="C55" s="117"/>
-      <c r="D55" s="117"/>
-      <c r="E55" s="117"/>
-      <c r="F55" s="117"/>
-      <c r="G55" s="117"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="72">
     <mergeCell ref="B7:O7"/>
-    <mergeCell ref="B41:F45"/>
+    <mergeCell ref="B36:F40"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D9:F9"/>
@@ -2615,7 +2532,7 @@
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="I30:L30"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B35:F35"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="G29:H29"/>
@@ -2636,11 +2553,6 @@
     <mergeCell ref="G23:I24"/>
     <mergeCell ref="J23:K24"/>
     <mergeCell ref="L23:L24"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B14:Q14"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="L15:L17"/>
     <mergeCell ref="J15:K16"/>
@@ -2650,17 +2562,22 @@
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="N10:O10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B14:Q14"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="I11:K11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D27" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2671,7 +2588,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
@@ -2826,7 +2743,7 @@
       <c r="A15" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="37" t="s">
         <v>85</v>
       </c>
     </row>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38EBB158-6A26-4525-A2B7-A4618BC97DB9}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5C23729-F91F-43E4-9E3D-5496BB18429B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -388,9 +388,6 @@
 </t>
   </si>
   <si>
-    <t>${table:offerProductValidation.DOSAGE}</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.MANUFACTURER}</t>
   </si>
   <si>
@@ -416,6 +413,9 @@
   </si>
   <si>
     <t>incl. vat.(Unit)</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PRESENTATION}</t>
   </si>
 </sst>
 </file>
@@ -875,6 +875,87 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -884,6 +965,114 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -898,195 +1087,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1602,57 +1602,57 @@
       <c r="B3" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
       <c r="H3" s="10"/>
       <c r="I3" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="J3" s="81" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="56"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="83"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
       <c r="H4" s="10"/>
       <c r="I4" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="59"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="122"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
       <c r="H5" s="10"/>
       <c r="I5" s="11"/>
       <c r="J5" s="12"/>
@@ -1681,139 +1681,139 @@
       <c r="P6" s="10"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="113"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="113"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="113"/>
-      <c r="M7" s="113"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="114"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="56"/>
     </row>
     <row r="8" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="74" t="s">
+      <c r="C8" s="119"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="75"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="104" t="s">
+      <c r="H8" s="114"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="105"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="70"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="72"/>
       <c r="P8" s="29"/>
     </row>
     <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="117" t="str">
+      <c r="C9" s="119"/>
+      <c r="D9" s="62" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="76" t="s">
+      <c r="E9" s="63"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="77"/>
-      <c r="I9" s="109" t="s">
+      <c r="H9" s="116"/>
+      <c r="I9" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="110"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="104" t="s">
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="M9" s="105"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="70"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="72"/>
       <c r="P9" s="29"/>
     </row>
     <row r="10" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="113" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="117" t="str">
+      <c r="C10" s="119"/>
+      <c r="D10" s="62" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="118"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="78" t="s">
+      <c r="E10" s="63"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="109" t="s">
+      <c r="H10" s="118"/>
+      <c r="I10" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="110"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="104" t="s">
+      <c r="J10" s="77"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="105"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="70"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="72"/>
       <c r="P10" s="29"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="106" t="s">
+      <c r="C11" s="119"/>
+      <c r="D11" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="107"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="74" t="s">
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="75"/>
-      <c r="I11" s="71" t="s">
+      <c r="H11" s="114"/>
+      <c r="I11" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="104" t="s">
+      <c r="J11" s="111"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="M11" s="105"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="70"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="72"/>
       <c r="P11" s="29"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="106" t="s">
+      <c r="C12" s="119"/>
+      <c r="D12" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -1842,109 +1842,109 @@
       <c r="P13" s="10"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="98" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="80"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="98"/>
+      <c r="O14" s="98"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="98"/>
     </row>
     <row r="15" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="59" t="s">
         <v>114</v>
       </c>
       <c r="H15" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="65" t="s">
+      <c r="J15" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="89"/>
-      <c r="L15" s="62" t="s">
+      <c r="K15" s="104"/>
+      <c r="L15" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="65" t="s">
+      <c r="M15" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="107"/>
       <c r="P15" s="38" t="s">
         <v>83</v>
       </c>
       <c r="Q15" s="39"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="83"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="67"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
       <c r="P16" s="40"/>
       <c r="Q16" s="41"/>
     </row>
     <row r="17" spans="2:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="84"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
       <c r="H17" s="31"/>
-      <c r="I17" s="64"/>
+      <c r="I17" s="61"/>
       <c r="J17" s="13" t="s">
         <v>84</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="64"/>
+      <c r="L17" s="61"/>
       <c r="M17" s="13" t="s">
         <v>84</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P17" s="13" t="s">
         <v>84</v>
@@ -1974,7 +1974,7 @@
         <v>24</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J18" s="49" t="s">
         <v>32</v>
@@ -1989,10 +1989,10 @@
         <v>54</v>
       </c>
       <c r="N18" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O18" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P18" s="52" t="s">
         <v>56</v>
@@ -2057,63 +2057,63 @@
       <c r="P21" s="10"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="98"/>
+      <c r="L22" s="98"/>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="88" t="s">
+      <c r="G23" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88" t="s">
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88" t="s">
+      <c r="K23" s="102"/>
+      <c r="L23" s="102" t="s">
         <v>92</v>
       </c>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B24" s="85"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="102"/>
       <c r="M24" s="10"/>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.25">
@@ -2126,13 +2126,13 @@
       <c r="D25" s="34"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="K25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="K25" s="72"/>
       <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
@@ -2144,11 +2144,11 @@
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="20"/>
       <c r="M26" s="10"/>
     </row>
@@ -2158,11 +2158,11 @@
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
       <c r="L27" s="20"/>
       <c r="M27" s="10"/>
     </row>
@@ -2184,17 +2184,17 @@
       <c r="P28" s="10"/>
     </row>
     <row r="29" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
       <c r="F29" s="22"/>
-      <c r="G29" s="98" t="s">
+      <c r="G29" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="99"/>
+      <c r="H29" s="91"/>
       <c r="I29" s="36" t="s">
         <v>95</v>
       </c>
@@ -2209,17 +2209,17 @@
         <v>96</v>
       </c>
       <c r="C30" s="24"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="102" t="s">
+      <c r="G30" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="H30" s="103"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="67"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2228,17 +2228,17 @@
         <v>98</v>
       </c>
       <c r="C31" s="24"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="101"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
       <c r="F31" s="10"/>
-      <c r="G31" s="102" t="s">
+      <c r="G31" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="103"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="108"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="67"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2252,14 +2252,14 @@
         <v>101</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="102" t="s">
+      <c r="G32" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="H32" s="103"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="108"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="67"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
     </row>
@@ -2273,14 +2273,14 @@
         <v>101</v>
       </c>
       <c r="F33" s="10"/>
-      <c r="G33" s="95" t="s">
+      <c r="G33" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="H33" s="96"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="56"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="83"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="10"/>
@@ -2300,13 +2300,13 @@
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B35" s="92" t="s">
+      <c r="B35" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="94"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="86"/>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -2319,13 +2319,13 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="115" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
+      <c r="B36" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
       <c r="G36" s="42"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -2338,11 +2338,11 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="116"/>
-      <c r="C37" s="116"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
       <c r="G37" s="42"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -2355,11 +2355,11 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="116"/>
-      <c r="C38" s="116"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="116"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
       <c r="G38" s="42"/>
       <c r="H38" s="28" t="s">
         <v>106</v>
@@ -2375,11 +2375,11 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="116"/>
-      <c r="C39" s="116"/>
-      <c r="D39" s="116"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
       <c r="G39" s="42"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10" t="s">
@@ -2393,11 +2393,11 @@
       <c r="P39" s="10"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="116"/>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
       <c r="G40" s="42"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
@@ -2506,6 +2506,62 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="M15:O16"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:I24"/>
+    <mergeCell ref="J23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="J15:K16"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="B36:F40"/>
     <mergeCell ref="E15:E17"/>
@@ -2522,62 +2578,6 @@
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="N11:O11"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:I24"/>
-    <mergeCell ref="J23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="J15:K16"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="M15:O16"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G5"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D27" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2741,7 +2741,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="37" t="s">
         <v>85</v>
@@ -2808,10 +2808,10 @@
         <v>53</v>
       </c>
       <c r="S17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T17" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="U17" s="2" t="s">
         <v>55</v>
@@ -2880,10 +2880,10 @@
         <v>54</v>
       </c>
       <c r="S18" t="s">
+        <v>118</v>
+      </c>
+      <c r="T18" t="s">
         <v>119</v>
-      </c>
-      <c r="T18" t="s">
-        <v>120</v>
       </c>
       <c r="U18" t="s">
         <v>56</v>
@@ -3317,15 +3317,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3522,6 +3513,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3537,14 +3537,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3563,6 +3555,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5C23729-F91F-43E4-9E3D-5496BB18429B}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A39CB95-14C1-4101-B671-F581D1C814C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="136">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -416,6 +416,36 @@
   </si>
   <si>
     <t>${table:offerProductValidation.PRESENTATION}</t>
+  </si>
+  <si>
+    <t>130/1 North Sathon Road, Silom, Bangrak, Bangkok 10500</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${offerValidation.TENDERID}		</t>
+  </si>
+  <si>
+    <t>${offerValidation.PRODUCT_UNIT_NAME}</t>
+  </si>
+  <si>
+    <t>ProductGenericname</t>
+  </si>
+  <si>
+    <t>ProductGenericName</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.CODE3}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.CODE2}</t>
+  </si>
+  <si>
+    <t>THCC</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.GOV_CODE}</t>
   </si>
 </sst>
 </file>
@@ -875,6 +905,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -931,15 +966,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1214,14 +1240,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}" name="Tabel2" displayName="Tabel2" ref="C17:W52" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="C17:W52" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}" name="Tabel2" displayName="Tabel2" ref="D18:AA53" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="D18:AA53" xr:uid="{2EFFBCB4-83C9-46C5-9D10-EDD296E322D9}"/>
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{6E1F8ECB-E862-46B4-998C-BE8E89C238BA}" name="PAID VOLUME"/>
     <tableColumn id="2" xr3:uid="{6497AF92-63C8-4790-818D-6E5BE819E8D6}" name="UNIT"/>
     <tableColumn id="3" xr3:uid="{A1E59B72-B459-4BFA-9B37-9736C0F03B7E}" name="OFFER PRICE" dataDxfId="5"/>
@@ -1237,13 +1259,16 @@
     <tableColumn id="13" xr3:uid="{7D1379AA-4B8F-4BC6-9726-365EBAE15341}" name="FOC"/>
     <tableColumn id="14" xr3:uid="{DF88A36E-0423-48FC-A1FC-B18BF3BA8D1A}" name="Total Quantity Units"/>
     <tableColumn id="15" xr3:uid="{6B128E87-63EB-483B-88D7-EA33600F43AB}" name="Total QTY" dataDxfId="1">
-      <calculatedColumnFormula>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(E19&gt;0,IF(E19="Unit",CONCATENATE(Settings!Q19," ",Settings!E19,"s"),CONCATENATE((Settings!Q19/Settings!M19)," ",Settings!E19,"s")),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{E4D044B6-D053-487A-AA8C-F40FE34F30A7}" name="Net Price"/>
     <tableColumn id="17" xr3:uid="{F95E93A8-C80D-4AC7-9526-72374F546CE7}" name="Net Price Pack Vat"/>
     <tableColumn id="18" xr3:uid="{2DDE85E8-6C8E-4D93-A4E8-1F80D965246B}" name="Net Price Unit Vat"/>
     <tableColumn id="20" xr3:uid="{CB417A4B-91CA-49CD-9B3D-699005D44488}" name="Amount in numbers"/>
     <tableColumn id="21" xr3:uid="{07B28F29-5FC9-406A-96FC-77FFBFB88A05}" name="VAT total"/>
+    <tableColumn id="23" xr3:uid="{6CCBAAC0-B712-4045-B8A8-11B1701BD7D7}" name="GPU"/>
+    <tableColumn id="24" xr3:uid="{CCFCD047-C7DB-493A-9963-D2A80EA567D1}" name="THCC"/>
+    <tableColumn id="19" xr3:uid="{EFC0A69B-3069-4765-A820-C00302221FA7}" name="TPU"/>
     <tableColumn id="22" xr3:uid="{275B8D63-D363-4D68-BC9C-CB91FD9D0201}" name="Amount in numbers vat"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1251,8 +1276,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{13195211-A053-4079-8580-181B8695617E}" name="Tabel14" displayName="Tabel14" ref="A1:B15" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:B15" xr:uid="{13195211-A053-4079-8580-181B8695617E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{13195211-A053-4079-8580-181B8695617E}" name="Tabel14" displayName="Tabel14" ref="A1:B16" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:B16" xr:uid="{13195211-A053-4079-8580-181B8695617E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{04053350-A8BA-4F7A-9272-32CAE894E561}" name="Header fields"/>
     <tableColumn id="2" xr3:uid="{91B26FA0-9378-480D-8354-6037F7FF582C}" name="Description"/>
@@ -1638,7 +1663,9 @@
       <c r="I4" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="120"/>
+      <c r="J4" s="120" t="s">
+        <v>126</v>
+      </c>
       <c r="K4" s="121"/>
       <c r="L4" s="121"/>
       <c r="M4" s="122"/>
@@ -1681,44 +1708,48 @@
       <c r="P6" s="10"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="56"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="59"/>
     </row>
     <row r="8" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="113" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="119"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
+      <c r="D8" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
       <c r="G8" s="113" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="114"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="75"/>
+      <c r="I8" s="76" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
       <c r="L8" s="79" t="s">
         <v>70</v>
       </c>
       <c r="M8" s="80"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="72"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="75"/>
       <c r="P8" s="29"/>
     </row>
     <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1726,12 +1757,12 @@
         <v>71</v>
       </c>
       <c r="C9" s="119"/>
-      <c r="D9" s="62" t="str">
+      <c r="D9" s="65" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="64"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="115" t="s">
         <v>72</v>
       </c>
@@ -1745,8 +1776,8 @@
         <v>73</v>
       </c>
       <c r="M9" s="80"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="72"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="75"/>
       <c r="P9" s="29"/>
     </row>
     <row r="10" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1754,12 +1785,12 @@
         <v>74</v>
       </c>
       <c r="C10" s="119"/>
-      <c r="D10" s="62" t="str">
+      <c r="D10" s="65" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="64"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
       <c r="G10" s="117" t="s">
         <v>5</v>
       </c>
@@ -1773,8 +1804,8 @@
         <v>75</v>
       </c>
       <c r="M10" s="80"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="72"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="75"/>
       <c r="P10" s="29"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -1782,11 +1813,11 @@
         <v>6</v>
       </c>
       <c r="C11" s="119"/>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="67"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="70"/>
       <c r="G11" s="113" t="s">
         <v>7</v>
       </c>
@@ -1800,8 +1831,8 @@
         <v>73</v>
       </c>
       <c r="M11" s="80"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="72"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="75"/>
       <c r="P11" s="29"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
@@ -1809,11 +1840,11 @@
         <v>8</v>
       </c>
       <c r="C12" s="119"/>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="70"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -1865,32 +1896,32 @@
       <c r="B15" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="E15" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="59" t="s">
+      <c r="G15" s="62" t="s">
         <v>114</v>
       </c>
       <c r="H15" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="59" t="s">
+      <c r="I15" s="62" t="s">
         <v>81</v>
       </c>
       <c r="J15" s="103" t="s">
         <v>10</v>
       </c>
       <c r="K15" s="104"/>
-      <c r="L15" s="59" t="s">
+      <c r="L15" s="62" t="s">
         <v>82</v>
       </c>
       <c r="M15" s="103" t="s">
@@ -1905,16 +1936,16 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="96"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="60"/>
+      <c r="I16" s="63"/>
       <c r="J16" s="105"/>
       <c r="K16" s="106"/>
-      <c r="L16" s="60"/>
+      <c r="L16" s="63"/>
       <c r="M16" s="108"/>
       <c r="N16" s="109"/>
       <c r="O16" s="109"/>
@@ -1923,20 +1954,20 @@
     </row>
     <row r="17" spans="2:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B17" s="97"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
       <c r="H17" s="31"/>
-      <c r="I17" s="61"/>
+      <c r="I17" s="64"/>
       <c r="J17" s="13" t="s">
         <v>84</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="61"/>
+      <c r="L17" s="64"/>
       <c r="M17" s="13" t="s">
         <v>84</v>
       </c>
@@ -1963,7 +1994,9 @@
       <c r="D18" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="43"/>
+      <c r="E18" s="43" t="s">
+        <v>22</v>
+      </c>
       <c r="F18" s="15" t="s">
         <v>28</v>
       </c>
@@ -2076,16 +2109,16 @@
       <c r="B23" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="62" t="s">
         <v>78</v>
       </c>
       <c r="D23" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="62" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="102" t="s">
@@ -2104,10 +2137,10 @@
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="99"/>
-      <c r="C24" s="61"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="101"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
       <c r="G24" s="102"/>
       <c r="H24" s="102"/>
       <c r="I24" s="102"/>
@@ -2124,15 +2157,21 @@
         <v>23</v>
       </c>
       <c r="D25" s="34"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="71" t="s">
+      <c r="E25" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" s="73" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="K25" s="72"/>
+      <c r="K25" s="75"/>
       <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
@@ -2144,11 +2183,11 @@
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
       <c r="L26" s="20"/>
       <c r="M26" s="10"/>
     </row>
@@ -2158,11 +2197,11 @@
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
       <c r="L27" s="20"/>
       <c r="M27" s="10"/>
     </row>
@@ -2216,10 +2255,10 @@
         <v>97</v>
       </c>
       <c r="H30" s="94"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="67"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="70"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2228,17 +2267,17 @@
         <v>98</v>
       </c>
       <c r="C31" s="24"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
       <c r="F31" s="10"/>
       <c r="G31" s="93" t="s">
         <v>99</v>
       </c>
       <c r="H31" s="94"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="67"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="70"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2256,10 +2295,10 @@
         <v>102</v>
       </c>
       <c r="H32" s="94"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="67"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="70"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
     </row>
@@ -2319,13 +2358,13 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
       <c r="G36" s="42"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -2338,11 +2377,11 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
       <c r="G37" s="42"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -2355,11 +2394,11 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
       <c r="G38" s="42"/>
       <c r="H38" s="28" t="s">
         <v>106</v>
@@ -2375,11 +2414,11 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
       <c r="G39" s="42"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10" t="s">
@@ -2393,11 +2432,11 @@
       <c r="P39" s="10"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
       <c r="G40" s="42"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
@@ -2599,43 +2638,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BADA0-6CEF-4001-8243-A13FFD1BF3BE}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="75.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" customWidth="1"/>
-    <col min="18" max="18" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.42578125" customWidth="1"/>
-    <col min="23" max="23" width="35.85546875" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="69.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" customWidth="1"/>
+    <col min="19" max="19" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="30.42578125" customWidth="1"/>
+    <col min="27" max="27" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="55"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2643,7 +2684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2651,7 +2692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2667,7 +2708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2675,7 +2716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2683,7 +2724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2691,7 +2732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2699,7 +2740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -2707,7 +2748,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2715,7 +2756,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>109</v>
       </c>
@@ -2723,7 +2764,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -2731,7 +2772,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -2739,567 +2780,600 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B16" s="54" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="C16" s="37"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="X18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA18" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
         <v>28</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G19" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="J19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K19" t="s">
         <v>42</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L19" t="s">
         <v>44</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M19" t="s">
         <v>24</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N19" t="s">
         <v>25</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O19" t="s">
         <v>26</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P19" t="s">
         <v>27</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q19" t="s">
         <v>63</v>
       </c>
-      <c r="Q18" t="e">
-        <f>IF(D18&gt;0,IF(D18="Unit",CONCATENATE(Settings!P18," ",Settings!D18,"s"),CONCATENATE((Settings!P18/Settings!L18)," ",Settings!D18,"s")),"")</f>
+      <c r="R19" t="e">
+        <f>IF(E19&gt;0,IF(E19="Unit",CONCATENATE(Settings!Q19," ",Settings!E19,"s"),CONCATENATE((Settings!Q19/Settings!M19)," ",Settings!E19,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S19" t="s">
         <v>54</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T19" t="s">
         <v>118</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U19" t="s">
         <v>119</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V19" t="s">
         <v>56</v>
       </c>
-      <c r="V18" t="s">
+      <c r="W19" t="s">
         <v>62</v>
       </c>
-      <c r="W18" t="s">
+      <c r="X19" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
-      <c r="E19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="Q19" t="str">
-        <f>IF(D19&gt;0,IF(D19="Unit",CONCATENATE(Settings!P19," ",Settings!D19,"s"),CONCATENATE((Settings!P19/Settings!L19)," ",Settings!D19,"s")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
-      <c r="E20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="Q20" t="str">
-        <f>IF(D20&gt;0,IF(D20="Unit",CONCATENATE(Settings!P20," ",Settings!D20,"s"),CONCATENATE((Settings!P20/Settings!L20)," ",Settings!D20,"s")),"")</f>
+      <c r="J20" s="9"/>
+      <c r="R20" t="str">
+        <f>IF(E20&gt;0,IF(E20="Unit",CONCATENATE(Settings!Q20," ",Settings!E20,"s"),CONCATENATE((Settings!Q20/Settings!M20)," ",Settings!E20,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
-      <c r="E21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="Q21" t="str">
-        <f>IF(D21&gt;0,IF(D21="Unit",CONCATENATE(Settings!P21," ",Settings!D21,"s"),CONCATENATE((Settings!P21/Settings!L21)," ",Settings!D21,"s")),"")</f>
+      <c r="J21" s="9"/>
+      <c r="R21" t="str">
+        <f>IF(E21&gt;0,IF(E21="Unit",CONCATENATE(Settings!Q21," ",Settings!E21,"s"),CONCATENATE((Settings!Q21/Settings!M21)," ",Settings!E21,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
-      <c r="E22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
-      <c r="Q22" t="str">
-        <f>IF(D22&gt;0,IF(D22="Unit",CONCATENATE(Settings!P22," ",Settings!D22,"s"),CONCATENATE((Settings!P22/Settings!L22)," ",Settings!D22,"s")),"")</f>
+      <c r="J22" s="9"/>
+      <c r="R22" t="str">
+        <f>IF(E22&gt;0,IF(E22="Unit",CONCATENATE(Settings!Q22," ",Settings!E22,"s"),CONCATENATE((Settings!Q22/Settings!M22)," ",Settings!E22,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
-      <c r="E23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
-      <c r="Q23" t="str">
-        <f>IF(D23&gt;0,IF(D23="Unit",CONCATENATE(Settings!P23," ",Settings!D23,"s"),CONCATENATE((Settings!P23/Settings!L23)," ",Settings!D23,"s")),"")</f>
+      <c r="J23" s="9"/>
+      <c r="R23" t="str">
+        <f>IF(E23&gt;0,IF(E23="Unit",CONCATENATE(Settings!Q23," ",Settings!E23,"s"),CONCATENATE((Settings!Q23/Settings!M23)," ",Settings!E23,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
-      <c r="E24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
-      <c r="Q24" t="str">
-        <f>IF(D24&gt;0,IF(D24="Unit",CONCATENATE(Settings!P24," ",Settings!D24,"s"),CONCATENATE((Settings!P24/Settings!L24)," ",Settings!D24,"s")),"")</f>
+      <c r="J24" s="9"/>
+      <c r="R24" t="str">
+        <f>IF(E24&gt;0,IF(E24="Unit",CONCATENATE(Settings!Q24," ",Settings!E24,"s"),CONCATENATE((Settings!Q24/Settings!M24)," ",Settings!E24,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
-      <c r="E25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="F25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
-      <c r="Q25" t="str">
-        <f>IF(D25&gt;0,IF(D25="Unit",CONCATENATE(Settings!P25," ",Settings!D25,"s"),CONCATENATE((Settings!P25/Settings!L25)," ",Settings!D25,"s")),"")</f>
+      <c r="J25" s="9"/>
+      <c r="R25" t="str">
+        <f>IF(E25&gt;0,IF(E25="Unit",CONCATENATE(Settings!Q25," ",Settings!E25,"s"),CONCATENATE((Settings!Q25/Settings!M25)," ",Settings!E25,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
-      <c r="E26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="F26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
-      <c r="Q26" t="str">
-        <f>IF(D26&gt;0,IF(D26="Unit",CONCATENATE(Settings!P26," ",Settings!D26,"s"),CONCATENATE((Settings!P26/Settings!L26)," ",Settings!D26,"s")),"")</f>
+      <c r="J26" s="9"/>
+      <c r="R26" t="str">
+        <f>IF(E26&gt;0,IF(E26="Unit",CONCATENATE(Settings!Q26," ",Settings!E26,"s"),CONCATENATE((Settings!Q26/Settings!M26)," ",Settings!E26,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
-      <c r="E27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="F27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="Q27" t="str">
-        <f>IF(D27&gt;0,IF(D27="Unit",CONCATENATE(Settings!P27," ",Settings!D27,"s"),CONCATENATE((Settings!P27/Settings!L27)," ",Settings!D27,"s")),"")</f>
+      <c r="J27" s="9"/>
+      <c r="R27" t="str">
+        <f>IF(E27&gt;0,IF(E27="Unit",CONCATENATE(Settings!Q27," ",Settings!E27,"s"),CONCATENATE((Settings!Q27/Settings!M27)," ",Settings!E27,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
-      <c r="E28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
-      <c r="Q28" t="str">
-        <f>IF(D28&gt;0,IF(D28="Unit",CONCATENATE(Settings!P28," ",Settings!D28,"s"),CONCATENATE((Settings!P28/Settings!L28)," ",Settings!D28,"s")),"")</f>
+      <c r="J28" s="9"/>
+      <c r="R28" t="str">
+        <f>IF(E28&gt;0,IF(E28="Unit",CONCATENATE(Settings!Q28," ",Settings!E28,"s"),CONCATENATE((Settings!Q28/Settings!M28)," ",Settings!E28,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
-      <c r="E29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
-      <c r="Q29" t="str">
-        <f>IF(D29&gt;0,IF(D29="Unit",CONCATENATE(Settings!P29," ",Settings!D29,"s"),CONCATENATE((Settings!P29/Settings!L29)," ",Settings!D29,"s")),"")</f>
+      <c r="J29" s="9"/>
+      <c r="R29" t="str">
+        <f>IF(E29&gt;0,IF(E29="Unit",CONCATENATE(Settings!Q29," ",Settings!E29,"s"),CONCATENATE((Settings!Q29/Settings!M29)," ",Settings!E29,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
-      <c r="E30" s="9"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
-      <c r="Q30" t="str">
-        <f>IF(D30&gt;0,IF(D30="Unit",CONCATENATE(Settings!P30," ",Settings!D30,"s"),CONCATENATE((Settings!P30/Settings!L30)," ",Settings!D30,"s")),"")</f>
+      <c r="J30" s="9"/>
+      <c r="R30" t="str">
+        <f>IF(E30&gt;0,IF(E30="Unit",CONCATENATE(Settings!Q30," ",Settings!E30,"s"),CONCATENATE((Settings!Q30/Settings!M30)," ",Settings!E30,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
-      <c r="E31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="F31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
-      <c r="Q31" t="str">
-        <f>IF(D31&gt;0,IF(D31="Unit",CONCATENATE(Settings!P31," ",Settings!D31,"s"),CONCATENATE((Settings!P31/Settings!L31)," ",Settings!D31,"s")),"")</f>
+      <c r="J31" s="9"/>
+      <c r="R31" t="str">
+        <f>IF(E31&gt;0,IF(E31="Unit",CONCATENATE(Settings!Q31," ",Settings!E31,"s"),CONCATENATE((Settings!Q31/Settings!M31)," ",Settings!E31,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="E32" s="9"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
-      <c r="Q32" t="str">
-        <f>IF(D32&gt;0,IF(D32="Unit",CONCATENATE(Settings!P32," ",Settings!D32,"s"),CONCATENATE((Settings!P32/Settings!L32)," ",Settings!D32,"s")),"")</f>
+      <c r="J32" s="9"/>
+      <c r="R32" t="str">
+        <f>IF(E32&gt;0,IF(E32="Unit",CONCATENATE(Settings!Q32," ",Settings!E32,"s"),CONCATENATE((Settings!Q32/Settings!M32)," ",Settings!E32,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
-      <c r="E33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
-      <c r="Q33" t="str">
-        <f>IF(D33&gt;0,IF(D33="Unit",CONCATENATE(Settings!P33," ",Settings!D33,"s"),CONCATENATE((Settings!P33/Settings!L33)," ",Settings!D33,"s")),"")</f>
+      <c r="J33" s="9"/>
+      <c r="R33" t="str">
+        <f>IF(E33&gt;0,IF(E33="Unit",CONCATENATE(Settings!Q33," ",Settings!E33,"s"),CONCATENATE((Settings!Q33/Settings!M33)," ",Settings!E33,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
-      <c r="E34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="F34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
-      <c r="Q34" t="str">
-        <f>IF(D34&gt;0,IF(D34="Unit",CONCATENATE(Settings!P34," ",Settings!D34,"s"),CONCATENATE((Settings!P34/Settings!L34)," ",Settings!D34,"s")),"")</f>
+      <c r="J34" s="9"/>
+      <c r="R34" t="str">
+        <f>IF(E34&gt;0,IF(E34="Unit",CONCATENATE(Settings!Q34," ",Settings!E34,"s"),CONCATENATE((Settings!Q34/Settings!M34)," ",Settings!E34,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
-      <c r="E35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="F35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
-      <c r="Q35" t="str">
-        <f>IF(D35&gt;0,IF(D35="Unit",CONCATENATE(Settings!P35," ",Settings!D35,"s"),CONCATENATE((Settings!P35/Settings!L35)," ",Settings!D35,"s")),"")</f>
+      <c r="J35" s="9"/>
+      <c r="R35" t="str">
+        <f>IF(E35&gt;0,IF(E35="Unit",CONCATENATE(Settings!Q35," ",Settings!E35,"s"),CONCATENATE((Settings!Q35/Settings!M35)," ",Settings!E35,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
-      <c r="E36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
-      <c r="Q36" t="str">
-        <f>IF(D36&gt;0,IF(D36="Unit",CONCATENATE(Settings!P36," ",Settings!D36,"s"),CONCATENATE((Settings!P36/Settings!L36)," ",Settings!D36,"s")),"")</f>
+      <c r="J36" s="9"/>
+      <c r="R36" t="str">
+        <f>IF(E36&gt;0,IF(E36="Unit",CONCATENATE(Settings!Q36," ",Settings!E36,"s"),CONCATENATE((Settings!Q36/Settings!M36)," ",Settings!E36,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
-      <c r="E37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="Q37" t="str">
-        <f>IF(D37&gt;0,IF(D37="Unit",CONCATENATE(Settings!P37," ",Settings!D37,"s"),CONCATENATE((Settings!P37/Settings!L37)," ",Settings!D37,"s")),"")</f>
+      <c r="J37" s="9"/>
+      <c r="R37" t="str">
+        <f>IF(E37&gt;0,IF(E37="Unit",CONCATENATE(Settings!Q37," ",Settings!E37,"s"),CONCATENATE((Settings!Q37/Settings!M37)," ",Settings!E37,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
-      <c r="E38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
-      <c r="Q38" t="str">
-        <f>IF(D38&gt;0,IF(D38="Unit",CONCATENATE(Settings!P38," ",Settings!D38,"s"),CONCATENATE((Settings!P38/Settings!L38)," ",Settings!D38,"s")),"")</f>
+      <c r="J38" s="9"/>
+      <c r="R38" t="str">
+        <f>IF(E38&gt;0,IF(E38="Unit",CONCATENATE(Settings!Q38," ",Settings!E38,"s"),CONCATENATE((Settings!Q38/Settings!M38)," ",Settings!E38,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
-      <c r="E39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="F39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
-      <c r="Q39" t="str">
-        <f>IF(D39&gt;0,IF(D39="Unit",CONCATENATE(Settings!P39," ",Settings!D39,"s"),CONCATENATE((Settings!P39/Settings!L39)," ",Settings!D39,"s")),"")</f>
+      <c r="J39" s="9"/>
+      <c r="R39" t="str">
+        <f>IF(E39&gt;0,IF(E39="Unit",CONCATENATE(Settings!Q39," ",Settings!E39,"s"),CONCATENATE((Settings!Q39/Settings!M39)," ",Settings!E39,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
-      <c r="E40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="F40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
-      <c r="Q40" t="str">
-        <f>IF(D40&gt;0,IF(D40="Unit",CONCATENATE(Settings!P40," ",Settings!D40,"s"),CONCATENATE((Settings!P40/Settings!L40)," ",Settings!D40,"s")),"")</f>
+      <c r="J40" s="9"/>
+      <c r="R40" t="str">
+        <f>IF(E40&gt;0,IF(E40="Unit",CONCATENATE(Settings!Q40," ",Settings!E40,"s"),CONCATENATE((Settings!Q40/Settings!M40)," ",Settings!E40,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
-      <c r="E41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="F41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
-      <c r="Q41" t="str">
-        <f>IF(D41&gt;0,IF(D41="Unit",CONCATENATE(Settings!P41," ",Settings!D41,"s"),CONCATENATE((Settings!P41/Settings!L41)," ",Settings!D41,"s")),"")</f>
+      <c r="J41" s="9"/>
+      <c r="R41" t="str">
+        <f>IF(E41&gt;0,IF(E41="Unit",CONCATENATE(Settings!Q41," ",Settings!E41,"s"),CONCATENATE((Settings!Q41/Settings!M41)," ",Settings!E41,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
-      <c r="E42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="F42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
-      <c r="Q42" t="str">
-        <f>IF(D42&gt;0,IF(D42="Unit",CONCATENATE(Settings!P42," ",Settings!D42,"s"),CONCATENATE((Settings!P42/Settings!L42)," ",Settings!D42,"s")),"")</f>
+      <c r="J42" s="9"/>
+      <c r="R42" t="str">
+        <f>IF(E42&gt;0,IF(E42="Unit",CONCATENATE(Settings!Q42," ",Settings!E42,"s"),CONCATENATE((Settings!Q42/Settings!M42)," ",Settings!E42,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
-      <c r="E43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="F43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
-      <c r="Q43" t="str">
-        <f>IF(D43&gt;0,IF(D43="Unit",CONCATENATE(Settings!P43," ",Settings!D43,"s"),CONCATENATE((Settings!P43/Settings!L43)," ",Settings!D43,"s")),"")</f>
+      <c r="J43" s="9"/>
+      <c r="R43" t="str">
+        <f>IF(E43&gt;0,IF(E43="Unit",CONCATENATE(Settings!Q43," ",Settings!E43,"s"),CONCATENATE((Settings!Q43/Settings!M43)," ",Settings!E43,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
-      <c r="E44" s="9"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
-      <c r="Q44" t="str">
-        <f>IF(D44&gt;0,IF(D44="Unit",CONCATENATE(Settings!P44," ",Settings!D44,"s"),CONCATENATE((Settings!P44/Settings!L44)," ",Settings!D44,"s")),"")</f>
+      <c r="J44" s="9"/>
+      <c r="R44" t="str">
+        <f>IF(E44&gt;0,IF(E44="Unit",CONCATENATE(Settings!Q44," ",Settings!E44,"s"),CONCATENATE((Settings!Q44/Settings!M44)," ",Settings!E44,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
-      <c r="E45" s="9"/>
-      <c r="G45" s="9"/>
+      <c r="F45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
-      <c r="Q45" t="str">
-        <f>IF(D45&gt;0,IF(D45="Unit",CONCATENATE(Settings!P45," ",Settings!D45,"s"),CONCATENATE((Settings!P45/Settings!L45)," ",Settings!D45,"s")),"")</f>
+      <c r="J45" s="9"/>
+      <c r="R45" t="str">
+        <f>IF(E45&gt;0,IF(E45="Unit",CONCATENATE(Settings!Q45," ",Settings!E45,"s"),CONCATENATE((Settings!Q45/Settings!M45)," ",Settings!E45,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="4"/>
-      <c r="E46" s="9"/>
-      <c r="G46" s="9"/>
+      <c r="F46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
-      <c r="Q46" t="str">
-        <f>IF(D46&gt;0,IF(D46="Unit",CONCATENATE(Settings!P46," ",Settings!D46,"s"),CONCATENATE((Settings!P46/Settings!L46)," ",Settings!D46,"s")),"")</f>
+      <c r="J46" s="9"/>
+      <c r="R46" t="str">
+        <f>IF(E46&gt;0,IF(E46="Unit",CONCATENATE(Settings!Q46," ",Settings!E46,"s"),CONCATENATE((Settings!Q46/Settings!M46)," ",Settings!E46,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
-      <c r="E47" s="9"/>
-      <c r="G47" s="9"/>
+      <c r="F47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
-      <c r="Q47" t="str">
-        <f>IF(D47&gt;0,IF(D47="Unit",CONCATENATE(Settings!P47," ",Settings!D47,"s"),CONCATENATE((Settings!P47/Settings!L47)," ",Settings!D47,"s")),"")</f>
+      <c r="J47" s="9"/>
+      <c r="R47" t="str">
+        <f>IF(E47&gt;0,IF(E47="Unit",CONCATENATE(Settings!Q47," ",Settings!E47,"s"),CONCATENATE((Settings!Q47/Settings!M47)," ",Settings!E47,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
-      <c r="E48" s="9"/>
-      <c r="G48" s="9"/>
+      <c r="F48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
-      <c r="Q48" t="str">
-        <f>IF(D48&gt;0,IF(D48="Unit",CONCATENATE(Settings!P48," ",Settings!D48,"s"),CONCATENATE((Settings!P48/Settings!L48)," ",Settings!D48,"s")),"")</f>
+      <c r="J48" s="9"/>
+      <c r="R48" t="str">
+        <f>IF(E48&gt;0,IF(E48="Unit",CONCATENATE(Settings!Q48," ",Settings!E48,"s"),CONCATENATE((Settings!Q48/Settings!M48)," ",Settings!E48,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
-      <c r="E49" s="9"/>
-      <c r="G49" s="9"/>
+      <c r="F49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
-      <c r="Q49" t="str">
-        <f>IF(D49&gt;0,IF(D49="Unit",CONCATENATE(Settings!P49," ",Settings!D49,"s"),CONCATENATE((Settings!P49/Settings!L49)," ",Settings!D49,"s")),"")</f>
+      <c r="J49" s="9"/>
+      <c r="R49" t="str">
+        <f>IF(E49&gt;0,IF(E49="Unit",CONCATENATE(Settings!Q49," ",Settings!E49,"s"),CONCATENATE((Settings!Q49/Settings!M49)," ",Settings!E49,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
-      <c r="E50" s="9"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
-      <c r="Q50" t="str">
-        <f>IF(D50&gt;0,IF(D50="Unit",CONCATENATE(Settings!P50," ",Settings!D50,"s"),CONCATENATE((Settings!P50/Settings!L50)," ",Settings!D50,"s")),"")</f>
+      <c r="J50" s="9"/>
+      <c r="R50" t="str">
+        <f>IF(E50&gt;0,IF(E50="Unit",CONCATENATE(Settings!Q50," ",Settings!E50,"s"),CONCATENATE((Settings!Q50/Settings!M50)," ",Settings!E50,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
-      <c r="E51" s="9"/>
-      <c r="G51" s="9"/>
+      <c r="F51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
-      <c r="Q51" t="str">
-        <f>IF(D51&gt;0,IF(D51="Unit",CONCATENATE(Settings!P51," ",Settings!D51,"s"),CONCATENATE((Settings!P51/Settings!L51)," ",Settings!D51,"s")),"")</f>
+      <c r="J51" s="9"/>
+      <c r="R51" t="str">
+        <f>IF(E51&gt;0,IF(E51="Unit",CONCATENATE(Settings!Q51," ",Settings!E51,"s"),CONCATENATE((Settings!Q51/Settings!M51)," ",Settings!E51,"s")),"")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6"/>
-      <c r="E52" s="9"/>
-      <c r="G52" s="9"/>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="F52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
-      <c r="Q52" t="str">
-        <f>IF(D52&gt;0,IF(D52="Unit",CONCATENATE(Settings!P52," ",Settings!D52,"s"),CONCATENATE((Settings!P52/Settings!L52)," ",Settings!D52,"s")),"")</f>
+      <c r="J52" s="9"/>
+      <c r="R52" t="str">
+        <f>IF(E52&gt;0,IF(E52="Unit",CONCATENATE(Settings!Q52," ",Settings!E52,"s"),CONCATENATE((Settings!Q52/Settings!M52)," ",Settings!E52,"s")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="F53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="R53" t="str">
+        <f>IF(E53&gt;0,IF(E53="Unit",CONCATENATE(Settings!Q53," ",Settings!E53,"s"),CONCATENATE((Settings!Q53/Settings!M53)," ",Settings!E53,"s")),"")</f>
         <v/>
       </c>
     </row>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46805220-69DA-43DB-8DA0-F7A265237728}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8858771C-6D27-4E6F-BDFF-4E35110ECB03}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView minimized="1" xWindow="5115" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -382,9 +382,6 @@
     <t>${offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
   </si>
   <si>
-    <t>${table:offerProductValidation.NET_PRICE_PACK_OFFER_CURRENCY_VAT}</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
   </si>
   <si>
@@ -397,12 +394,6 @@
     <t xml:space="preserve">With reference to the above tender, you must not on-sell the above mentioned products at a price higher than those listed above. However, you are always free to sell at a price lower, at your discretion. </t>
   </si>
   <si>
-    <t>incl. vat.(Pack)</t>
-  </si>
-  <si>
-    <t>incl. vat.(Unit)</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.PRESENTATION}</t>
   </si>
   <si>
@@ -415,28 +406,34 @@
     <t xml:space="preserve">${offerValidation.TENDERID}		</t>
   </si>
   <si>
+    <t>ProductGenericname</t>
+  </si>
+  <si>
+    <t>ProductGenericName</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.CODE3}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.CODE2}</t>
+  </si>
+  <si>
+    <t>THCC</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.GOV_CODE}</t>
+  </si>
+  <si>
+    <t>Unit Dosage</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PRODUCTGENERICNAME}</t>
+  </si>
+  <si>
     <t>${offerValidation.PRODUCT_UNIT_NAME}</t>
   </si>
   <si>
-    <t>ProductGenericname</t>
-  </si>
-  <si>
-    <t>ProductGenericName</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.CODE3}</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.CODE2}</t>
-  </si>
-  <si>
-    <t>THCC</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.GOV_CODE}</t>
-  </si>
-  <si>
-    <t>Unit Dosage</t>
+    <t>${table:offerProductValidation.NET_PRICE_VAT}</t>
   </si>
 </sst>
 </file>
@@ -783,7 +780,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -871,7 +868,6 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -882,6 +878,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -891,6 +977,69 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -900,27 +1049,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,12 +1058,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -945,9 +1067,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -962,117 +1081,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1155,8 +1163,8 @@
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>613834</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>42334</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>105833</xdr:rowOff>
     </xdr:to>
@@ -1221,6 +1229,10 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1581,9 +1593,9 @@
     <col min="10" max="10" width="17.5703125" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" customWidth="1"/>
     <col min="14" max="14" width="18.140625" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" customWidth="1"/>
     <col min="16" max="16" width="15.28515625" customWidth="1"/>
     <col min="17" max="17" width="17.85546875" customWidth="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
@@ -1610,23 +1622,23 @@
       <c r="B3" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="81"/>
       <c r="H3" s="10"/>
       <c r="I3" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="52"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="81"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -1635,23 +1647,23 @@
       <c r="B4" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="58"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
       <c r="H4" s="10"/>
       <c r="I4" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="55"/>
+      <c r="J4" s="103" t="s">
+        <v>119</v>
+      </c>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="105"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -1674,143 +1686,143 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="109"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="59"/>
     </row>
     <row r="7" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="71" t="s">
+      <c r="C7" s="99"/>
+      <c r="D7" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="72"/>
-      <c r="I7" s="104" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="99" t="s">
+      <c r="H7" s="112"/>
+      <c r="I7" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="100"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="67"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="73"/>
       <c r="P7" s="26"/>
     </row>
     <row r="8" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="78"/>
-      <c r="D8" s="56" t="str">
+      <c r="C8" s="99"/>
+      <c r="D8" s="63" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="73" t="s">
+      <c r="E8" s="64"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="113" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="74"/>
-      <c r="I8" s="104" t="s">
+      <c r="H8" s="114"/>
+      <c r="I8" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="99" t="s">
+      <c r="J8" s="75"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="100"/>
-      <c r="N8" s="66"/>
-      <c r="O8" s="67"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="73"/>
       <c r="P8" s="26"/>
     </row>
     <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="56" t="str">
+      <c r="C9" s="99"/>
+      <c r="D9" s="63" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="75" t="s">
+      <c r="E9" s="64"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="76"/>
-      <c r="I9" s="104" t="s">
+      <c r="H9" s="116"/>
+      <c r="I9" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="105"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="99" t="s">
+      <c r="J9" s="75"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="100"/>
-      <c r="N9" s="66"/>
-      <c r="O9" s="67"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="73"/>
       <c r="P9" s="26"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="101" t="s">
+      <c r="C10" s="99"/>
+      <c r="D10" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="71" t="s">
+      <c r="E10" s="67"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="72"/>
-      <c r="I10" s="68" t="s">
+      <c r="H10" s="112"/>
+      <c r="I10" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="69"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="99" t="s">
+      <c r="J10" s="110"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="100"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="67"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="73"/>
       <c r="P10" s="26"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="78"/>
-      <c r="D11" s="101" t="s">
+      <c r="C11" s="99"/>
+      <c r="D11" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="103"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="68"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1839,110 +1851,108 @@
       <c r="P12" s="10"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="77"/>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="77"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
     </row>
     <row r="14" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="93" t="s">
         <v>110</v>
       </c>
       <c r="H14" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="J14" s="62" t="s">
+      <c r="I14" s="93" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="85"/>
-      <c r="L14" s="59" t="s">
+      <c r="K14" s="54"/>
+      <c r="L14" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="M14" s="62" t="s">
+      <c r="M14" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="62" t="s">
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="Q14" s="85"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="80"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
       <c r="H15" s="29"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="86"/>
-    </row>
-    <row r="16" spans="2:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="81"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="108"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="56"/>
+    </row>
+    <row r="16" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="102"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="61"/>
+      <c r="I16" s="95"/>
       <c r="J16" s="11" t="s">
         <v>83</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="61"/>
+      <c r="L16" s="95"/>
       <c r="M16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>119</v>
-      </c>
+      <c r="N16" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="O16" s="50"/>
       <c r="P16" s="11" t="s">
         <v>83</v>
       </c>
@@ -1961,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>28</v>
@@ -1973,7 +1983,7 @@
         <v>24</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J17" s="41" t="s">
         <v>32</v>
@@ -1987,17 +1997,14 @@
       <c r="M17" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="43" t="str">
-        <f>IF(B17&gt;0,IF(G17="Unit",CONCATENATE((Settings!L20)," "),CONCATENATE(Settings!L20,"")))</f>
-        <v>${table:offerProductValidation.SORTER}</v>
-      </c>
-      <c r="O17" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="P17" s="44" t="s">
+      <c r="N17" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="O17" s="52"/>
+      <c r="P17" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="45" t="s">
+      <c r="Q17" s="44" t="s">
         <v>58</v>
       </c>
       <c r="R17" s="38"/>
@@ -2016,8 +2023,8 @@
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="30"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="52"/>
       <c r="P18" s="14"/>
       <c r="Q18" s="17"/>
     </row>
@@ -2034,8 +2041,8 @@
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="30"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="52"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="17"/>
     </row>
@@ -2057,63 +2064,63 @@
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="84" t="s">
+      <c r="G22" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84" t="s">
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84" t="s">
+      <c r="K22" s="62"/>
+      <c r="L22" s="62" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="82"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
+      <c r="B23" s="97"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
@@ -2125,20 +2132,20 @@
       </c>
       <c r="D24" s="30"/>
       <c r="E24" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" s="113" t="s">
-        <v>131</v>
-      </c>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="67"/>
+      <c r="K24" s="73"/>
       <c r="L24" s="18" t="s">
         <v>26</v>
       </c>
@@ -2146,29 +2153,29 @@
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
-      <c r="C25" s="49"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
       <c r="L25" s="18"/>
       <c r="M25" s="10"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
-      <c r="C26" s="49"/>
+      <c r="C26" s="48"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
       <c r="L26" s="18"/>
       <c r="M26" s="10"/>
     </row>
@@ -2190,17 +2197,17 @@
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="92" t="s">
+      <c r="B28" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="20"/>
-      <c r="G28" s="93" t="s">
+      <c r="G28" s="88" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="94"/>
+      <c r="H28" s="89"/>
       <c r="I28" s="32" t="s">
         <v>94</v>
       </c>
@@ -2215,17 +2222,17 @@
         <v>95</v>
       </c>
       <c r="C29" s="22"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="97" t="s">
+      <c r="G29" s="91" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="98"/>
-      <c r="I29" s="101"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="103"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="68"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2234,17 +2241,17 @@
         <v>97</v>
       </c>
       <c r="C30" s="22"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="97" t="s">
+      <c r="G30" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="H30" s="98"/>
-      <c r="I30" s="101"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="103"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="68"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2258,14 +2265,14 @@
         <v>100</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="97" t="s">
+      <c r="G31" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="98"/>
-      <c r="I31" s="101"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="103"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="68"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2279,14 +2286,14 @@
         <v>100</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="90" t="s">
+      <c r="G32" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="91"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="52"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="81"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2306,13 +2313,13 @@
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="84"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -2325,13 +2332,13 @@
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="110" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="110"/>
+      <c r="B35" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
       <c r="G35" s="34"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -2344,11 +2351,11 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
       <c r="G36" s="34"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -2361,11 +2368,11 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="111"/>
-      <c r="C37" s="111"/>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="111"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
       <c r="G37" s="34"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -2378,11 +2385,11 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="111"/>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111"/>
-      <c r="F38" s="111"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
       <c r="G38" s="34"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
@@ -2395,11 +2402,11 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="111"/>
-      <c r="C39" s="111"/>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111"/>
-      <c r="F39" s="111"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
       <c r="G39" s="34"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
@@ -2529,8 +2536,62 @@
       <c r="G49" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="P14:Q15"/>
+  <mergeCells count="76">
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="M14:O15"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B13:Q13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
     <mergeCell ref="B6:O6"/>
     <mergeCell ref="B35:F39"/>
     <mergeCell ref="E14:E16"/>
@@ -2547,61 +2608,11 @@
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="J14:K15"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="M14:O15"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B13:Q13"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P14:Q15"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2659,7 +2670,7 @@
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="47"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2767,17 +2778,17 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="45" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="33"/>
@@ -2794,8 +2805,8 @@
       <c r="B19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="48" t="s">
-        <v>127</v>
+      <c r="C19" s="47" t="s">
+        <v>123</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>30</v>
@@ -2846,10 +2857,10 @@
         <v>53</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>55</v>
@@ -2861,7 +2872,7 @@
         <v>88</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>87</v>
@@ -2878,7 +2889,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -2930,10 +2941,10 @@
         <v>54</v>
       </c>
       <c r="T20" t="s">
+        <v>131</v>
+      </c>
+      <c r="U20" t="s">
         <v>114</v>
-      </c>
-      <c r="U20" t="s">
-        <v>115</v>
       </c>
       <c r="V20" t="s">
         <v>56</v>
@@ -2942,13 +2953,13 @@
         <v>62</v>
       </c>
       <c r="X20" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y20" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Z20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="AA20" t="s">
         <v>58</v>
@@ -3376,6 +3387,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3572,30 +3606,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3612,22 +3641,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8858771C-6D27-4E6F-BDFF-4E35110ECB03}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C11C3FC-06E5-4BCC-80FE-6D90FE054333}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5115" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="133">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -379,9 +379,6 @@
     <t>${table:offerProductValidation.MANUFACTURER}</t>
   </si>
   <si>
-    <t>${offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
-  </si>
-  <si>
     <t>${table:offerProductValidation.NET_PRICE_UNIT_OFFER_CURRENCY_VAT}</t>
   </si>
   <si>
@@ -434,6 +431,12 @@
   </si>
   <si>
     <t>${table:offerProductValidation.NET_PRICE_VAT}</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.NET_OFFER_PRICE}</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -766,12 +769,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -780,7 +783,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -804,7 +807,6 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -822,15 +824,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -850,58 +843,207 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -911,48 +1053,6 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -968,119 +1068,11 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1157,16 +1149,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>793750</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>148166</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:rowOff>116416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>42334</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>105833</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1519766</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>154516</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1181,8 +1173,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13663083" y="158750"/>
-          <a:ext cx="1788584" cy="709083"/>
+          <a:off x="14668499" y="116416"/>
+          <a:ext cx="1371600" cy="1371600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1596,12 +1588,12 @@
     <col min="13" max="13" width="19.5703125" customWidth="1"/>
     <col min="14" max="14" width="18.140625" customWidth="1"/>
     <col min="15" max="15" width="4.7109375" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="28.140625" customWidth="1"/>
     <col min="17" max="17" width="17.85546875" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1618,57 +1610,57 @@
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55"/>
       <c r="H3" s="10"/>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="81"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="55"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+    <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="103" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="105"/>
+      <c r="J4" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="58"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1685,144 +1677,144 @@
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="57" t="s">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="59"/>
-    </row>
-    <row r="7" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="98" t="s">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="104"/>
+    </row>
+    <row r="7" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="98" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="75"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="77" t="s">
+      <c r="H7" s="73"/>
+      <c r="I7" s="105" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="106"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="78"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="26"/>
-    </row>
-    <row r="8" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="98" t="s">
+      <c r="M7" s="109"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="25"/>
+    </row>
+    <row r="8" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="99"/>
-      <c r="D8" s="63" t="str">
+      <c r="C8" s="44"/>
+      <c r="D8" s="59" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="113" t="s">
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="114"/>
-      <c r="I8" s="74" t="s">
+      <c r="H8" s="75"/>
+      <c r="I8" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="75"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="77" t="s">
+      <c r="J8" s="106"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="78"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="26"/>
-    </row>
-    <row r="9" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="98" t="s">
+      <c r="M8" s="109"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="25"/>
+    </row>
+    <row r="9" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="63" t="str">
+      <c r="C9" s="44"/>
+      <c r="D9" s="59" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="115" t="s">
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="116"/>
-      <c r="I9" s="74" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="75"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="77" t="s">
+      <c r="J9" s="106"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="78"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="26"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="98" t="s">
+      <c r="M9" s="109"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="25"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="66" t="s">
+      <c r="C10" s="44"/>
+      <c r="D10" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="87"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="109" t="s">
+      <c r="H10" s="73"/>
+      <c r="I10" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="110"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="77" t="s">
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="78"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="26"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="98" t="s">
+      <c r="M10" s="109"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="25"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="99"/>
-      <c r="D11" s="66" t="s">
+      <c r="C11" s="44"/>
+      <c r="D11" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="67"/>
-      <c r="F11" s="68"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="88"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1833,7 +1825,7 @@
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -1850,201 +1842,211 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="96" t="s">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-    </row>
-    <row r="14" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="100" t="s">
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="99"/>
+    </row>
+    <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="93" t="s">
+      <c r="D14" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="93" t="s">
-        <v>128</v>
-      </c>
-      <c r="J14" s="53" t="s">
+      <c r="I14" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="54"/>
-      <c r="L14" s="93" t="s">
+      <c r="K14" s="64"/>
+      <c r="L14" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="M14" s="53" t="s">
+      <c r="M14" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="53" t="s">
+      <c r="N14" s="63"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="Q14" s="54"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="101"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="56"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="108"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="56"/>
-    </row>
-    <row r="16" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="102"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="95"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="46"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="51"/>
+    </row>
+    <row r="16" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="50"/>
       <c r="J16" s="11" t="s">
         <v>83</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="95"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="49" t="s">
+      <c r="N16" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="O16" s="50"/>
+      <c r="O16" s="79"/>
       <c r="P16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="Q16" s="52" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="2:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="R16" s="52"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E17" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="13" t="s">
+      <c r="E17" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="41" t="s">
+      <c r="I17" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="40" t="s">
+      <c r="L17" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="51" t="s">
+      <c r="M17" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="O17" s="52"/>
-      <c r="P17" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
+      <c r="N17" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="33"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
-      <c r="E18" s="35"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="30"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="17"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
-      <c r="E19" s="35"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="12"/>
-      <c r="G19" s="30"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="17"/>
+      <c r="N19" s="110" t="s">
+        <v>132</v>
+      </c>
+      <c r="O19" s="101"/>
+      <c r="P19" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q19" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="R19" s="42"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
@@ -2064,129 +2066,129 @@
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="97" t="s">
+      <c r="B22" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="93" t="s">
+      <c r="E22" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="93" t="s">
+      <c r="F22" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62" t="s">
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62" t="s">
+      <c r="K22" s="51"/>
+      <c r="L22" s="51" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="97"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72" t="s">
+      <c r="G24" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="73"/>
-      <c r="L24" s="18" t="s">
+      <c r="K24" s="69"/>
+      <c r="L24" s="17" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="10"/>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B25" s="18"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="18"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="L25" s="17"/>
       <c r="M25" s="10"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="18"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="17"/>
       <c r="M26" s="10"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="19"/>
+      <c r="D27" s="18"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="19"/>
+      <c r="H27" s="18"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
@@ -2197,103 +2199,103 @@
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="88" t="s">
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="89"/>
-      <c r="I28" s="32" t="s">
+      <c r="H28" s="81"/>
+      <c r="I28" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="91" t="s">
+      <c r="G29" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="92"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="68"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="88"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="91" t="s">
+      <c r="G30" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="H30" s="92"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="68"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="88"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="23" t="s">
+      <c r="C31" s="21"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="22" t="s">
         <v>100</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="91" t="s">
+      <c r="G31" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="92"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="68"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="88"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="23" t="s">
+      <c r="C32" s="24"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="22" t="s">
         <v>100</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="85" t="s">
+      <c r="G32" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="86"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="55"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2313,13 +2315,13 @@
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="84"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -2332,14 +2334,14 @@
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="34"/>
+      <c r="B35" s="96" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -2351,12 +2353,12 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="34"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="97"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="30"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -2368,12 +2370,12 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="34"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="97"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="97"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2385,12 +2387,12 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="34"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -2402,12 +2404,12 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="34"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="97"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="30"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2419,16 +2421,16 @@
       <c r="P39" s="10"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
-      <c r="K40" s="19"/>
+      <c r="K40" s="18"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
@@ -2436,16 +2438,16 @@
       <c r="P40" s="10"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="19"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="18"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -2453,90 +2455,140 @@
       <c r="P41" s="10"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="19"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="18"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="77">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="I14:I16"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="C3:G3"/>
@@ -2550,69 +2602,20 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B13:Q13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="Q19:R19"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="J14:K15"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="Q16:R16"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P14:Q15"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2639,7 +2642,7 @@
   <cols>
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.28515625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" style="26" customWidth="1"/>
     <col min="4" max="4" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.7109375" bestFit="1" customWidth="1"/>
@@ -2670,7 +2673,7 @@
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="46"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2778,20 +2781,15 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="29"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2805,8 +2803,8 @@
       <c r="B19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="47" t="s">
-        <v>123</v>
+      <c r="C19" s="36" t="s">
+        <v>122</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>30</v>
@@ -2857,10 +2855,10 @@
         <v>53</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>55</v>
@@ -2872,7 +2870,7 @@
         <v>88</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>87</v>
@@ -2888,8 +2886,8 @@
       <c r="B20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="30" t="s">
-        <v>129</v>
+      <c r="C20" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -2941,10 +2939,10 @@
         <v>54</v>
       </c>
       <c r="T20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="U20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V20" t="s">
         <v>56</v>
@@ -2953,13 +2951,13 @@
         <v>62</v>
       </c>
       <c r="X20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA20" t="s">
         <v>58</v>
@@ -3396,20 +3394,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3606,6 +3590,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
   <ds:schemaRefs>
@@ -3615,16 +3613,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3641,4 +3629,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C11C3FC-06E5-4BCC-80FE-6D90FE054333}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641749B8-DA7C-49B8-AEDA-CB7746319FEB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -431,9 +431,6 @@
   </si>
   <si>
     <t>${table:offerProductValidation.NET_PRICE_VAT}</t>
-  </si>
-  <si>
-    <t>${table:offerProductValidation.NET_OFFER_PRICE}</t>
   </si>
   <si>
     <t>Total</t>
@@ -783,7 +780,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -861,18 +858,201 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,196 +1062,28 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1586,8 +1598,8 @@
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" customWidth="1"/>
     <col min="13" max="13" width="19.5703125" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" customWidth="1"/>
+    <col min="14" max="14" width="26.85546875" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="28.140625" customWidth="1"/>
     <col min="17" max="17" width="17.85546875" customWidth="1"/>
     <col min="18" max="18" width="11.85546875" customWidth="1"/>
@@ -1614,23 +1626,23 @@
       <c r="B3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="55"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="73"/>
       <c r="H3" s="10"/>
       <c r="I3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="55"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="73"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -1639,23 +1651,23 @@
       <c r="B4" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
       <c r="H4" s="10"/>
       <c r="I4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="58"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -1678,143 +1690,143 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="104"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="103"/>
     </row>
     <row r="7" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="59" t="s">
+      <c r="C7" s="43"/>
+      <c r="D7" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="43" t="s">
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="73"/>
-      <c r="I7" s="105" t="s">
+      <c r="H7" s="94"/>
+      <c r="I7" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="106"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="108" t="s">
+      <c r="J7" s="45"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="109"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="69"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
     </row>
     <row r="8" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="59" t="str">
+      <c r="C8" s="43"/>
+      <c r="D8" s="54" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="74" t="s">
+      <c r="E8" s="55"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="75"/>
-      <c r="I8" s="105" t="s">
+      <c r="H8" s="96"/>
+      <c r="I8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="106"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="108" t="s">
+      <c r="J8" s="45"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="109"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="69"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
     </row>
     <row r="9" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="59" t="str">
+      <c r="C9" s="43"/>
+      <c r="D9" s="54" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="60"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="76" t="s">
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="77"/>
-      <c r="I9" s="105" t="s">
+      <c r="H9" s="98"/>
+      <c r="I9" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="106"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="108" t="s">
+      <c r="J9" s="45"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="109"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="69"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="86" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="43" t="s">
+      <c r="E10" s="58"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="73"/>
-      <c r="I10" s="70" t="s">
+      <c r="H10" s="94"/>
+      <c r="I10" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="108" t="s">
+      <c r="J10" s="92"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="109"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="69"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="86" t="s">
+      <c r="C11" s="43"/>
+      <c r="D11" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="88"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1843,118 +1855,118 @@
       <c r="P12" s="10"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="99" t="s">
+      <c r="B13" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="99"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="99"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
     </row>
     <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="106" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="51" t="s">
         <v>110</v>
       </c>
       <c r="H14" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="48" t="s">
+      <c r="I14" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="62" t="s">
+      <c r="J14" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="64"/>
-      <c r="L14" s="48" t="s">
+      <c r="K14" s="84"/>
+      <c r="L14" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="M14" s="62" t="s">
+      <c r="M14" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="63"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="51" t="s">
+      <c r="N14" s="89"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="46"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
       <c r="H15" s="39"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="65"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="90"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
     </row>
     <row r="16" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
       <c r="H16" s="40"/>
-      <c r="I16" s="50"/>
+      <c r="I16" s="53"/>
       <c r="J16" s="11" t="s">
         <v>83</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="78" t="s">
+      <c r="N16" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="O16" s="79"/>
+      <c r="O16" s="100"/>
       <c r="P16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="Q16" s="52" t="s">
+      <c r="Q16" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="R16" s="52"/>
+      <c r="R16" s="109"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
@@ -1987,21 +1999,21 @@
       <c r="K17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="26" t="s">
+      <c r="L17" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="N17" s="26" t="s">
+      <c r="M17" s="115" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26" t="s">
+      <c r="O17" s="41"/>
+      <c r="P17" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
       <c r="S17" s="33"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.25">
@@ -2017,11 +2029,11 @@
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="111"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
       <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
+      <c r="Q18" s="104"/>
+      <c r="R18" s="105"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
@@ -2036,17 +2048,17 @@
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="110" t="s">
-        <v>132</v>
-      </c>
-      <c r="O19" s="101"/>
+      <c r="N19" s="111" t="s">
+        <v>131</v>
+      </c>
+      <c r="O19" s="112"/>
       <c r="P19" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="Q19" s="41" t="s">
+      <c r="Q19" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="R19" s="42"/>
+      <c r="R19" s="105"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
@@ -2066,63 +2078,63 @@
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="99" t="s">
+      <c r="B21" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="99"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="100" t="s">
+      <c r="B22" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="51" t="s">
+      <c r="G22" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51" t="s">
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51" t="s">
+      <c r="K22" s="65"/>
+      <c r="L22" s="65" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="100"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
@@ -2139,15 +2151,15 @@
       <c r="F24" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="95" t="s">
+      <c r="G24" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="68" t="s">
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="69"/>
+      <c r="K24" s="70"/>
       <c r="L24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2159,11 +2171,11 @@
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
       <c r="L25" s="17"/>
       <c r="M25" s="10"/>
     </row>
@@ -2173,11 +2185,11 @@
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
       <c r="L26" s="17"/>
       <c r="M26" s="10"/>
     </row>
@@ -2199,17 +2211,17 @@
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="98" t="s">
+      <c r="B28" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
       <c r="F28" s="19"/>
-      <c r="G28" s="80" t="s">
+      <c r="G28" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="81"/>
+      <c r="H28" s="80"/>
       <c r="I28" s="28" t="s">
         <v>94</v>
       </c>
@@ -2224,17 +2236,17 @@
         <v>95</v>
       </c>
       <c r="C29" s="21"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="84" t="s">
+      <c r="G29" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="85"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="59"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2243,17 +2255,17 @@
         <v>97</v>
       </c>
       <c r="C30" s="21"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="84" t="s">
+      <c r="G30" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="H30" s="85"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="59"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2267,14 +2279,14 @@
         <v>100</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="85"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="59"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2288,14 +2300,14 @@
         <v>100</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="92" t="s">
+      <c r="G32" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="93"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="55"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2315,13 +2327,13 @@
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -2334,13 +2346,13 @@
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
       <c r="G35" s="30"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -2353,11 +2365,11 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="97"/>
-      <c r="C36" s="97"/>
-      <c r="D36" s="97"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="97"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
       <c r="G36" s="30"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -2370,11 +2382,11 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="97"/>
-      <c r="C37" s="97"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
       <c r="G37" s="30"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -2387,11 +2399,11 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="97"/>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
       <c r="G38" s="30"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
@@ -2404,11 +2416,11 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="97"/>
-      <c r="C39" s="97"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="97"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
       <c r="G39" s="30"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
@@ -2538,14 +2550,63 @@
       <c r="G49" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
+  <mergeCells count="79">
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="M14:O15"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J22:K23"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
@@ -2562,60 +2623,13 @@
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="J14:K15"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="M14:O15"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:R13"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2935,10 +2949,10 @@
         <f>IF(E20&gt;0,IF(E20="Unit",CONCATENATE(Settings!Q20," ",Settings!E20,"s"),CONCATENATE((Settings!Q20/Settings!M20)," ",Settings!E20,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T20" s="9" t="s">
         <v>130</v>
       </c>
       <c r="U20" t="s">
@@ -3394,6 +3408,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3590,20 +3618,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
   <ds:schemaRefs>
@@ -3613,6 +3627,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3629,14 +3653,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641749B8-DA7C-49B8-AEDA-CB7746319FEB}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFA8F3B-8E67-4FC0-B970-36BA47AA0A77}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -780,7 +780,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -861,12 +861,223 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -875,216 +1086,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1626,23 +1627,23 @@
       <c r="B3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="73"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
       <c r="H3" s="10"/>
       <c r="I3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="73"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="69"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -1651,23 +1652,23 @@
       <c r="B4" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="75"/>
       <c r="H4" s="10"/>
       <c r="I4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="86" t="s">
+      <c r="J4" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="88"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -1690,143 +1691,143 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="103"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="94"/>
     </row>
     <row r="7" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="54" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="42" t="s">
+      <c r="E7" s="74"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="94"/>
-      <c r="I7" s="44" t="s">
+      <c r="H7" s="85"/>
+      <c r="I7" s="115" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="47" t="s">
+      <c r="J7" s="116"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="70"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="63"/>
       <c r="P7" s="25"/>
     </row>
     <row r="8" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="54" t="str">
+      <c r="C8" s="49"/>
+      <c r="D8" s="73" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="95" t="s">
+      <c r="E8" s="74"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="44" t="s">
+      <c r="H8" s="87"/>
+      <c r="I8" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="45"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="47" t="s">
+      <c r="J8" s="116"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="70"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="63"/>
       <c r="P8" s="25"/>
     </row>
     <row r="9" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="54" t="str">
+      <c r="C9" s="49"/>
+      <c r="D9" s="73" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="97" t="s">
+      <c r="E9" s="74"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="44" t="s">
+      <c r="H9" s="89"/>
+      <c r="I9" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="45"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="47" t="s">
+      <c r="J9" s="116"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="48"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="70"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="63"/>
       <c r="P9" s="25"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="57" t="s">
+      <c r="C10" s="49"/>
+      <c r="D10" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="42" t="s">
+      <c r="E10" s="96"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="94"/>
-      <c r="I10" s="91" t="s">
+      <c r="H10" s="85"/>
+      <c r="I10" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="92"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="47" t="s">
+      <c r="J10" s="83"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="48"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="70"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="63"/>
       <c r="P10" s="25"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="57" t="s">
+      <c r="C11" s="49"/>
+      <c r="D11" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="59"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="97"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1855,118 +1856,118 @@
       <c r="P12" s="10"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
     </row>
     <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106" t="s">
+      <c r="B14" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="53" t="s">
         <v>110</v>
       </c>
       <c r="H14" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="51" t="s">
+      <c r="I14" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="63" t="s">
+      <c r="J14" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="84"/>
-      <c r="L14" s="51" t="s">
+      <c r="K14" s="78"/>
+      <c r="L14" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="M14" s="63" t="s">
+      <c r="M14" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="89"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="65" t="s">
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="107"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
       <c r="H15" s="39"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
     </row>
     <row r="16" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="108"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
       <c r="H16" s="40"/>
-      <c r="I16" s="53"/>
+      <c r="I16" s="55"/>
       <c r="J16" s="11" t="s">
         <v>83</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="55"/>
       <c r="M16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="99" t="s">
+      <c r="N16" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="O16" s="100"/>
+      <c r="O16" s="91"/>
       <c r="P16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="Q16" s="109" t="s">
+      <c r="Q16" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="R16" s="109"/>
+      <c r="R16" s="58"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
@@ -1999,21 +2000,21 @@
       <c r="K17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="113" t="s">
+      <c r="L17" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="115" t="s">
+      <c r="M17" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="116" t="s">
+      <c r="N17" s="44" t="s">
         <v>130</v>
       </c>
       <c r="O17" s="41"/>
-      <c r="P17" s="113" t="s">
+      <c r="P17" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
       <c r="S17" s="33"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.25">
@@ -2029,11 +2030,11 @@
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
       <c r="P18" s="26"/>
-      <c r="Q18" s="104"/>
-      <c r="R18" s="105"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="47"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
@@ -2048,17 +2049,17 @@
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="111" t="s">
+      <c r="N19" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="O19" s="112"/>
+      <c r="O19" s="61"/>
       <c r="P19" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="Q19" s="104" t="s">
+      <c r="Q19" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="R19" s="105"/>
+      <c r="R19" s="47"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
@@ -2078,63 +2079,63 @@
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="61"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="114" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="65" t="s">
+      <c r="G22" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65" t="s">
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65" t="s">
+      <c r="K22" s="57"/>
+      <c r="L22" s="57" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="62"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
@@ -2151,15 +2152,15 @@
       <c r="F24" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="108" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="69" t="s">
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="70"/>
+      <c r="K24" s="63"/>
       <c r="L24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2171,11 +2172,11 @@
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
       <c r="L25" s="17"/>
       <c r="M25" s="10"/>
     </row>
@@ -2185,11 +2186,11 @@
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="107"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
       <c r="L26" s="17"/>
       <c r="M26" s="10"/>
     </row>
@@ -2211,17 +2212,17 @@
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="113" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
       <c r="F28" s="19"/>
-      <c r="G28" s="79" t="s">
+      <c r="G28" s="109" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="80"/>
+      <c r="H28" s="110"/>
       <c r="I28" s="28" t="s">
         <v>94</v>
       </c>
@@ -2236,17 +2237,17 @@
         <v>95</v>
       </c>
       <c r="C29" s="21"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="82" t="s">
+      <c r="G29" s="105" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="83"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="59"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="97"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2255,17 +2256,17 @@
         <v>97</v>
       </c>
       <c r="C30" s="21"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="82" t="s">
+      <c r="G30" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="H30" s="83"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="59"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="97"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2279,14 +2280,14 @@
         <v>100</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="83"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="59"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="97"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2300,14 +2301,14 @@
         <v>100</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="77" t="s">
+      <c r="G32" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="78"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="73"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="69"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2327,13 +2328,13 @@
       <c r="P33" s="10"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="100"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -2346,13 +2347,13 @@
       <c r="P34" s="10"/>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
       <c r="G35" s="30"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -2365,11 +2366,11 @@
       <c r="P35" s="10"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
+      <c r="B36" s="112"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="112"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
       <c r="G36" s="30"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -2382,11 +2383,11 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="30"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -2399,11 +2400,11 @@
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="112"/>
+      <c r="D38" s="112"/>
+      <c r="E38" s="112"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="30"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
@@ -2416,11 +2417,11 @@
       <c r="P38" s="10"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
       <c r="G39" s="30"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
@@ -2551,19 +2552,56 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:R13"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="I14:I16"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="C3:G3"/>
@@ -2580,56 +2618,19 @@
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="B6:O6"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="J14:K15"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2949,13 +2950,13 @@
         <f>IF(E20&gt;0,IF(E20="Unit",CONCATENATE(Settings!Q20," ",Settings!E20,"s"),CONCATENATE((Settings!Q20/Settings!M20)," ",Settings!E20,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="S20" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="T20" s="9" t="s">
+      <c r="T20" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="U20" t="s">
+      <c r="U20" s="45" t="s">
         <v>113</v>
       </c>
       <c r="V20" t="s">
@@ -3387,7 +3388,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
@@ -3408,20 +3409,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3618,6 +3605,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
   <ds:schemaRefs>
@@ -3627,16 +3628,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3653,4 +3644,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFA8F3B-8E67-4FC0-B970-36BA47AA0A77}"/>
+  <xr:revisionPtr revIDLastSave="665" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{737E030B-9C41-441E-88FF-D2B2D9EC2958}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="130">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -79,9 +79,6 @@
     <t>FOC</t>
   </si>
   <si>
-    <t>NSP</t>
-  </si>
-  <si>
     <t>${offerValidation.OFFERID}</t>
   </si>
   <si>
@@ -278,10 +275,6 @@
   </si>
   <si>
     <t>Product Generic Name</t>
-  </si>
-  <si>
-    <t>FOC/
-Discount</t>
   </si>
   <si>
     <t>Total Offer Value</t>
@@ -545,7 +538,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -570,8 +563,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -700,17 +699,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -726,17 +714,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -765,22 +742,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -803,7 +770,6 @@
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -849,249 +815,207 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -1163,75 +1087,63 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>148166</xdr:colOff>
+      <xdr:colOff>95249</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>116416</xdr:rowOff>
+      <xdr:rowOff>105833</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1519766</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>154516</xdr:rowOff>
+      <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3F11885-C9F0-4058-833F-C71676B7D676}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44BD9831-3539-F32F-2D10-1E8D489D4C1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="14668499" y="116416"/>
-          <a:ext cx="1371600" cy="1371600"/>
+          <a:off x="19557999" y="105833"/>
+          <a:ext cx="2636309" cy="1357842"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:blipFill dpi="0" rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </a:blipFill>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fLocksWithSheet="0"/>
+    </xdr:pic>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -1584,29 +1496,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:S49"/>
+  <dimension ref="B2:P49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" customWidth="1"/>
-    <col min="14" max="14" width="26.85546875" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="28.140625" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" customWidth="1"/>
-    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="14" max="14" width="26.7109375" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1621,59 +1530,56 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="69"/>
+      <c r="J3" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75"/>
+    </row>
+    <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="72"/>
+      <c r="I4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="57"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1688,146 +1594,141 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="92" t="s">
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="67"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="94"/>
-    </row>
-    <row r="7" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="48" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="91" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="91"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="73" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="74"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="48" t="s">
+      <c r="H7" s="95"/>
+      <c r="I7" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="88"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="85"/>
-      <c r="I7" s="115" t="s">
-        <v>119</v>
-      </c>
-      <c r="J7" s="116"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="64" t="s">
+      <c r="M7" s="50"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+    </row>
+    <row r="8" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="65"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="25"/>
-    </row>
-    <row r="8" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="73" t="str">
+      <c r="C8" s="39"/>
+      <c r="D8" s="91" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="86" t="s">
+      <c r="E8" s="91"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="96"/>
+      <c r="I8" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="88"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="87"/>
-      <c r="I8" s="115" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="116"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="64" t="s">
+      <c r="M8" s="50"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="77"/>
+    </row>
+    <row r="9" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="25"/>
-    </row>
-    <row r="9" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="73" t="str">
+      <c r="C9" s="39"/>
+      <c r="D9" s="58" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="88" t="s">
+      <c r="E9" s="60"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="89"/>
-      <c r="I9" s="115" t="s">
+      <c r="H9" s="97"/>
+      <c r="I9" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="88"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="50"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="39"/>
+      <c r="D10" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="70"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="98" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="98"/>
+      <c r="I10" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="63"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="50"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="77"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="116"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="65"/>
-      <c r="N9" s="62"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="25"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="96"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="85"/>
-      <c r="I10" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="83"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M10" s="65"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="25"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="96"/>
-      <c r="F11" s="97"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="94"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1838,7 +1739,7 @@
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -1853,215 +1754,181 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="56" t="s">
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-    </row>
-    <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="50" t="s">
+      <c r="C14" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="D14" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="E14" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="F14" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="76" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="78"/>
-      <c r="L14" s="53" t="s">
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="87"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+    </row>
+    <row r="16" spans="2:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="87"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="M14" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="N14" s="77"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="57" t="s">
+      <c r="K16" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="57"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="51"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="57"/>
-      <c r="R15" s="57"/>
-    </row>
-    <row r="16" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="52"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="55"/>
+      <c r="L16" s="45"/>
       <c r="M16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="N16" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="O16" s="91"/>
-      <c r="P16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q16" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="R16" s="58"/>
-    </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O16" s="45"/>
+    </row>
+    <row r="17" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="90" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="I17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="51"/>
+      <c r="M17" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="O17" s="41"/>
-      <c r="P17" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="33"/>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="N17" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="101"/>
+      <c r="P17" s="32"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
-      <c r="E18" s="31"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="26"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="47"/>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
-      <c r="E19" s="31"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="12"/>
-      <c r="G19" s="26"/>
+      <c r="G19" s="25"/>
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="O19" s="61"/>
-      <c r="P19" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q19" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="R19" s="47"/>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="K19" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="L19" s="103"/>
+      <c r="M19" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="O19" s="51"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -2076,132 +1943,131 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-    </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="56" t="s">
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="87" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" s="114" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="76" t="s">
+      <c r="F22" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="G22" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="57" t="s">
+      <c r="K22" s="44"/>
+      <c r="L22" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57" t="s">
-        <v>91</v>
-      </c>
       <c r="M22" s="10"/>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B23" s="114"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="87"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="42"/>
       <c r="M23" s="10"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="108" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="63"/>
-      <c r="L24" s="17" t="s">
-        <v>26</v>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="K24" s="48"/>
+      <c r="L24" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="M24" s="10"/>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B25" s="17"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="17"/>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="16"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="17"/>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="77"/>
+      <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="18"/>
+      <c r="D27" s="17"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
@@ -2209,108 +2075,107 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="113" t="s">
+    </row>
+    <row r="28" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="83"/>
+      <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="113"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="113"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="109" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="110"/>
-      <c r="I28" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B29" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="105" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" s="106"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="97"/>
+      <c r="G29" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="79"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="70"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B30" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="105" t="s">
-        <v>98</v>
-      </c>
-      <c r="H30" s="106"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="97"/>
+      <c r="G30" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="79"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="70"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="20" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="106"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="97"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="70"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B32" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="22" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
         <v>100</v>
       </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="101" t="s">
-        <v>103</v>
-      </c>
-      <c r="H32" s="102"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="68"/>
-      <c r="L32" s="69"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G32" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="75"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="54"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -2325,16 +2190,15 @@
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
       <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="98" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="99"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="100"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B34" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="73"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -2344,17 +2208,16 @@
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
       <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-    </row>
-    <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="30"/>
+    </row>
+    <row r="35" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="84" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="29"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -2363,15 +2226,14 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
       <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="30"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="85"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="29"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -2380,15 +2242,14 @@
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
       <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="30"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="29"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2397,15 +2258,14 @@
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
       <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="112"/>
-      <c r="C38" s="112"/>
-      <c r="D38" s="112"/>
-      <c r="E38" s="112"/>
-      <c r="F38" s="112"/>
-      <c r="G38" s="30"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="29"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -2414,15 +2274,14 @@
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="30"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="29"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2431,127 +2290,124 @@
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
       <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
-      <c r="K40" s="18"/>
+      <c r="K40" s="17"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
       <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="18"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="17"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
       <c r="K42" s="10"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="18"/>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="17"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="79">
+  <mergeCells count="78">
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
@@ -2559,16 +2415,16 @@
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I9:K9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="B35:F39"/>
     <mergeCell ref="E14:E16"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="B21:L21"/>
@@ -2599,9 +2455,13 @@
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="L22:L23"/>
     <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="J14:K15"/>
     <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H14:H16"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="C3:G3"/>
@@ -2612,25 +2472,20 @@
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="N16:O16"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="B6:O6"/>
-    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="N19:O19"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:R13"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="B13:O13"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="L10:M10"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="N17:O17"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2657,7 +2512,7 @@
   <cols>
     <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.28515625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" style="25" customWidth="1"/>
     <col min="4" max="4" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.7109375" bestFit="1" customWidth="1"/>
@@ -2683,16 +2538,16 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="35"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -2700,7 +2555,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -2708,7 +2563,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -2716,7 +2571,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -2724,7 +2579,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -2732,7 +2587,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -2740,7 +2595,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -2756,97 +2611,97 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B17" s="34"/>
-      <c r="C17" s="29"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>122</v>
+      <c r="C19" s="35" t="s">
+        <v>120</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>9</v>
@@ -2861,121 +2716,121 @@
         <v>13</v>
       </c>
       <c r="Q19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="T19" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" t="s">
-        <v>42</v>
-      </c>
-      <c r="L20" t="s">
-        <v>44</v>
-      </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>24</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>25</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>26</v>
       </c>
-      <c r="P20" t="s">
-        <v>27</v>
-      </c>
       <c r="Q20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R20" t="e">
         <f>IF(E20&gt;0,IF(E20="Unit",CONCATENATE(Settings!Q20," ",Settings!E20,"s"),CONCATENATE((Settings!Q20/Settings!M20)," ",Settings!E20,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S20" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="T20" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="U20" s="45" t="s">
-        <v>113</v>
+      <c r="S20" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="T20" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="U20" s="37" t="s">
+        <v>111</v>
       </c>
       <c r="V20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X20" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y20" t="s">
         <v>124</v>
       </c>
-      <c r="Y20" t="s">
-        <v>126</v>
-      </c>
       <c r="Z20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
@@ -3400,15 +3255,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3605,7 +3451,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
@@ -3619,15 +3465,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3646,7 +3493,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3654,4 +3501,12 @@
     <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="665" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{737E030B-9C41-441E-88FF-D2B2D9EC2958}"/>
+  <xr:revisionPtr revIDLastSave="687" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BA4863-7F57-4116-8700-E674655548D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -32,6 +32,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -742,12 +764,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -816,38 +858,212 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -855,161 +1071,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1082,74 +1150,70 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>105833</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>130175</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44BD9831-3539-F32F-2D10-1E8D489D4C1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="19557999" y="105833"/>
-          <a:ext cx="2636309" cy="1357842"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+    <v>image</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,7 +1560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:P49"/>
+  <dimension ref="B2:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1512,10 +1576,9 @@
     <col min="12" max="12" width="12.5703125" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
     <col min="14" max="14" width="26.7109375" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1529,57 +1592,54 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="73"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="54"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="73"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="55"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="55" t="s">
+      <c r="J4" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="57"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="95"/>
       <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1593,142 +1653,136 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="67"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="38" t="s">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="104"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="91" t="s">
+      <c r="C7" s="110"/>
+      <c r="D7" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="95" t="s">
+      <c r="E7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="95"/>
-      <c r="I7" s="88" t="s">
+      <c r="H7" s="44"/>
+      <c r="I7" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="88"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="49" t="s">
+      <c r="J7" s="48"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="50"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-    </row>
-    <row r="8" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="M7" s="106"/>
+      <c r="N7" s="45"/>
+    </row>
+    <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="91" t="str">
+      <c r="C8" s="47"/>
+      <c r="D8" s="53" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="96" t="s">
+      <c r="E8" s="53"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="88" t="s">
+      <c r="H8" s="99"/>
+      <c r="I8" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="49" t="s">
+      <c r="J8" s="50"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="50"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-    </row>
-    <row r="9" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="38" t="s">
+      <c r="M8" s="108"/>
+      <c r="N8" s="40"/>
+    </row>
+    <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="58" t="str">
+      <c r="C9" s="47"/>
+      <c r="D9" s="54" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="60"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="97" t="s">
+      <c r="E9" s="55"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="97"/>
-      <c r="I9" s="88" t="s">
+      <c r="H9" s="100"/>
+      <c r="I9" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="88"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="49" t="s">
+      <c r="J9" s="50"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="50"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="77"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="38" t="s">
+      <c r="M9" s="108"/>
+      <c r="N9" s="40"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="47"/>
+      <c r="D10" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="57"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="98"/>
-      <c r="I10" s="63" t="s">
+      <c r="H10" s="101"/>
+      <c r="I10" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="49" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="50"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="38" t="s">
+      <c r="M10" s="108"/>
+      <c r="N10" s="40"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="94"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1737,9 +1791,8 @@
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -1753,113 +1806,108 @@
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="102" t="s">
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="87" t="s">
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="44" t="s">
+      <c r="J14" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44" t="s">
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="87"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-    </row>
-    <row r="16" spans="2:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="87"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="44"/>
+      <c r="N14" s="59"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="61"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="59"/>
+      <c r="N15" s="59"/>
+    </row>
+    <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="61"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="59"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="45" t="s">
+      <c r="K16" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="45"/>
+      <c r="L16" s="88"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="N16" s="45" t="s">
+      <c r="N16" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="O16" s="45"/>
-    </row>
-    <row r="17" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="90" t="s">
+      <c r="D17" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="E17" s="41" t="s">
         <v>126</v>
       </c>
       <c r="F17" s="25" t="s">
@@ -1877,20 +1925,19 @@
       <c r="J17" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="51" t="s">
+      <c r="K17" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="51"/>
-      <c r="M17" s="100" t="s">
+      <c r="L17" s="89"/>
+      <c r="M17" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="101" t="s">
+      <c r="N17" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="O17" s="101"/>
-      <c r="P17" s="32"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O17" s="32"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -1900,13 +1947,12 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N18" s="38"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1916,19 +1962,18 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="103" t="s">
+      <c r="K19" s="91" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="103"/>
+      <c r="L19" s="91"/>
       <c r="M19" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="51" t="s">
+      <c r="N19" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="O19" s="51"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -1942,69 +1987,68 @@
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
       <c r="M21" s="10"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="87" t="s">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44" t="s">
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="44"/>
-      <c r="L22" s="40" t="s">
+      <c r="K22" s="59"/>
+      <c r="L22" s="64" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="87"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="42"/>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="65"/>
       <c r="M23" s="10"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>43</v>
       </c>
@@ -2012,55 +2056,55 @@
         <v>22</v>
       </c>
       <c r="D24" s="25"/>
-      <c r="E24" s="16" t="s">
-        <v>121</v>
+      <c r="E24" s="40" t="s">
+        <v>124</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="81" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="47" t="s">
+      <c r="G24" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="48"/>
+      <c r="K24" s="76"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
       <c r="M24" s="10"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="16"/>
       <c r="C25" s="36"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="16"/>
       <c r="C26" s="36"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="77"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="17"/>
@@ -2074,20 +2118,19 @@
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="86" t="s">
+    </row>
+    <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="82" t="s">
+      <c r="G28" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="83"/>
+      <c r="H28" s="69"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2097,45 +2140,45 @@
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="78" t="s">
+      <c r="G29" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="79"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="70"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="57"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="78" t="s">
+      <c r="G30" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="79"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="70"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="57"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>97</v>
       </c>
@@ -2145,18 +2188,18 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="78" t="s">
+      <c r="G31" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="79"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="70"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="57"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
         <v>100</v>
       </c>
@@ -2166,16 +2209,16 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="74" t="s">
+      <c r="G32" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="75"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="54"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H32" s="81"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -2189,164 +2232,158 @@
       <c r="L33" s="10"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="71" t="s">
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B34" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="73"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="79"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
+      <c r="H34" s="85" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-    </row>
-    <row r="35" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="84" t="s">
+    </row>
+    <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="85"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="85"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="85"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B38" s="87"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
       <c r="D40" s="29"/>
       <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="29"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="17"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
       <c r="G41" s="29"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="17"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
       <c r="G42" s="29"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
       <c r="K42" s="10"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
       <c r="G43" s="29"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
@@ -2357,7 +2394,7 @@
       <c r="I44" s="24"/>
       <c r="J44" s="24"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
@@ -2368,7 +2405,7 @@
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
@@ -2379,7 +2416,7 @@
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
@@ -2390,7 +2427,7 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="D48" s="29"/>
@@ -2407,8 +2444,67 @@
       <c r="G49" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="71">
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="M14:N15"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="E14:E16"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="H34:J41"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B11:C11"/>
@@ -2420,72 +2516,6 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="M14:O15"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:O13"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N17:O17"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2495,12 +2525,14 @@
       <formula1>"Days (วัน), Months (เดือน), Years (ปี)"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H34" r:id="rId1" display="Picture1.png" xr:uid="{8A2AAFAF-E3BA-4662-8D09-F4BA07D9B9BA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3452,6 +3484,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
@@ -3463,15 +3504,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3494,6 +3526,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3501,12 +3541,4 @@
     <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="687" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BA4863-7F57-4116-8700-E674655548D2}"/>
+  <xr:revisionPtr revIDLastSave="701" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3328E643-C3C1-4356-99A1-8825AF896200}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -592,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -713,17 +713,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -789,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -845,9 +834,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -856,7 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -876,11 +861,116 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -888,19 +978,25 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -912,125 +1008,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1059,26 +1044,11 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1148,6 +1118,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1597,46 +1571,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="73"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="73"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="63"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="55"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="90"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="95"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="66"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1655,133 +1629,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="104"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="102"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="52" t="s">
+      <c r="C7" s="78"/>
+      <c r="D7" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="44" t="s">
+      <c r="E7" s="87"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="48" t="s">
+      <c r="H7" s="42"/>
+      <c r="I7" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="48"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="105" t="s">
+      <c r="J7" s="83"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="106"/>
-      <c r="N7" s="45"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="53" t="str">
+      <c r="C8" s="80"/>
+      <c r="D8" s="88" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="53"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="99" t="s">
+      <c r="E8" s="88"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="99"/>
-      <c r="I8" s="50" t="s">
+      <c r="H8" s="97"/>
+      <c r="I8" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="107" t="s">
+      <c r="J8" s="85"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="108"/>
-      <c r="N8" s="40"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="54" t="str">
+      <c r="C9" s="80"/>
+      <c r="D9" s="89" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="100" t="s">
+      <c r="E9" s="90"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="100"/>
-      <c r="I9" s="50" t="s">
+      <c r="H9" s="98"/>
+      <c r="I9" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="50"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="107" t="s">
+      <c r="J9" s="85"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="108"/>
-      <c r="N9" s="40"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="80"/>
       <c r="D10" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="57"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="101" t="s">
+      <c r="G10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="101"/>
-      <c r="I10" s="97" t="s">
+      <c r="H10" s="99"/>
+      <c r="I10" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="107" t="s">
+      <c r="J10" s="95"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="108"/>
-      <c r="N10" s="40"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="47"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="57"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1808,88 +1782,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="91"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="64" t="s">
+      <c r="H14" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="59" t="s">
+      <c r="I14" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="59" t="s">
+      <c r="J14" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59" t="s">
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="59"/>
+      <c r="N14" s="46"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="61"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="61"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="59"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="46"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="88" t="s">
+      <c r="K16" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="88"/>
+      <c r="L16" s="55"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1904,10 +1878,10 @@
       <c r="C17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="39" t="s">
         <v>126</v>
       </c>
       <c r="F17" s="25" t="s">
@@ -1925,17 +1899,17 @@
       <c r="J17" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="89" t="s">
+      <c r="K17" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="89"/>
-      <c r="M17" s="43" t="s">
+      <c r="L17" s="81"/>
+      <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="43" t="s">
+      <c r="N17" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="O17" s="32"/>
+      <c r="O17" s="31"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
@@ -1947,10 +1921,10 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="38"/>
+      <c r="N18" s="36"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
@@ -1962,14 +1936,14 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="91" t="s">
+      <c r="K19" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="91"/>
-      <c r="M19" s="25" t="s">
+      <c r="L19" s="59"/>
+      <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="N19" s="37" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1989,88 +1963,88 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59" t="s">
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="59"/>
-      <c r="L22" s="64" t="s">
+      <c r="K22" s="46"/>
+      <c r="L22" s="46" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="61"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="65"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="40" t="s">
+      <c r="D24" s="37"/>
+      <c r="E24" s="38" t="s">
         <v>124</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="74" t="s">
+      <c r="G24" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="75" t="s">
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="76"/>
+      <c r="K24" s="52"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
@@ -2078,29 +2052,29 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="16"/>
-      <c r="C25" s="36"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="16"/>
-      <c r="C26" s="36"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
@@ -2120,17 +2094,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="68" t="s">
+      <c r="G28" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="69"/>
+      <c r="H28" s="54"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2145,17 +2119,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="83" t="s">
+      <c r="G29" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="84"/>
+      <c r="H29" s="74"/>
       <c r="I29" s="56"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="58"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2164,17 +2138,17 @@
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="83" t="s">
+      <c r="G30" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="84"/>
+      <c r="H30" s="74"/>
       <c r="I30" s="56"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="58"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2188,14 +2162,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="83" t="s">
+      <c r="G31" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="84"/>
+      <c r="H31" s="74"/>
       <c r="I31" s="56"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="58"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2209,14 +2183,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="80" t="s">
+      <c r="G32" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="81"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="73"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="63"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2234,100 +2208,76 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="79"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="69"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="85" t="e" vm="1">
+      <c r="H34" s="44" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
-      <c r="D36" s="87"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="87"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="85"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="85"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2336,13 +2286,9 @@
       <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="29"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="29"/>
@@ -2351,13 +2297,9 @@
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
       <c r="G41" s="29"/>
-      <c r="H41" s="85"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" s="29"/>
@@ -2445,9 +2387,6 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="L10:M10"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="F14:F16"/>
@@ -2461,13 +2400,22 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="E14:E16"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="B34:F34"/>
@@ -2477,11 +2425,14 @@
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="G30:H30"/>
-    <mergeCell ref="H34:J41"/>
     <mergeCell ref="I30:L30"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="I29:L29"/>
     <mergeCell ref="J22:K23"/>
     <mergeCell ref="G26:I26"/>
@@ -2489,6 +2440,9 @@
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="L22:L23"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="H34:J39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="B21:L21"/>
@@ -2504,18 +2458,6 @@
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="I14:I16"/>
     <mergeCell ref="J14:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2525,11 +2467,8 @@
       <formula1>"Days (วัน), Months (เดือน), Years (ปี)"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="H34" r:id="rId1" display="Picture1.png" xr:uid="{8A2AAFAF-E3BA-4662-8D09-F4BA07D9B9BA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
@@ -2575,7 +2514,7 @@
       <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="34"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2690,7 +2629,7 @@
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -2705,7 +2644,7 @@
       <c r="B19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="34" t="s">
         <v>120</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2837,13 +2776,13 @@
         <f>IF(E20&gt;0,IF(E20="Unit",CONCATENATE(Settings!Q20," ",Settings!E20,"s"),CONCATENATE((Settings!Q20/Settings!M20)," ",Settings!E20,"s")),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S20" s="37" t="s">
+      <c r="S20" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="T20" s="37" t="s">
+      <c r="T20" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="U20" s="37" t="s">
+      <c r="U20" s="35" t="s">
         <v>111</v>
       </c>
       <c r="V20" t="s">

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="701" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3328E643-C3C1-4356-99A1-8825AF896200}"/>
+  <xr:revisionPtr revIDLastSave="744" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6687FCF-85C2-4609-9F31-BEAC31927B96}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="131">
   <si>
     <t>${offerValidation.INSTITUTENAME}</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>${table:offerProductValidation.PRESENTATION_2}</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -747,15 +750,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -778,7 +772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -867,188 +861,206 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1571,36 +1583,36 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="61" t="s">
+      <c r="J3" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="63"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="C4" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="90"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
@@ -1629,133 +1641,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101"/>
-      <c r="L6" s="101"/>
-      <c r="M6" s="101"/>
-      <c r="N6" s="102"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="59"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="87" t="s">
+      <c r="C7" s="71"/>
+      <c r="D7" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="87"/>
+      <c r="E7" s="81"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="83" t="s">
+      <c r="I7" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="83"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="103" t="s">
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="104"/>
+      <c r="M7" s="61"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="80"/>
-      <c r="D8" s="88" t="str">
+      <c r="C8" s="73"/>
+      <c r="D8" s="82" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="88"/>
+      <c r="E8" s="82"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="97" t="s">
+      <c r="G8" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="85" t="s">
+      <c r="H8" s="54"/>
+      <c r="I8" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="85"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="92" t="s">
+      <c r="J8" s="79"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="93"/>
+      <c r="M8" s="63"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="89" t="str">
+      <c r="C9" s="73"/>
+      <c r="D9" s="48" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="90"/>
+      <c r="E9" s="50"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="98" t="s">
+      <c r="G9" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="85" t="s">
+      <c r="H9" s="55"/>
+      <c r="I9" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="92" t="s">
+      <c r="J9" s="79"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="93"/>
+      <c r="M9" s="63"/>
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="56" t="s">
+      <c r="C10" s="73"/>
+      <c r="D10" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="58"/>
+      <c r="E10" s="84"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="99" t="s">
+      <c r="G10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="99"/>
-      <c r="I10" s="95" t="s">
+      <c r="H10" s="56"/>
+      <c r="I10" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="92" t="s">
+      <c r="J10" s="52"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="93"/>
+      <c r="M10" s="63"/>
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="56" t="s">
+      <c r="C11" s="73"/>
+      <c r="D11" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="58"/>
+      <c r="E11" s="84"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1782,88 +1794,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="46" t="s">
+      <c r="I14" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="46" t="s">
+      <c r="J14" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46" t="s">
+      <c r="K14" s="51"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="46"/>
+      <c r="N14" s="51"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="46"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="51"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="55" t="s">
+      <c r="K16" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="55"/>
+      <c r="L16" s="98"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1899,10 +1911,10 @@
       <c r="J17" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="81" t="s">
+      <c r="K17" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="81"/>
+      <c r="L17" s="75"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1921,8 +1933,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1936,10 +1948,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="59" t="s">
+      <c r="K19" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="59"/>
+      <c r="L19" s="100"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1963,88 +1975,90 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="102"/>
+      <c r="L21" s="102"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E22" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="F22" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46" t="s">
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46" t="s">
+      <c r="K22" s="51"/>
+      <c r="L22" s="51" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="48"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
       <c r="M23" s="10"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="37"/>
+      <c r="D24" s="44" t="s">
+        <v>130</v>
+      </c>
       <c r="E24" s="38" t="s">
         <v>124</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G24" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52" t="s">
+      <c r="H24" s="107"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="52"/>
+      <c r="K24" s="91"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
@@ -2056,11 +2070,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="52"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
@@ -2070,11 +2084,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
@@ -2094,17 +2108,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="53" t="s">
+      <c r="G28" s="103" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="54"/>
+      <c r="H28" s="104"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2119,17 +2133,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="73" t="s">
+      <c r="G29" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="74"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="58"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="84"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2138,17 +2152,17 @@
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="91"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="74"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="58"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="84"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2162,14 +2176,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="73" t="s">
+      <c r="G31" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="74"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="58"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="84"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2183,14 +2197,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="71"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="63"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="47"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2208,76 +2222,76 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="87"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="44" t="e" vm="1">
+      <c r="H34" s="94" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
+      <c r="B35" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="94"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="44"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="94"/>
+      <c r="J36" s="94"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="76"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="44"/>
+      <c r="H37" s="94"/>
+      <c r="I37" s="94"/>
+      <c r="J37" s="94"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="76"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="95"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="44"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="94"/>
+      <c r="J38" s="94"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="76"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="44"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="94"/>
+      <c r="J39" s="94"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2387,6 +2401,61 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="H34:J39"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="F14:F16"/>
@@ -2400,64 +2469,9 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="E14:E16"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="J4:M4"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="K19:L19"/>
     <mergeCell ref="H14:H16"/>
-    <mergeCell ref="H34:J39"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:L15"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -3226,6 +3240,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3422,30 +3459,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3462,22 +3494,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="744" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6687FCF-85C2-4609-9F31-BEAC31927B96}"/>
+  <xr:revisionPtr revIDLastSave="761" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC6B85E-805A-4A0F-AC84-A7CE4808D1D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -772,7 +772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1011,9 +1011,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1038,30 +1035,25 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1794,21 +1786,21 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
@@ -1872,10 +1864,10 @@
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="98" t="s">
+      <c r="K16" s="97" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="98"/>
+      <c r="L16" s="97"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1896,19 +1888,19 @@
       <c r="E17" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
       <c r="K17" s="75" t="s">
@@ -1948,10 +1940,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="100" t="s">
+      <c r="K19" s="99" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="100"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1975,19 +1967,19 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
@@ -2050,11 +2042,11 @@
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="105" t="s">
+      <c r="G24" s="91" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="107"/>
-      <c r="I24" s="106"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
       <c r="J24" s="91" t="s">
         <v>110</v>
       </c>
@@ -2070,9 +2062,9 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="110"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104"/>
       <c r="J25" s="91"/>
       <c r="K25" s="91"/>
       <c r="L25" s="16"/>
@@ -2084,9 +2076,9 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="98"/>
       <c r="J26" s="91"/>
       <c r="K26" s="91"/>
       <c r="L26" s="16"/>
@@ -2108,17 +2100,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="101" t="s">
+      <c r="B28" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="103" t="s">
+      <c r="G28" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="104"/>
+      <c r="H28" s="106"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2141,8 +2133,8 @@
       </c>
       <c r="H29" s="93"/>
       <c r="I29" s="83"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
       <c r="L29" s="84"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -2160,8 +2152,8 @@
       </c>
       <c r="H30" s="93"/>
       <c r="I30" s="83"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
       <c r="L30" s="84"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -2181,8 +2173,8 @@
       </c>
       <c r="H31" s="93"/>
       <c r="I31" s="83"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
       <c r="L31" s="84"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -2230,68 +2222,48 @@
       <c r="E34" s="86"/>
       <c r="F34" s="87"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="94" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="95" t="s">
+      <c r="B35" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="95"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
-      <c r="F35" s="95"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="94"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="95"/>
-      <c r="C37" s="95"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="95"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="95"/>
-      <c r="C38" s="95"/>
-      <c r="D38" s="95"/>
-      <c r="E38" s="95"/>
-      <c r="F38" s="95"/>
+      <c r="B38" s="94"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
+      <c r="F38" s="94"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="94"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="95"/>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="95"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="94"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="94"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2308,7 +2280,9 @@
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
       <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="E41" s="107" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F41" s="29"/>
       <c r="G41" s="29"/>
       <c r="H41" s="10"/>
@@ -2319,9 +2293,9 @@
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
+      <c r="E42" s="107"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -2331,9 +2305,9 @@
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -2343,9 +2317,9 @@
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
+      <c r="E44" s="107"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
       <c r="H44" s="24"/>
       <c r="I44" s="24"/>
       <c r="J44" s="24"/>
@@ -2354,9 +2328,9 @@
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
+      <c r="E45" s="107"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
@@ -2365,9 +2339,9 @@
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
@@ -2376,9 +2350,9 @@
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
+      <c r="E47" s="107"/>
+      <c r="F47" s="108"/>
+      <c r="G47" s="108"/>
       <c r="H47" s="17"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -2387,7 +2361,7 @@
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
+      <c r="E48" s="107"/>
       <c r="F48" s="29"/>
       <c r="G48" s="29"/>
     </row>
@@ -2401,6 +2375,7 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="E41:E48"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="G28:H28"/>
@@ -2435,7 +2410,6 @@
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="G30:H30"/>
-    <mergeCell ref="H34:J39"/>
     <mergeCell ref="B35:F39"/>
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="I32:L32"/>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="761" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC6B85E-805A-4A0F-AC84-A7CE4808D1D7}"/>
+  <xr:revisionPtr revIDLastSave="772" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A587D404-6800-4221-BE89-519C547051E0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -864,6 +864,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -882,24 +927,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -915,12 +942,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -930,14 +951,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -978,11 +993,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1002,9 +1047,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1014,46 +1056,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1173,7 +1175,6 @@
   <rv s="0">
     <v>0</v>
     <v>5</v>
-    <v>image</v>
   </rv>
 </rvData>
 </file>
@@ -1183,7 +1184,6 @@
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
   </s>
 </rvStructures>
 </file>
@@ -1538,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBA1999-1CF9-4903-BA7D-DD523B82D6C3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:O49"/>
+  <dimension ref="B2:O51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1575,46 +1575,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="62"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="47"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="62"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="66"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="73"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1633,133 +1633,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="59"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="68"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="81" t="s">
+      <c r="C7" s="76"/>
+      <c r="D7" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="81"/>
+      <c r="E7" s="86"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="77" t="s">
+      <c r="I7" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="60" t="s">
+      <c r="J7" s="82"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="61"/>
+      <c r="M7" s="70"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="82" t="str">
+      <c r="C8" s="78"/>
+      <c r="D8" s="87" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="82"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="54"/>
-      <c r="I8" s="79" t="s">
+      <c r="H8" s="50"/>
+      <c r="I8" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="62" t="s">
+      <c r="J8" s="84"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="63"/>
+      <c r="M8" s="54"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="48" t="str">
+      <c r="C9" s="78"/>
+      <c r="D9" s="63" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="50"/>
+      <c r="E9" s="65"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="55"/>
-      <c r="I9" s="79" t="s">
+      <c r="H9" s="51"/>
+      <c r="I9" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="79"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="62" t="s">
+      <c r="J9" s="84"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="63"/>
+      <c r="M9" s="54"/>
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="83" t="s">
+      <c r="C10" s="78"/>
+      <c r="D10" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="84"/>
+      <c r="E10" s="59"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="56" t="s">
+      <c r="G10" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="56"/>
-      <c r="I10" s="52" t="s">
+      <c r="H10" s="52"/>
+      <c r="I10" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="52"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="62" t="s">
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="63"/>
+      <c r="M10" s="54"/>
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="83" t="s">
+      <c r="C11" s="78"/>
+      <c r="D11" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="84"/>
+      <c r="E11" s="59"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1786,88 +1786,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="67" t="s">
+      <c r="H14" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="51" t="s">
+      <c r="I14" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51" t="s">
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="51"/>
+      <c r="N14" s="47"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="74"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="74"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="51"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="47"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="97" t="s">
+      <c r="K16" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="97"/>
+      <c r="L16" s="89"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1903,10 +1903,10 @@
       <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="75" t="s">
+      <c r="K17" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="75"/>
+      <c r="L17" s="80"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1925,8 +1925,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1940,10 +1940,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="99" t="s">
+      <c r="K19" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="99"/>
+      <c r="L19" s="92"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1967,63 +1967,63 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="101" t="s">
+      <c r="B21" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="94"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="51" t="s">
+      <c r="G22" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51" t="s">
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51" t="s">
+      <c r="K22" s="47"/>
+      <c r="L22" s="47" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="74"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2062,9 +2062,9 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="97"/>
       <c r="J25" s="91"/>
       <c r="K25" s="91"/>
       <c r="L25" s="16"/>
@@ -2076,9 +2076,9 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="98"/>
-      <c r="I26" s="98"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
       <c r="J26" s="91"/>
       <c r="K26" s="91"/>
       <c r="L26" s="16"/>
@@ -2100,17 +2100,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="100" t="s">
+      <c r="B28" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
+      <c r="C28" s="93"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="105" t="s">
+      <c r="G28" s="98" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="106"/>
+      <c r="H28" s="99"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2125,17 +2125,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="92" t="s">
+      <c r="G29" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="93"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="84"/>
+      <c r="H29" s="107"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="59"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2147,14 +2147,14 @@
       <c r="D30" s="91"/>
       <c r="E30" s="91"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="92" t="s">
+      <c r="G30" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="93"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="84"/>
+      <c r="H30" s="107"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="59"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2168,14 +2168,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="92" t="s">
+      <c r="G31" s="106" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="93"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="84"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="59"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2189,14 +2189,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="88" t="s">
+      <c r="G32" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="89"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="47"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="62"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2214,56 +2214,76 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
       <c r="G34" s="10"/>
+      <c r="H34" s="46" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="108" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
       <c r="G35" s="29"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="94"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
       <c r="G36" s="29"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="29"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="94"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="94"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="29"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
       <c r="G39" s="29"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2280,9 +2300,7 @@
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
       <c r="D41" s="29"/>
-      <c r="E41" s="107" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="E41" s="29"/>
       <c r="F41" s="29"/>
       <c r="G41" s="29"/>
       <c r="H41" s="10"/>
@@ -2293,9 +2311,7 @@
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
+      <c r="E42" s="29"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -2305,9 +2321,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
+      <c r="E43" s="29"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -2317,9 +2331,7 @@
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
-      <c r="E44" s="107"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
+      <c r="E44" s="29"/>
       <c r="H44" s="24"/>
       <c r="I44" s="24"/>
       <c r="J44" s="24"/>
@@ -2328,9 +2340,7 @@
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
-      <c r="E45" s="107"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="108"/>
+      <c r="E45" s="29"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
@@ -2339,9 +2349,7 @@
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
+      <c r="E46" s="29"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
@@ -2350,9 +2358,7 @@
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
-      <c r="E47" s="107"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
+      <c r="E47" s="29"/>
       <c r="H47" s="17"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -2361,11 +2367,11 @@
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="D48" s="29"/>
-      <c r="E48" s="107"/>
+      <c r="E48" s="29"/>
       <c r="F48" s="29"/>
       <c r="G48" s="29"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
@@ -2373,15 +2379,23 @@
       <c r="F49" s="29"/>
       <c r="G49" s="29"/>
     </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J51" s="45"/>
+    </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="E41:E48"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B35:F39"/>
+    <mergeCell ref="I31:L31"/>
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="I14:I16"/>
     <mergeCell ref="J14:L15"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
@@ -2403,25 +2417,6 @@
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="B21:L21"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="B35:F39"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I9:K9"/>
@@ -2433,19 +2428,33 @@
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="F14:F16"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="H34:J39"/>
     <mergeCell ref="M14:N15"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="L7:M7"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L9:M9"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
     <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G28:H28"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -3214,29 +3223,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3433,25 +3419,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3468,4 +3459,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bayergroup-my.sharepoint.com/personal/kosal_kirthiga_ext_bayer_com/Documents/Desktop/ThailandLates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHMHV\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="772" documentId="8_{DE39F225-2AE1-4446-AB5F-E204FEABCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A587D404-6800-4221-BE89-519C547051E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38E8596-0C53-468E-88CD-BB6E0AB3C7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="18975" windowHeight="9195" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -32,28 +32,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -867,9 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -904,19 +880,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -951,9 +954,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -969,10 +969,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -993,41 +993,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1052,9 +1031,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1126,72 +1102,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>21167</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>21168</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>973666</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>21166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50A1767-231E-B5ED-57E9-BF5A3261A4D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9694334" y="6932085"/>
+          <a:ext cx="1841499" cy="952498"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1575,46 +1532,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="60"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="60" t="s">
+      <c r="J3" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="82"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1633,67 +1590,67 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="68"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="77"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="86" t="s">
+      <c r="C7" s="84"/>
+      <c r="D7" s="94" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="86"/>
+      <c r="E7" s="94"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="82" t="s">
+      <c r="I7" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="82"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="69" t="s">
+      <c r="J7" s="90"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="70"/>
+      <c r="M7" s="79"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="78"/>
-      <c r="D8" s="87" t="str">
+      <c r="C8" s="86"/>
+      <c r="D8" s="95" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="87"/>
+      <c r="E8" s="95"/>
       <c r="F8" s="40"/>
       <c r="G8" s="50" t="s">
         <v>71</v>
       </c>
       <c r="H8" s="50"/>
-      <c r="I8" s="84" t="s">
+      <c r="I8" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="85"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="93"/>
       <c r="L8" s="53" t="s">
         <v>72</v>
       </c>
@@ -1701,25 +1658,25 @@
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="63" t="str">
+      <c r="C9" s="86"/>
+      <c r="D9" s="72" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="65"/>
+      <c r="E9" s="74"/>
       <c r="F9" s="40"/>
       <c r="G9" s="51" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="51"/>
-      <c r="I9" s="84" t="s">
+      <c r="I9" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="84"/>
-      <c r="K9" s="85"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="93"/>
       <c r="L9" s="53" t="s">
         <v>74</v>
       </c>
@@ -1727,14 +1684,14 @@
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="58" t="s">
+      <c r="C10" s="86"/>
+      <c r="D10" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="59"/>
+      <c r="E10" s="63"/>
       <c r="F10" s="10"/>
       <c r="G10" s="52" t="s">
         <v>7</v>
@@ -1752,14 +1709,14 @@
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="78"/>
-      <c r="D11" s="58" t="s">
+      <c r="C11" s="86"/>
+      <c r="D11" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="59"/>
+      <c r="E11" s="63"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1786,24 +1743,24 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="88"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="87" t="s">
         <v>76</v>
       </c>
       <c r="C14" s="47" t="s">
@@ -1838,7 +1795,7 @@
       <c r="N14" s="47"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="79"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="47"/>
       <c r="D15" s="47"/>
       <c r="E15" s="47"/>
@@ -1853,7 +1810,7 @@
       <c r="N15" s="47"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="79"/>
+      <c r="B16" s="87"/>
       <c r="C16" s="47"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -1864,10 +1821,10 @@
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="89" t="s">
+      <c r="K16" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="89"/>
+      <c r="L16" s="98"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1903,10 +1860,10 @@
       <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="80" t="s">
+      <c r="K17" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="80"/>
+      <c r="L17" s="64"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1925,8 +1882,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1940,10 +1897,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="92" t="s">
+      <c r="K19" s="99" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="92"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1967,23 +1924,23 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="87" t="s">
         <v>76</v>
       </c>
       <c r="C22" s="47" t="s">
@@ -2013,7 +1970,7 @@
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="79"/>
+      <c r="B23" s="87"/>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
@@ -2042,15 +1999,15 @@
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="91" t="s">
+      <c r="G24" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91" t="s">
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="91"/>
+      <c r="K24" s="69"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
@@ -2062,11 +2019,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
@@ -2076,11 +2033,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
@@ -2100,17 +2057,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="98" t="s">
+      <c r="G28" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="99"/>
+      <c r="H28" s="71"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2125,17 +2082,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="106" t="s">
+      <c r="G29" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="107"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="59"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="63"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2144,17 +2101,17 @@
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="106" t="s">
+      <c r="G30" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="107"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="59"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="63"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2168,14 +2125,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="106" t="s">
+      <c r="G31" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="107"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="59"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="63"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2189,14 +2146,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="103" t="s">
+      <c r="G32" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="104"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="62"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="60"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2214,72 +2171,70 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="100" t="s">
+      <c r="B34" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="46" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="108" t="s">
+      <c r="B35" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="108"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="100"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="108"/>
-      <c r="C39" s="108"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="108"/>
+      <c r="B39" s="100"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="100"/>
       <c r="G39" s="29"/>
       <c r="H39" s="46"/>
       <c r="I39" s="46"/>
@@ -2383,7 +2338,9 @@
       <c r="J51" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="70">
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="K19:L19"/>
     <mergeCell ref="B35:F39"/>
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="G14:G16"/>
@@ -2399,12 +2356,6 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="K16:L16"/>
     <mergeCell ref="I29:L29"/>
     <mergeCell ref="J22:K23"/>
     <mergeCell ref="G26:I26"/>
@@ -2412,7 +2363,7 @@
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="L22:L23"/>
-    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="G22:I23"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="B21:L21"/>
@@ -2425,6 +2376,10 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="F14:F16"/>
@@ -2439,7 +2394,6 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H34:J39"/>
     <mergeCell ref="M14:N15"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="G8:H8"/>
@@ -2469,6 +2423,7 @@
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHMHV\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38E8596-0C53-468E-88CD-BB6E0AB3C7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9419719E-963E-4454-BBA4-4F014989B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="18975" windowHeight="9195" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -32,6 +32,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -845,10 +867,147 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -864,12 +1023,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -879,24 +1032,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -912,125 +1047,14 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1102,53 +1126,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>21167</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>21168</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>973666</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>21166</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50A1767-231E-B5ED-57E9-BF5A3261A4D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9694334" y="6932085"/>
-          <a:ext cx="1841499" cy="952498"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1532,46 +1571,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="79"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="60"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="79"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="72"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="82"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1590,133 +1629,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="77"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="83"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="94" t="s">
+      <c r="C7" s="90"/>
+      <c r="D7" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="94"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="90" t="s">
+      <c r="I7" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="90"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="78" t="s">
+      <c r="J7" s="65"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="79"/>
+      <c r="M7" s="85"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="95" t="str">
+      <c r="C8" s="92"/>
+      <c r="D8" s="70" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="95"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="50"/>
-      <c r="I8" s="92" t="s">
+      <c r="H8" s="95"/>
+      <c r="I8" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="92"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="53" t="s">
+      <c r="J8" s="67"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="54"/>
+      <c r="M8" s="75"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="72" t="str">
+      <c r="C9" s="92"/>
+      <c r="D9" s="71" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="74"/>
+      <c r="E9" s="72"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="51" t="s">
+      <c r="G9" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="92" t="s">
+      <c r="H9" s="96"/>
+      <c r="I9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="53" t="s">
+      <c r="J9" s="67"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="54"/>
+      <c r="M9" s="75"/>
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="61" t="s">
+      <c r="C10" s="92"/>
+      <c r="D10" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="63"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="52"/>
-      <c r="I10" s="48" t="s">
+      <c r="H10" s="97"/>
+      <c r="I10" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="53" t="s">
+      <c r="J10" s="93"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="54"/>
+      <c r="M10" s="75"/>
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="61" t="s">
+      <c r="C11" s="92"/>
+      <c r="D11" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="63"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1743,88 +1782,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47" t="s">
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="47"/>
+      <c r="N14" s="46"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="87"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="87"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="47"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="46"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="98" t="s">
+      <c r="K16" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="98"/>
+      <c r="L16" s="76"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1860,10 +1899,10 @@
       <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="64" t="s">
+      <c r="K17" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="64"/>
+      <c r="L17" s="101"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1882,8 +1921,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1897,10 +1936,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="99" t="s">
+      <c r="K19" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="99"/>
+      <c r="L19" s="47"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1924,63 +1963,63 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="47" t="s">
+      <c r="E22" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47" t="s">
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47" t="s">
+      <c r="K22" s="46"/>
+      <c r="L22" s="46" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="87"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1999,15 +2038,15 @@
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="69" t="s">
+      <c r="G24" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69" t="s">
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="69"/>
+      <c r="K24" s="58"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
@@ -2019,11 +2058,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
@@ -2033,11 +2072,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
@@ -2057,17 +2096,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="70" t="s">
+      <c r="G28" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="71"/>
+      <c r="H28" s="107"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2082,17 +2121,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="107" t="s">
+      <c r="G29" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="108"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="63"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="51"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2101,17 +2140,17 @@
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="107" t="s">
+      <c r="G30" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="108"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="63"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2125,14 +2164,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="107" t="s">
+      <c r="G31" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="108"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="63"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="51"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2146,14 +2185,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="104" t="s">
+      <c r="G32" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="105"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="60"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="79"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2171,74 +2210,76 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="101" t="s">
+      <c r="B34" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="103"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="100" t="s">
+      <c r="B35" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="100"/>
-      <c r="D35" s="100"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="100"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
+      <c r="I35" s="108" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J35" s="108"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="100"/>
-      <c r="C36" s="100"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="100"/>
-      <c r="C37" s="100"/>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
       <c r="G37" s="29"/>
       <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="100"/>
-      <c r="C38" s="100"/>
-      <c r="D38" s="100"/>
-      <c r="E38" s="100"/>
-      <c r="F38" s="100"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
       <c r="G38" s="29"/>
       <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="100"/>
-      <c r="C39" s="100"/>
-      <c r="D39" s="100"/>
-      <c r="E39" s="100"/>
-      <c r="F39" s="100"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2247,9 +2288,9 @@
       <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="29"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="29"/>
@@ -2338,7 +2379,62 @@
       <c r="J51" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="I35:J40"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="M14:N15"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="B35:F39"/>
@@ -2355,60 +2451,6 @@
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="G22:I23"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="M14:N15"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G28:H28"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25:D26" xr:uid="{B316A799-CF60-4C99-A88E-2204076E38E6}">
@@ -2423,7 +2465,6 @@
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3178,6 +3219,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075F372E8CCA016418A193AD921508903" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f5e922417d740f1a527805650dc2dfa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399317f3-0083-4d0b-9572-12af99626311" xmlns:ns3="1444eecc-14bb-4066-abe6-ce6de21d9439" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="078d79524add6eac9b94134ca637184e" ns2:_="" ns3:_="">
     <xsd:import namespace="399317f3-0083-4d0b-9572-12af99626311"/>
@@ -3374,30 +3438,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="1444eecc-14bb-4066-abe6-ce6de21d9439">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399317f3-0083-4d0b-9572-12af99626311"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF88A1C-AA0D-4F8F-A0FD-6F3FAFCA9DC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3414,22 +3480,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A00E6A9-20DD-4842-9306-307EB080AF2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHQUT\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHMHV\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9419719E-963E-4454-BBA4-4F014989B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ECB580-A460-4417-90A6-8EB7C7BA10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="18975" windowHeight="9195" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="3" r:id="rId1"/>
@@ -32,28 +32,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -772,7 +750,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -867,6 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1126,68 +1105,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>52916</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>914545</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>52916</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F78D5277-9880-4CA1-9F61-2DE6FEFC8117}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9726083" y="6995584"/>
+          <a:ext cx="1750629" cy="920749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1571,46 +1541,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="80"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="77" t="s">
+      <c r="J3" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="80"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="72"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="73"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="86" t="s">
+      <c r="J4" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1629,133 +1599,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="84"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="69" t="s">
+      <c r="C7" s="91"/>
+      <c r="D7" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="69"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="65" t="s">
+      <c r="I7" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="65"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="84" t="s">
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="85"/>
+      <c r="M7" s="86"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="70" t="str">
+      <c r="C8" s="93"/>
+      <c r="D8" s="71" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="70"/>
+      <c r="E8" s="71"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="95" t="s">
+      <c r="G8" s="96" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="67" t="s">
+      <c r="H8" s="96"/>
+      <c r="I8" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="74" t="s">
+      <c r="J8" s="68"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="75"/>
+      <c r="M8" s="76"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="71" t="str">
+      <c r="C9" s="93"/>
+      <c r="D9" s="72" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="72"/>
+      <c r="E9" s="73"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="96" t="s">
+      <c r="G9" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="96"/>
-      <c r="I9" s="67" t="s">
+      <c r="H9" s="97"/>
+      <c r="I9" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="74" t="s">
+      <c r="J9" s="68"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="75"/>
+      <c r="M9" s="76"/>
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="49" t="s">
+      <c r="C10" s="93"/>
+      <c r="D10" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="51"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="97"/>
-      <c r="I10" s="93" t="s">
+      <c r="H10" s="98"/>
+      <c r="I10" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="74" t="s">
+      <c r="J10" s="94"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="75"/>
+      <c r="M10" s="76"/>
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="92"/>
-      <c r="D11" s="49" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="51"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1782,88 +1752,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="73"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="73"/>
-      <c r="N13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="98" t="s">
+      <c r="H14" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="46" t="s">
+      <c r="I14" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="46" t="s">
+      <c r="J14" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46" t="s">
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="46"/>
+      <c r="N14" s="47"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="64"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="64"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="46"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="47"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="76" t="s">
+      <c r="K16" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="76"/>
+      <c r="L16" s="77"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1899,10 +1869,10 @@
       <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="101" t="s">
+      <c r="K17" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="101"/>
+      <c r="L17" s="102"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1921,8 +1891,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1936,10 +1906,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="47" t="s">
+      <c r="K19" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="47"/>
+      <c r="L19" s="48"/>
       <c r="M19" s="37" t="s">
         <v>55</v>
       </c>
@@ -1963,63 +1933,63 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
       <c r="M21" s="10"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E22" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="F22" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46" t="s">
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46" t="s">
+      <c r="K22" s="47"/>
+      <c r="L22" s="47" t="s">
         <v>89</v>
       </c>
       <c r="M22" s="10"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="64"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2038,15 +2008,15 @@
       <c r="F24" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="58" t="s">
+      <c r="G24" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58" t="s">
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="58"/>
+      <c r="K24" s="59"/>
       <c r="L24" s="16" t="s">
         <v>25</v>
       </c>
@@ -2058,11 +2028,11 @@
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
       <c r="L25" s="16"/>
       <c r="M25" s="10"/>
     </row>
@@ -2072,11 +2042,11 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
       <c r="L26" s="16"/>
       <c r="M26" s="10"/>
     </row>
@@ -2096,17 +2066,17 @@
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="106" t="s">
+      <c r="G28" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="107"/>
+      <c r="H28" s="108"/>
       <c r="I28" s="27" t="s">
         <v>92</v>
       </c>
@@ -2121,17 +2091,17 @@
         <v>93</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="59" t="s">
+      <c r="G29" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="60"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="51"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="52"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
@@ -2140,17 +2110,17 @@
         <v>95</v>
       </c>
       <c r="C30" s="20"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="60"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="51"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="52"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
@@ -2164,14 +2134,14 @@
         <v>98</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="59" t="s">
+      <c r="G31" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="60"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="51"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="52"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
@@ -2185,14 +2155,14 @@
         <v>98</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="55" t="s">
+      <c r="G32" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="56"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="79"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="80"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="10"/>
@@ -2210,76 +2180,74 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="55"/>
       <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="109"/>
       <c r="J34" s="29"/>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="108" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J35" s="108"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="29"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="108"/>
-      <c r="J36" s="108"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="108"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="29"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="48"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
       <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="108"/>
-      <c r="J39" s="108"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="109"/>
+      <c r="J39" s="46"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2288,9 +2256,9 @@
       <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="108"/>
-      <c r="J40" s="108"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="29"/>
@@ -2380,7 +2348,7 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="I35:J40"/>
+    <mergeCell ref="H34:I39"/>
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="I30:L30"/>
     <mergeCell ref="K17:L17"/>
@@ -2465,6 +2433,7 @@
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;22&amp;KFF8939 RESTRICTED</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3449,16 +3418,9 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EBE950A-5812-419E-B174-6A5D9B8E0414}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="1444eecc-14bb-4066-abe6-ce6de21d9439"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399317f3-0083-4d0b-9572-12af99626311"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHMHV\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ECB580-A460-4417-90A6-8EB7C7BA10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD26EB38-52AB-4F09-BD45-BA62FBD55816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="18975" windowHeight="9195" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -1107,18 +1107,18 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>52916</xdr:colOff>
+      <xdr:colOff>74083</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>84667</xdr:rowOff>
+      <xdr:rowOff>148167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>914545</xdr:colOff>
+      <xdr:colOff>935712</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>52916</xdr:rowOff>
+      <xdr:rowOff>116416</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1147,7 +1147,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9726083" y="6995584"/>
+          <a:off x="9747250" y="7059084"/>
           <a:ext cx="1750629" cy="920749"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/srv/xlsx-templates/TH - Quotation Template.xlsx
+++ b/srv/xlsx-templates/TH - Quotation Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EHMHV\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD26EB38-52AB-4F09-BD45-BA62FBD55816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BC1848-C142-4F90-8E00-555F39087203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="18975" windowHeight="9195" xr2:uid="{F5CC2154-27BB-4652-B61E-D913F0CC6809}"/>
   </bookViews>
@@ -846,24 +846,171 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -882,158 +1029,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1107,7 +1107,7 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>74083</xdr:colOff>
@@ -1541,46 +1541,46 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="80"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="10"/>
       <c r="I3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="78" t="s">
+      <c r="J3" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="80"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="50"/>
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="73"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
       <c r="H4" s="10"/>
       <c r="I4" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="87" t="s">
+      <c r="J4" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="89"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="80"/>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1599,133 +1599,133 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="84"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="75"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="91"/>
-      <c r="D7" s="70" t="s">
+      <c r="C7" s="82"/>
+      <c r="D7" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="70"/>
+      <c r="E7" s="93"/>
       <c r="F7" s="40"/>
       <c r="G7" s="42" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="42"/>
-      <c r="I7" s="66" t="s">
+      <c r="I7" s="89" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="66"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="85" t="s">
+      <c r="J7" s="89"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="86"/>
+      <c r="M7" s="77"/>
       <c r="N7" s="43"/>
     </row>
     <row r="8" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="71" t="str">
+      <c r="C8" s="84"/>
+      <c r="D8" s="94" t="str">
         <f>Settings!A14</f>
         <v>${offerValidation.CUSTOMER_CODE}</v>
       </c>
-      <c r="E8" s="71"/>
+      <c r="E8" s="94"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="96" t="s">
+      <c r="G8" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="68" t="s">
+      <c r="H8" s="97"/>
+      <c r="I8" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="68"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="75" t="s">
+      <c r="J8" s="91"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="76"/>
+      <c r="M8" s="65"/>
       <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="72" t="str">
+      <c r="C9" s="84"/>
+      <c r="D9" s="69" t="str">
         <f>Settings!A9</f>
         <v>${offerValidation.INSTITUTENAME}</v>
       </c>
-      <c r="E9" s="73"/>
+      <c r="E9" s="71"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="97" t="s">
+      <c r="G9" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="97"/>
-      <c r="I9" s="68" t="s">
+      <c r="H9" s="62"/>
+      <c r="I9" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="75" t="s">
+      <c r="J9" s="91"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="76"/>
+      <c r="M9" s="65"/>
       <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="52"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="98" t="s">
+      <c r="G10" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="98"/>
-      <c r="I10" s="94" t="s">
+      <c r="H10" s="63"/>
+      <c r="I10" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="75" t="s">
+      <c r="J10" s="86"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="76"/>
+      <c r="M10" s="65"/>
       <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="84"/>
+      <c r="D11" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="52"/>
+      <c r="E11" s="53"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1752,88 +1752,88 @@
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="99" t="s">
+      <c r="H14" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47" t="s">
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="47"/>
+      <c r="N14" s="72"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="65"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
     </row>
     <row r="16" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="65"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="47"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="72"/>
       <c r="J16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="77" t="s">
+      <c r="K16" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="77"/>
+      <c r="L16" s="96"/>
       <c r="M16" s="11" t="s">
         <v>81</v>
       </c>
@@ -1869,10 +1869,10 @@
       <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="102" t="s">
+      <c r="K17" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="102"/>
+      <c r="L17" s="54"/>
       <c r="M17" s="41" t="s">
         <v>37</v>
       </c>
@@ -1891,8 +1891,8 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="55"/>
       <c r="M18" s="14"/>
       <c r="N18" s="36"/>
     </row>
@@ -1906,10 +1906,10 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="48" t="s">
+      <c r="K19" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="48"/>
+      <c r="L19" s="100"/>
       <c r="M19" s="